--- a/산출물/01_기획/4팀_WBS.xlsx
+++ b/산출물/01_기획/4팀_WBS.xlsx
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB114"/>
+  <dimension ref="A1:BB117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col width="4.25" customWidth="1" style="103" min="1" max="1"/>
@@ -1325,7 +1325,7 @@
       <c r="N5" s="105" t="n"/>
       <c r="O5" s="105" t="n"/>
       <c r="P5" s="26" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="Q5" s="105" t="n"/>
       <c r="R5" s="105" t="n"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C26" s="82" t="inlineStr">
         <is>
-          <t>10/14 개정 동기화(에이전트 재구성·3인)</t>
+          <t>10/14~15 개정 동기화(에이전트·MVP 재정의)</t>
         </is>
       </c>
       <c r="D26" s="96" t="inlineStr">
@@ -3350,175 +3350,175 @@
       <c r="BA30" s="72" t="n"/>
       <c r="BB30" s="75" t="n"/>
     </row>
-    <row r="31" outlineLevel="1" ht="21" customHeight="1" s="103">
-      <c r="A31" s="47" t="n"/>
-      <c r="B31" s="48" t="n">
+    <row r="31" outlineLevel="1" ht="17.25" customHeight="1" s="103">
+      <c r="A31" s="59" t="n"/>
+      <c r="B31" s="60" t="inlineStr">
+        <is>
+          <t>1.5.5</t>
+        </is>
+      </c>
+      <c r="C31" s="82" t="inlineStr">
+        <is>
+          <t>10/15 MVP 재정의: 기획서·요구사항·WBS 정리</t>
+        </is>
+      </c>
+      <c r="D31" s="96" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F31" s="63" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G31" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="77" t="n"/>
+      <c r="J31" s="79" t="n"/>
+      <c r="K31" s="72" t="n"/>
+      <c r="L31" s="72" t="n"/>
+      <c r="M31" s="72" t="n"/>
+      <c r="N31" s="70" t="n"/>
+      <c r="O31" s="71" t="n"/>
+      <c r="P31" s="71" t="n"/>
+      <c r="Q31" s="71" t="n"/>
+      <c r="R31" s="70" t="n"/>
+      <c r="S31" s="72" t="n"/>
+      <c r="T31" s="72" t="n"/>
+      <c r="U31" s="72" t="n"/>
+      <c r="V31" s="68" t="n"/>
+      <c r="W31" s="72" t="n"/>
+      <c r="X31" s="72" t="n"/>
+      <c r="Y31" s="72" t="n"/>
+      <c r="Z31" s="72" t="n"/>
+      <c r="AA31" s="72" t="n"/>
+      <c r="AB31" s="72" t="n"/>
+      <c r="AC31" s="73" t="n"/>
+      <c r="AD31" s="73" t="n"/>
+      <c r="AE31" s="73" t="n"/>
+      <c r="AF31" s="73" t="n"/>
+      <c r="AG31" s="73" t="n"/>
+      <c r="AH31" s="72" t="n"/>
+      <c r="AI31" s="72" t="n"/>
+      <c r="AJ31" s="72" t="n"/>
+      <c r="AK31" s="72" t="n"/>
+      <c r="AL31" s="72" t="n"/>
+      <c r="AM31" s="72" t="n"/>
+      <c r="AN31" s="72" t="n"/>
+      <c r="AO31" s="72" t="n"/>
+      <c r="AP31" s="72" t="n"/>
+      <c r="AQ31" s="72" t="n"/>
+      <c r="AR31" s="74" t="n"/>
+      <c r="AS31" s="74" t="n"/>
+      <c r="AT31" s="74" t="n"/>
+      <c r="AU31" s="74" t="n"/>
+      <c r="AV31" s="74" t="n"/>
+      <c r="AW31" s="72" t="n"/>
+      <c r="AX31" s="72" t="n"/>
+      <c r="AY31" s="72" t="n"/>
+      <c r="AZ31" s="72" t="n"/>
+      <c r="BA31" s="72" t="n"/>
+      <c r="BB31" s="75" t="n"/>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" s="103">
+      <c r="A32" s="47" t="n"/>
+      <c r="B32" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="49" t="inlineStr">
+      <c r="C32" s="49" t="inlineStr">
         <is>
           <t>데이터 수집 및 저장</t>
         </is>
       </c>
-      <c r="D31" s="50" t="n"/>
-      <c r="E31" s="51" t="n">
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="51" t="n">
         <v>46296</v>
       </c>
-      <c r="F31" s="51" t="n">
+      <c r="F32" s="51" t="n">
         <v>46323</v>
       </c>
-      <c r="G31" s="52" t="n">
+      <c r="G32" s="52" t="n">
         <v>18</v>
       </c>
-      <c r="H31" s="53" t="n">
+      <c r="H32" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="58" t="n"/>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="111" t="n"/>
-      <c r="L31" s="112" t="n"/>
-      <c r="M31" s="85" t="n"/>
-      <c r="N31" s="85" t="n"/>
-      <c r="O31" s="85" t="n"/>
-      <c r="P31" s="85" t="n"/>
-      <c r="Q31" s="85" t="n"/>
-      <c r="R31" s="85" t="n"/>
-      <c r="S31" s="85" t="n"/>
-      <c r="T31" s="85" t="n"/>
-      <c r="U31" s="85" t="n"/>
-      <c r="V31" s="85" t="n"/>
-      <c r="W31" s="85" t="n"/>
-      <c r="X31" s="85" t="n"/>
-      <c r="Y31" s="85" t="n"/>
-      <c r="Z31" s="85" t="n"/>
-      <c r="AA31" s="85" t="n"/>
-      <c r="AB31" s="85" t="n"/>
-      <c r="AC31" s="85" t="n"/>
-      <c r="AD31" s="85" t="n"/>
-      <c r="AE31" s="85" t="n"/>
-      <c r="AF31" s="58" t="n"/>
-      <c r="AG31" s="58" t="n"/>
-      <c r="AH31" s="58" t="n"/>
-      <c r="AI31" s="58" t="n"/>
-      <c r="AJ31" s="58" t="n"/>
-      <c r="AK31" s="58" t="n"/>
-      <c r="AL31" s="58" t="n"/>
-      <c r="AM31" s="58" t="n"/>
-      <c r="AN31" s="58" t="n"/>
-      <c r="AO31" s="58" t="n"/>
-      <c r="AP31" s="58" t="n"/>
-      <c r="AQ31" s="58" t="n"/>
-      <c r="AR31" s="58" t="n"/>
-      <c r="AS31" s="58" t="n"/>
-      <c r="AT31" s="58" t="n"/>
-      <c r="AU31" s="58" t="n"/>
-      <c r="AV31" s="58" t="n"/>
-      <c r="AW31" s="58" t="n"/>
-      <c r="AX31" s="58" t="n"/>
-      <c r="AY31" s="58" t="n"/>
-      <c r="AZ31" s="58" t="n"/>
-      <c r="BA31" s="58" t="n"/>
-      <c r="BB31" s="29" t="n"/>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" s="103">
-      <c r="A32" s="59" t="n"/>
-      <c r="B32" s="60" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C32" s="61" t="inlineStr">
-        <is>
-          <t>[2주] 수집 데이터 보고서</t>
-        </is>
-      </c>
-      <c r="D32" s="96" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="E32" s="63" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F32" s="63" t="n">
-        <v>46303</v>
-      </c>
-      <c r="G32" s="64" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="77" t="n"/>
-      <c r="J32" s="79" t="n"/>
-      <c r="K32" s="72" t="n"/>
-      <c r="L32" s="88" t="n"/>
-      <c r="M32" s="88" t="n"/>
-      <c r="N32" s="88" t="n"/>
-      <c r="O32" s="88" t="n"/>
-      <c r="P32" s="88" t="n"/>
-      <c r="Q32" s="89" t="n"/>
-      <c r="R32" s="70" t="n"/>
-      <c r="S32" s="72" t="n"/>
-      <c r="T32" s="72" t="n"/>
-      <c r="U32" s="72" t="n"/>
-      <c r="V32" s="72" t="n"/>
-      <c r="W32" s="72" t="n"/>
-      <c r="X32" s="72" t="n"/>
-      <c r="Y32" s="72" t="n"/>
-      <c r="Z32" s="72" t="n"/>
-      <c r="AA32" s="72" t="n"/>
-      <c r="AB32" s="72" t="n"/>
-      <c r="AC32" s="73" t="n"/>
-      <c r="AD32" s="73" t="n"/>
-      <c r="AE32" s="73" t="n"/>
-      <c r="AF32" s="73" t="n"/>
-      <c r="AG32" s="73" t="n"/>
-      <c r="AH32" s="72" t="n"/>
-      <c r="AI32" s="72" t="n"/>
-      <c r="AJ32" s="72" t="n"/>
-      <c r="AK32" s="72" t="n"/>
-      <c r="AL32" s="72" t="n"/>
-      <c r="AM32" s="72" t="n"/>
-      <c r="AN32" s="72" t="n"/>
-      <c r="AO32" s="72" t="n"/>
-      <c r="AP32" s="72" t="n"/>
-      <c r="AQ32" s="72" t="n"/>
-      <c r="AR32" s="74" t="n"/>
-      <c r="AS32" s="74" t="n"/>
-      <c r="AT32" s="74" t="n"/>
-      <c r="AU32" s="74" t="n"/>
-      <c r="AV32" s="74" t="n"/>
-      <c r="AW32" s="72" t="n"/>
-      <c r="AX32" s="72" t="n"/>
-      <c r="AY32" s="72" t="n"/>
-      <c r="AZ32" s="72" t="n"/>
-      <c r="BA32" s="72" t="n"/>
-      <c r="BB32" s="75" t="n"/>
+      <c r="I32" s="58" t="n"/>
+      <c r="J32" s="84" t="n"/>
+      <c r="K32" s="111" t="n"/>
+      <c r="L32" s="112" t="n"/>
+      <c r="M32" s="85" t="n"/>
+      <c r="N32" s="85" t="n"/>
+      <c r="O32" s="85" t="n"/>
+      <c r="P32" s="85" t="n"/>
+      <c r="Q32" s="85" t="n"/>
+      <c r="R32" s="85" t="n"/>
+      <c r="S32" s="85" t="n"/>
+      <c r="T32" s="85" t="n"/>
+      <c r="U32" s="85" t="n"/>
+      <c r="V32" s="85" t="n"/>
+      <c r="W32" s="85" t="n"/>
+      <c r="X32" s="85" t="n"/>
+      <c r="Y32" s="85" t="n"/>
+      <c r="Z32" s="85" t="n"/>
+      <c r="AA32" s="85" t="n"/>
+      <c r="AB32" s="85" t="n"/>
+      <c r="AC32" s="85" t="n"/>
+      <c r="AD32" s="85" t="n"/>
+      <c r="AE32" s="85" t="n"/>
+      <c r="AF32" s="58" t="n"/>
+      <c r="AG32" s="58" t="n"/>
+      <c r="AH32" s="58" t="n"/>
+      <c r="AI32" s="58" t="n"/>
+      <c r="AJ32" s="58" t="n"/>
+      <c r="AK32" s="58" t="n"/>
+      <c r="AL32" s="58" t="n"/>
+      <c r="AM32" s="58" t="n"/>
+      <c r="AN32" s="58" t="n"/>
+      <c r="AO32" s="58" t="n"/>
+      <c r="AP32" s="58" t="n"/>
+      <c r="AQ32" s="58" t="n"/>
+      <c r="AR32" s="58" t="n"/>
+      <c r="AS32" s="58" t="n"/>
+      <c r="AT32" s="58" t="n"/>
+      <c r="AU32" s="58" t="n"/>
+      <c r="AV32" s="58" t="n"/>
+      <c r="AW32" s="58" t="n"/>
+      <c r="AX32" s="58" t="n"/>
+      <c r="AY32" s="58" t="n"/>
+      <c r="AZ32" s="58" t="n"/>
+      <c r="BA32" s="58" t="n"/>
+      <c r="BB32" s="29" t="n"/>
     </row>
     <row r="33" ht="17.25" customHeight="1" s="103">
       <c r="A33" s="59" t="n"/>
-      <c r="B33" s="60" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="C33" s="82" t="inlineStr">
-        <is>
-          <t>거래 API 필드·접근·출처·이용조건 확인</t>
+      <c r="B33" s="60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C33" s="61" t="inlineStr">
+        <is>
+          <t>[2주] 수집 데이터 보고서</t>
         </is>
       </c>
       <c r="D33" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E33" s="63" t="n">
         <v>46296</v>
       </c>
       <c r="F33" s="63" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="G33" s="64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" s="65" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
       <c r="N33" s="88" t="n"/>
       <c r="O33" s="88" t="n"/>
       <c r="P33" s="88" t="n"/>
-      <c r="Q33" s="71" t="n"/>
+      <c r="Q33" s="89" t="n"/>
       <c r="R33" s="70" t="n"/>
       <c r="S33" s="72" t="n"/>
       <c r="T33" s="72" t="n"/>
@@ -3574,17 +3574,17 @@
       <c r="A34" s="59" t="n"/>
       <c r="B34" s="60" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C34" s="82" t="inlineStr">
         <is>
-          <t>예산 정책·금융 교육 지식원 확보</t>
+          <t>거래 API 필드·접근·출처·이용조건 확인</t>
         </is>
       </c>
       <c r="D34" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E34" s="63" t="n">
@@ -3650,27 +3650,27 @@
       <c r="A35" s="59" t="n"/>
       <c r="B35" s="60" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C35" s="82" t="inlineStr">
         <is>
-          <t>합성·수동 대체데이터 확보·탐색·필터링</t>
+          <t>예산 정책·생활비 참고 자료 확보</t>
         </is>
       </c>
       <c r="D35" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E35" s="63" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="F35" s="63" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="G35" s="64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="65" t="n">
         <v>0</v>
@@ -3678,12 +3678,12 @@
       <c r="I35" s="77" t="n"/>
       <c r="J35" s="79" t="n"/>
       <c r="K35" s="72" t="n"/>
-      <c r="L35" s="72" t="n"/>
-      <c r="M35" s="72" t="n"/>
-      <c r="N35" s="70" t="n"/>
+      <c r="L35" s="88" t="n"/>
+      <c r="M35" s="88" t="n"/>
+      <c r="N35" s="88" t="n"/>
       <c r="O35" s="88" t="n"/>
       <c r="P35" s="88" t="n"/>
-      <c r="Q35" s="88" t="n"/>
+      <c r="Q35" s="71" t="n"/>
       <c r="R35" s="70" t="n"/>
       <c r="S35" s="72" t="n"/>
       <c r="T35" s="72" t="n"/>
@@ -3726,27 +3726,27 @@
       <c r="A36" s="59" t="n"/>
       <c r="B36" s="60" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="C36" s="82" t="inlineStr">
         <is>
-          <t>수집 보고서·개인정보 검토·제출</t>
+          <t>합성·수동 대체데이터 확보·탐색·필터링</t>
         </is>
       </c>
       <c r="D36" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E36" s="63" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="F36" s="63" t="n">
         <v>46303</v>
       </c>
       <c r="G36" s="64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="65" t="n">
         <v>0</v>
@@ -3757,7 +3757,7 @@
       <c r="L36" s="72" t="n"/>
       <c r="M36" s="72" t="n"/>
       <c r="N36" s="70" t="n"/>
-      <c r="O36" s="71" t="n"/>
+      <c r="O36" s="88" t="n"/>
       <c r="P36" s="88" t="n"/>
       <c r="Q36" s="88" t="n"/>
       <c r="R36" s="70" t="n"/>
@@ -3800,12 +3800,14 @@
     </row>
     <row r="37" ht="17.25" customHeight="1" s="103">
       <c r="A37" s="59" t="n"/>
-      <c r="B37" s="60" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C37" s="61" t="inlineStr">
-        <is>
-          <t>[3주] DB·저장소 설계 문서</t>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+      <c r="C37" s="82" t="inlineStr">
+        <is>
+          <t>수집 보고서·개인정보 검토·제출</t>
         </is>
       </c>
       <c r="D37" s="96" t="inlineStr">
@@ -3814,13 +3816,13 @@
         </is>
       </c>
       <c r="E37" s="63" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" s="63" t="n">
-        <v>46311</v>
+        <v>46303</v>
       </c>
       <c r="G37" s="64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H37" s="65" t="n">
         <v>0</v>
@@ -3831,15 +3833,15 @@
       <c r="L37" s="72" t="n"/>
       <c r="M37" s="72" t="n"/>
       <c r="N37" s="70" t="n"/>
-      <c r="O37" s="88" t="n"/>
+      <c r="O37" s="71" t="n"/>
       <c r="P37" s="88" t="n"/>
       <c r="Q37" s="88" t="n"/>
-      <c r="R37" s="88" t="n"/>
-      <c r="S37" s="88" t="n"/>
-      <c r="T37" s="88" t="n"/>
-      <c r="U37" s="88" t="n"/>
-      <c r="V37" s="88" t="n"/>
-      <c r="W37" s="89" t="n"/>
+      <c r="R37" s="70" t="n"/>
+      <c r="S37" s="72" t="n"/>
+      <c r="T37" s="72" t="n"/>
+      <c r="U37" s="72" t="n"/>
+      <c r="V37" s="72" t="n"/>
+      <c r="W37" s="72" t="n"/>
       <c r="X37" s="72" t="n"/>
       <c r="Y37" s="72" t="n"/>
       <c r="Z37" s="72" t="n"/>
@@ -3874,14 +3876,12 @@
     </row>
     <row r="38" outlineLevel="1" ht="17.25" customHeight="1" s="103">
       <c r="A38" s="59" t="n"/>
-      <c r="B38" s="60" t="inlineStr">
-        <is>
-          <t>2.2.1</t>
-        </is>
-      </c>
-      <c r="C38" s="82" t="inlineStr">
-        <is>
-          <t>DB·API 입출력·상태·변경규칙 v1 합의</t>
+      <c r="B38" s="60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C38" s="61" t="inlineStr">
+        <is>
+          <t>[3주] DB·저장소 설계 문서</t>
         </is>
       </c>
       <c r="D38" s="96" t="inlineStr">
@@ -3893,10 +3893,10 @@
         <v>46301</v>
       </c>
       <c r="F38" s="63" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="G38" s="64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H38" s="65" t="n">
         <v>0</v>
@@ -3913,9 +3913,9 @@
       <c r="R38" s="88" t="n"/>
       <c r="S38" s="88" t="n"/>
       <c r="T38" s="88" t="n"/>
-      <c r="U38" s="72" t="n"/>
-      <c r="V38" s="72" t="n"/>
-      <c r="W38" s="72" t="n"/>
+      <c r="U38" s="88" t="n"/>
+      <c r="V38" s="88" t="n"/>
+      <c r="W38" s="89" t="n"/>
       <c r="X38" s="72" t="n"/>
       <c r="Y38" s="72" t="n"/>
       <c r="Z38" s="72" t="n"/>
@@ -3952,27 +3952,27 @@
       <c r="A39" s="59" t="n"/>
       <c r="B39" s="60" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C39" s="82" t="inlineStr">
         <is>
-          <t>예산 버전·조정 모드·승인 이력 스키마</t>
+          <t>DB·API 입출력·상태·변경규칙 v1 합의</t>
         </is>
       </c>
       <c r="D39" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E39" s="63" t="n">
-        <v>46307</v>
+        <v>46301</v>
       </c>
       <c r="F39" s="63" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G39" s="64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39" s="65" t="n">
         <v>0</v>
@@ -3983,13 +3983,13 @@
       <c r="L39" s="72" t="n"/>
       <c r="M39" s="72" t="n"/>
       <c r="N39" s="70" t="n"/>
-      <c r="O39" s="71" t="n"/>
-      <c r="P39" s="71" t="n"/>
-      <c r="Q39" s="71" t="n"/>
-      <c r="R39" s="70" t="n"/>
+      <c r="O39" s="88" t="n"/>
+      <c r="P39" s="88" t="n"/>
+      <c r="Q39" s="88" t="n"/>
+      <c r="R39" s="88" t="n"/>
       <c r="S39" s="88" t="n"/>
       <c r="T39" s="88" t="n"/>
-      <c r="U39" s="88" t="n"/>
+      <c r="U39" s="72" t="n"/>
       <c r="V39" s="72" t="n"/>
       <c r="W39" s="72" t="n"/>
       <c r="X39" s="72" t="n"/>
@@ -4028,24 +4028,24 @@
       <c r="A40" s="59" t="n"/>
       <c r="B40" s="60" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C40" s="82" t="inlineStr">
         <is>
-          <t>보안·무결성·권한 v1 승인(Agent 무쓰기)</t>
+          <t>예산 버전·조정 모드·승인 이력 스키마</t>
         </is>
       </c>
       <c r="D40" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E40" s="63" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F40" s="63" t="n">
         <v>46309</v>
-      </c>
-      <c r="F40" s="63" t="n">
-        <v>46311</v>
       </c>
       <c r="G40" s="64" t="n">
         <v>3</v>
@@ -4063,11 +4063,11 @@
       <c r="P40" s="71" t="n"/>
       <c r="Q40" s="71" t="n"/>
       <c r="R40" s="70" t="n"/>
-      <c r="S40" s="72" t="n"/>
-      <c r="T40" s="72" t="n"/>
+      <c r="S40" s="88" t="n"/>
+      <c r="T40" s="88" t="n"/>
       <c r="U40" s="88" t="n"/>
-      <c r="V40" s="88" t="n"/>
-      <c r="W40" s="88" t="n"/>
+      <c r="V40" s="72" t="n"/>
+      <c r="W40" s="72" t="n"/>
       <c r="X40" s="72" t="n"/>
       <c r="Y40" s="72" t="n"/>
       <c r="Z40" s="72" t="n"/>
@@ -4104,17 +4104,17 @@
       <c r="A41" s="59" t="n"/>
       <c r="B41" s="60" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C41" s="82" t="inlineStr">
         <is>
-          <t>라우터 진입점·조정 모드·LLM 출력 7항목 합의</t>
+          <t>보안·무결성·권한 v1 승인(Agent 무쓰기)</t>
         </is>
       </c>
       <c r="D41" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E41" s="63" t="n">
@@ -4178,12 +4178,14 @@
     </row>
     <row r="42" ht="17.25" customHeight="1" s="103">
       <c r="A42" s="59" t="n"/>
-      <c r="B42" s="60" t="n">
-        <v>2.3</v>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
       </c>
       <c r="C42" s="82" t="inlineStr">
         <is>
-          <t>v5 추가 데이터 확보·검증 과제</t>
+          <t>라우터 진입점·조정 모드·LLM 출력 7항목 합의</t>
         </is>
       </c>
       <c r="D42" s="96" t="inlineStr">
@@ -4192,13 +4194,13 @@
         </is>
       </c>
       <c r="E42" s="63" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="F42" s="63" t="n">
-        <v>46323</v>
+        <v>46311</v>
       </c>
       <c r="G42" s="64" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H42" s="65" t="n">
         <v>0</v>
@@ -4213,19 +4215,19 @@
       <c r="P42" s="71" t="n"/>
       <c r="Q42" s="71" t="n"/>
       <c r="R42" s="70" t="n"/>
-      <c r="S42" s="88" t="n"/>
-      <c r="T42" s="88" t="n"/>
+      <c r="S42" s="72" t="n"/>
+      <c r="T42" s="72" t="n"/>
       <c r="U42" s="88" t="n"/>
       <c r="V42" s="88" t="n"/>
       <c r="W42" s="88" t="n"/>
-      <c r="X42" s="88" t="n"/>
-      <c r="Y42" s="88" t="n"/>
-      <c r="Z42" s="88" t="n"/>
-      <c r="AA42" s="88" t="n"/>
-      <c r="AB42" s="88" t="n"/>
-      <c r="AC42" s="88" t="n"/>
-      <c r="AD42" s="88" t="n"/>
-      <c r="AE42" s="88" t="n"/>
+      <c r="X42" s="72" t="n"/>
+      <c r="Y42" s="72" t="n"/>
+      <c r="Z42" s="72" t="n"/>
+      <c r="AA42" s="72" t="n"/>
+      <c r="AB42" s="72" t="n"/>
+      <c r="AC42" s="73" t="n"/>
+      <c r="AD42" s="73" t="n"/>
+      <c r="AE42" s="73" t="n"/>
       <c r="AF42" s="73" t="n"/>
       <c r="AG42" s="73" t="n"/>
       <c r="AH42" s="72" t="n"/>
@@ -4252,29 +4254,27 @@
     </row>
     <row r="43" outlineLevel="1" ht="17.25" customHeight="1" s="103">
       <c r="A43" s="59" t="n"/>
-      <c r="B43" s="60" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
+      <c r="B43" s="60" t="n">
+        <v>2.3</v>
       </c>
       <c r="C43" s="82" t="inlineStr">
         <is>
-          <t>MDIS·KOSIS 가계동향 확보·변수 결합 확인</t>
+          <t>v5 추가 데이터 확보·검증 과제</t>
         </is>
       </c>
       <c r="D43" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E43" s="63" t="n">
         <v>46307</v>
       </c>
       <c r="F43" s="63" t="n">
-        <v>46310</v>
+        <v>46323</v>
       </c>
       <c r="G43" s="64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H43" s="65" t="n">
         <v>0</v>
@@ -4293,15 +4293,15 @@
       <c r="T43" s="88" t="n"/>
       <c r="U43" s="88" t="n"/>
       <c r="V43" s="88" t="n"/>
-      <c r="W43" s="72" t="n"/>
-      <c r="X43" s="72" t="n"/>
-      <c r="Y43" s="72" t="n"/>
-      <c r="Z43" s="72" t="n"/>
-      <c r="AA43" s="72" t="n"/>
-      <c r="AB43" s="72" t="n"/>
-      <c r="AC43" s="73" t="n"/>
-      <c r="AD43" s="73" t="n"/>
-      <c r="AE43" s="73" t="n"/>
+      <c r="W43" s="88" t="n"/>
+      <c r="X43" s="88" t="n"/>
+      <c r="Y43" s="88" t="n"/>
+      <c r="Z43" s="88" t="n"/>
+      <c r="AA43" s="88" t="n"/>
+      <c r="AB43" s="88" t="n"/>
+      <c r="AC43" s="88" t="n"/>
+      <c r="AD43" s="88" t="n"/>
+      <c r="AE43" s="88" t="n"/>
       <c r="AF43" s="73" t="n"/>
       <c r="AG43" s="73" t="n"/>
       <c r="AH43" s="72" t="n"/>
@@ -4330,27 +4330,27 @@
       <c r="A44" s="59" t="n"/>
       <c r="B44" s="60" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C44" s="82" t="inlineStr">
         <is>
-          <t>CODEF 대출 조회 항목·기관 범위 연동 테스트</t>
+          <t>MDIS·KOSIS 가계동향 확보·변수 결합 확인</t>
         </is>
       </c>
       <c r="D44" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E44" s="63" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="F44" s="63" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="G44" s="64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" s="65" t="n">
         <v>0</v>
@@ -4365,11 +4365,11 @@
       <c r="P44" s="71" t="n"/>
       <c r="Q44" s="71" t="n"/>
       <c r="R44" s="70" t="n"/>
-      <c r="S44" s="72" t="n"/>
-      <c r="T44" s="72" t="n"/>
+      <c r="S44" s="88" t="n"/>
+      <c r="T44" s="88" t="n"/>
       <c r="U44" s="88" t="n"/>
       <c r="V44" s="88" t="n"/>
-      <c r="W44" s="88" t="n"/>
+      <c r="W44" s="72" t="n"/>
       <c r="X44" s="72" t="n"/>
       <c r="Y44" s="72" t="n"/>
       <c r="Z44" s="72" t="n"/>
@@ -4406,17 +4406,17 @@
       <c r="A45" s="59" t="n"/>
       <c r="B45" s="60" t="inlineStr">
         <is>
-          <t>2.3.3</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C45" s="82" t="inlineStr">
         <is>
-          <t>(3차) 복지 API·대출 상품 데이터 범위 확인</t>
+          <t>CODEF 대출 조회 항목·기관 범위 연동 테스트</t>
         </is>
       </c>
       <c r="D45" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E45" s="63" t="n">
@@ -4482,24 +4482,24 @@
       <c r="A46" s="59" t="n"/>
       <c r="B46" s="60" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.3</t>
         </is>
       </c>
       <c r="C46" s="82" t="inlineStr">
         <is>
-          <t>(검증) 카드 OCR·BIN 식별 지원 범위 검증</t>
+          <t>(3차) 복지 API·대출 상품 데이터 범위 확인</t>
         </is>
       </c>
       <c r="D46" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E46" s="63" t="n">
-        <v>46321</v>
+        <v>46309</v>
       </c>
       <c r="F46" s="63" t="n">
-        <v>46323</v>
+        <v>46311</v>
       </c>
       <c r="G46" s="64" t="n">
         <v>3</v>
@@ -4519,17 +4519,17 @@
       <c r="R46" s="70" t="n"/>
       <c r="S46" s="72" t="n"/>
       <c r="T46" s="72" t="n"/>
-      <c r="U46" s="72" t="n"/>
-      <c r="V46" s="72" t="n"/>
-      <c r="W46" s="72" t="n"/>
+      <c r="U46" s="88" t="n"/>
+      <c r="V46" s="88" t="n"/>
+      <c r="W46" s="88" t="n"/>
       <c r="X46" s="72" t="n"/>
       <c r="Y46" s="72" t="n"/>
       <c r="Z46" s="72" t="n"/>
       <c r="AA46" s="72" t="n"/>
       <c r="AB46" s="72" t="n"/>
-      <c r="AC46" s="88" t="n"/>
-      <c r="AD46" s="88" t="n"/>
-      <c r="AE46" s="88" t="n"/>
+      <c r="AC46" s="73" t="n"/>
+      <c r="AD46" s="73" t="n"/>
+      <c r="AE46" s="73" t="n"/>
       <c r="AF46" s="73" t="n"/>
       <c r="AG46" s="73" t="n"/>
       <c r="AH46" s="72" t="n"/>
@@ -4555,174 +4555,174 @@
       <c r="BB46" s="75" t="n"/>
     </row>
     <row r="47" ht="21" customHeight="1" s="103">
-      <c r="A47" s="47" t="n"/>
-      <c r="B47" s="48" t="n">
+      <c r="A47" s="59" t="n"/>
+      <c r="B47" s="60" t="inlineStr">
+        <is>
+          <t>2.3.4</t>
+        </is>
+      </c>
+      <c r="C47" s="82" t="inlineStr">
+        <is>
+          <t>(검증) 카드 OCR·BIN 식별 지원 범위 검증</t>
+        </is>
+      </c>
+      <c r="D47" s="96" t="inlineStr">
+        <is>
+          <t>김혜리</t>
+        </is>
+      </c>
+      <c r="E47" s="63" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F47" s="63" t="n">
+        <v>46323</v>
+      </c>
+      <c r="G47" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="49" t="inlineStr">
+      <c r="H47" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="77" t="n"/>
+      <c r="J47" s="79" t="n"/>
+      <c r="K47" s="72" t="n"/>
+      <c r="L47" s="72" t="n"/>
+      <c r="M47" s="72" t="n"/>
+      <c r="N47" s="70" t="n"/>
+      <c r="O47" s="71" t="n"/>
+      <c r="P47" s="71" t="n"/>
+      <c r="Q47" s="71" t="n"/>
+      <c r="R47" s="70" t="n"/>
+      <c r="S47" s="72" t="n"/>
+      <c r="T47" s="72" t="n"/>
+      <c r="U47" s="72" t="n"/>
+      <c r="V47" s="72" t="n"/>
+      <c r="W47" s="72" t="n"/>
+      <c r="X47" s="72" t="n"/>
+      <c r="Y47" s="72" t="n"/>
+      <c r="Z47" s="72" t="n"/>
+      <c r="AA47" s="72" t="n"/>
+      <c r="AB47" s="72" t="n"/>
+      <c r="AC47" s="88" t="n"/>
+      <c r="AD47" s="88" t="n"/>
+      <c r="AE47" s="88" t="n"/>
+      <c r="AF47" s="73" t="n"/>
+      <c r="AG47" s="73" t="n"/>
+      <c r="AH47" s="72" t="n"/>
+      <c r="AI47" s="72" t="n"/>
+      <c r="AJ47" s="72" t="n"/>
+      <c r="AK47" s="72" t="n"/>
+      <c r="AL47" s="72" t="n"/>
+      <c r="AM47" s="72" t="n"/>
+      <c r="AN47" s="72" t="n"/>
+      <c r="AO47" s="72" t="n"/>
+      <c r="AP47" s="72" t="n"/>
+      <c r="AQ47" s="72" t="n"/>
+      <c r="AR47" s="74" t="n"/>
+      <c r="AS47" s="74" t="n"/>
+      <c r="AT47" s="74" t="n"/>
+      <c r="AU47" s="74" t="n"/>
+      <c r="AV47" s="74" t="n"/>
+      <c r="AW47" s="72" t="n"/>
+      <c r="AX47" s="72" t="n"/>
+      <c r="AY47" s="72" t="n"/>
+      <c r="AZ47" s="72" t="n"/>
+      <c r="BA47" s="72" t="n"/>
+      <c r="BB47" s="75" t="n"/>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" s="103">
+      <c r="A48" s="47" t="n"/>
+      <c r="B48" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
         <is>
           <t>데이터 전처리</t>
         </is>
       </c>
-      <c r="D47" s="50" t="n"/>
-      <c r="E47" s="51" t="n">
+      <c r="D48" s="50" t="n"/>
+      <c r="E48" s="51" t="n">
         <v>46307</v>
       </c>
-      <c r="F47" s="51" t="n">
+      <c r="F48" s="51" t="n">
         <v>46318</v>
       </c>
-      <c r="G47" s="52" t="n">
+      <c r="G48" s="52" t="n">
         <v>10</v>
       </c>
-      <c r="H47" s="53" t="n">
+      <c r="H48" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="58" t="n"/>
-      <c r="J47" s="84" t="n"/>
-      <c r="K47" s="111" t="n"/>
-      <c r="L47" s="111" t="n"/>
-      <c r="M47" s="58" t="n"/>
-      <c r="N47" s="57" t="n"/>
-      <c r="O47" s="58" t="n"/>
-      <c r="P47" s="58" t="n"/>
-      <c r="Q47" s="58" t="n"/>
-      <c r="R47" s="57" t="n"/>
-      <c r="S47" s="90" t="n"/>
-      <c r="T47" s="90" t="n"/>
-      <c r="U47" s="90" t="n"/>
-      <c r="V47" s="90" t="n"/>
-      <c r="W47" s="90" t="n"/>
-      <c r="X47" s="90" t="n"/>
-      <c r="Y47" s="90" t="n"/>
-      <c r="Z47" s="90" t="n"/>
-      <c r="AA47" s="90" t="n"/>
-      <c r="AB47" s="90" t="n"/>
-      <c r="AC47" s="58" t="n"/>
-      <c r="AD47" s="58" t="n"/>
-      <c r="AE47" s="58" t="n"/>
-      <c r="AF47" s="58" t="n"/>
-      <c r="AG47" s="58" t="n"/>
-      <c r="AH47" s="58" t="n"/>
-      <c r="AI47" s="58" t="n"/>
-      <c r="AJ47" s="58" t="n"/>
-      <c r="AK47" s="58" t="n"/>
-      <c r="AL47" s="58" t="n"/>
-      <c r="AM47" s="58" t="n"/>
-      <c r="AN47" s="58" t="n"/>
-      <c r="AO47" s="58" t="n"/>
-      <c r="AP47" s="58" t="n"/>
-      <c r="AQ47" s="58" t="n"/>
-      <c r="AR47" s="58" t="n"/>
-      <c r="AS47" s="58" t="n"/>
-      <c r="AT47" s="58" t="n"/>
-      <c r="AU47" s="58" t="n"/>
-      <c r="AV47" s="58" t="n"/>
-      <c r="AW47" s="58" t="n"/>
-      <c r="AX47" s="58" t="n"/>
-      <c r="AY47" s="58" t="n"/>
-      <c r="AZ47" s="58" t="n"/>
-      <c r="BA47" s="58" t="n"/>
-      <c r="BB47" s="29" t="n"/>
-    </row>
-    <row r="48" ht="17.25" customHeight="1" s="103">
-      <c r="A48" s="59" t="n"/>
-      <c r="B48" s="60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C48" s="61" t="inlineStr">
-        <is>
-          <t>[3주] 데이터 전처리 결과서</t>
-        </is>
-      </c>
-      <c r="D48" s="96" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="E48" s="63" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F48" s="63" t="n">
-        <v>46311</v>
-      </c>
-      <c r="G48" s="64" t="n">
-        <v>5</v>
-      </c>
-      <c r="H48" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="77" t="n"/>
-      <c r="J48" s="79" t="n"/>
-      <c r="K48" s="72" t="n"/>
-      <c r="L48" s="72" t="n"/>
-      <c r="M48" s="72" t="n"/>
-      <c r="N48" s="70" t="n"/>
-      <c r="O48" s="71" t="n"/>
-      <c r="P48" s="71" t="n"/>
-      <c r="Q48" s="71" t="n"/>
-      <c r="R48" s="70" t="n"/>
-      <c r="S48" s="91" t="n"/>
-      <c r="T48" s="91" t="n"/>
-      <c r="U48" s="91" t="n"/>
-      <c r="V48" s="91" t="n"/>
-      <c r="W48" s="92" t="n"/>
-      <c r="X48" s="72" t="n"/>
-      <c r="Y48" s="72" t="n"/>
-      <c r="Z48" s="72" t="n"/>
-      <c r="AA48" s="72" t="n"/>
-      <c r="AB48" s="72" t="n"/>
-      <c r="AC48" s="73" t="n"/>
-      <c r="AD48" s="73" t="n"/>
-      <c r="AE48" s="73" t="n"/>
-      <c r="AF48" s="73" t="n"/>
-      <c r="AG48" s="73" t="n"/>
-      <c r="AH48" s="72" t="n"/>
-      <c r="AI48" s="72" t="n"/>
-      <c r="AJ48" s="72" t="n"/>
-      <c r="AK48" s="72" t="n"/>
-      <c r="AL48" s="72" t="n"/>
-      <c r="AM48" s="72" t="n"/>
-      <c r="AN48" s="72" t="n"/>
-      <c r="AO48" s="72" t="n"/>
-      <c r="AP48" s="72" t="n"/>
-      <c r="AQ48" s="72" t="n"/>
-      <c r="AR48" s="74" t="n"/>
-      <c r="AS48" s="74" t="n"/>
-      <c r="AT48" s="74" t="n"/>
-      <c r="AU48" s="74" t="n"/>
-      <c r="AV48" s="74" t="n"/>
-      <c r="AW48" s="72" t="n"/>
-      <c r="AX48" s="72" t="n"/>
-      <c r="AY48" s="72" t="n"/>
-      <c r="AZ48" s="72" t="n"/>
-      <c r="BA48" s="72" t="n"/>
-      <c r="BB48" s="75" t="n"/>
+      <c r="I48" s="58" t="n"/>
+      <c r="J48" s="84" t="n"/>
+      <c r="K48" s="111" t="n"/>
+      <c r="L48" s="111" t="n"/>
+      <c r="M48" s="58" t="n"/>
+      <c r="N48" s="57" t="n"/>
+      <c r="O48" s="58" t="n"/>
+      <c r="P48" s="58" t="n"/>
+      <c r="Q48" s="58" t="n"/>
+      <c r="R48" s="57" t="n"/>
+      <c r="S48" s="90" t="n"/>
+      <c r="T48" s="90" t="n"/>
+      <c r="U48" s="90" t="n"/>
+      <c r="V48" s="90" t="n"/>
+      <c r="W48" s="90" t="n"/>
+      <c r="X48" s="90" t="n"/>
+      <c r="Y48" s="90" t="n"/>
+      <c r="Z48" s="90" t="n"/>
+      <c r="AA48" s="90" t="n"/>
+      <c r="AB48" s="90" t="n"/>
+      <c r="AC48" s="58" t="n"/>
+      <c r="AD48" s="58" t="n"/>
+      <c r="AE48" s="58" t="n"/>
+      <c r="AF48" s="58" t="n"/>
+      <c r="AG48" s="58" t="n"/>
+      <c r="AH48" s="58" t="n"/>
+      <c r="AI48" s="58" t="n"/>
+      <c r="AJ48" s="58" t="n"/>
+      <c r="AK48" s="58" t="n"/>
+      <c r="AL48" s="58" t="n"/>
+      <c r="AM48" s="58" t="n"/>
+      <c r="AN48" s="58" t="n"/>
+      <c r="AO48" s="58" t="n"/>
+      <c r="AP48" s="58" t="n"/>
+      <c r="AQ48" s="58" t="n"/>
+      <c r="AR48" s="58" t="n"/>
+      <c r="AS48" s="58" t="n"/>
+      <c r="AT48" s="58" t="n"/>
+      <c r="AU48" s="58" t="n"/>
+      <c r="AV48" s="58" t="n"/>
+      <c r="AW48" s="58" t="n"/>
+      <c r="AX48" s="58" t="n"/>
+      <c r="AY48" s="58" t="n"/>
+      <c r="AZ48" s="58" t="n"/>
+      <c r="BA48" s="58" t="n"/>
+      <c r="BB48" s="29" t="n"/>
     </row>
     <row r="49" ht="17.25" customHeight="1" s="103">
       <c r="A49" s="59" t="n"/>
-      <c r="B49" s="60" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="C49" s="82" t="inlineStr">
-        <is>
-          <t>거래 정제·상가정보 업종→카테고리 매핑</t>
+      <c r="B49" s="60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C49" s="61" t="inlineStr">
+        <is>
+          <t>[3주] 데이터 전처리 결과서</t>
         </is>
       </c>
       <c r="D49" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E49" s="63" t="n">
         <v>46307</v>
       </c>
       <c r="F49" s="63" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="G49" s="64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H49" s="65" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
       <c r="T49" s="91" t="n"/>
       <c r="U49" s="91" t="n"/>
       <c r="V49" s="91" t="n"/>
-      <c r="W49" s="72" t="n"/>
+      <c r="W49" s="92" t="n"/>
       <c r="X49" s="72" t="n"/>
       <c r="Y49" s="72" t="n"/>
       <c r="Z49" s="72" t="n"/>
@@ -4778,17 +4778,17 @@
       <c r="A50" s="59" t="n"/>
       <c r="B50" s="60" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="C50" s="82" t="inlineStr">
         <is>
-          <t>가계동향 카테고리·가구 범위·단위 정리</t>
+          <t>거래 정제·상가정보 업종→카테고리 매핑</t>
         </is>
       </c>
       <c r="D50" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E50" s="63" t="n">
@@ -4854,27 +4854,27 @@
       <c r="A51" s="59" t="n"/>
       <c r="B51" s="60" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="C51" s="82" t="inlineStr">
         <is>
-          <t>가맹점·사용자·시간 단위 분할·누수 검증</t>
+          <t>가계동향 카테고리·가구 범위·단위 정리</t>
         </is>
       </c>
       <c r="D51" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E51" s="63" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F51" s="63" t="n">
         <v>46310</v>
       </c>
       <c r="G51" s="64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="65" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
       <c r="P51" s="71" t="n"/>
       <c r="Q51" s="71" t="n"/>
       <c r="R51" s="70" t="n"/>
-      <c r="S51" s="72" t="n"/>
+      <c r="S51" s="91" t="n"/>
       <c r="T51" s="91" t="n"/>
       <c r="U51" s="91" t="n"/>
       <c r="V51" s="91" t="n"/>
@@ -4930,27 +4930,27 @@
       <c r="A52" s="59" t="n"/>
       <c r="B52" s="60" t="inlineStr">
         <is>
-          <t>3.1.4</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="C52" s="82" t="inlineStr">
         <is>
-          <t>전처리 결과서 작성·검토·제출</t>
+          <t>가맹점·사용자·시간 단위 분할·누수 검증</t>
         </is>
       </c>
       <c r="D52" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E52" s="63" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F52" s="63" t="n">
         <v>46310</v>
       </c>
-      <c r="F52" s="63" t="n">
-        <v>46311</v>
-      </c>
       <c r="G52" s="64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" s="65" t="n">
         <v>0</v>
@@ -4966,10 +4966,10 @@
       <c r="Q52" s="71" t="n"/>
       <c r="R52" s="70" t="n"/>
       <c r="S52" s="72" t="n"/>
-      <c r="T52" s="72" t="n"/>
-      <c r="U52" s="72" t="n"/>
+      <c r="T52" s="91" t="n"/>
+      <c r="U52" s="91" t="n"/>
       <c r="V52" s="91" t="n"/>
-      <c r="W52" s="91" t="n"/>
+      <c r="W52" s="72" t="n"/>
       <c r="X52" s="72" t="n"/>
       <c r="Y52" s="72" t="n"/>
       <c r="Z52" s="72" t="n"/>
@@ -5004,12 +5004,14 @@
     </row>
     <row r="53" ht="17.25" customHeight="1" s="103">
       <c r="A53" s="59" t="n"/>
-      <c r="B53" s="60" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C53" s="61" t="inlineStr">
-        <is>
-          <t>[4주] ML/DL 학습결과서</t>
+      <c r="B53" s="60" t="inlineStr">
+        <is>
+          <t>3.1.4</t>
+        </is>
+      </c>
+      <c r="C53" s="82" t="inlineStr">
+        <is>
+          <t>전처리 결과서 작성·검토·제출</t>
         </is>
       </c>
       <c r="D53" s="96" t="inlineStr">
@@ -5021,10 +5023,10 @@
         <v>46310</v>
       </c>
       <c r="F53" s="63" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="G53" s="64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H53" s="65" t="n">
         <v>0</v>
@@ -5044,11 +5046,11 @@
       <c r="U53" s="72" t="n"/>
       <c r="V53" s="91" t="n"/>
       <c r="W53" s="91" t="n"/>
-      <c r="X53" s="91" t="n"/>
-      <c r="Y53" s="91" t="n"/>
-      <c r="Z53" s="91" t="n"/>
-      <c r="AA53" s="91" t="n"/>
-      <c r="AB53" s="92" t="n"/>
+      <c r="X53" s="72" t="n"/>
+      <c r="Y53" s="72" t="n"/>
+      <c r="Z53" s="72" t="n"/>
+      <c r="AA53" s="72" t="n"/>
+      <c r="AB53" s="72" t="n"/>
       <c r="AC53" s="73" t="n"/>
       <c r="AD53" s="73" t="n"/>
       <c r="AE53" s="73" t="n"/>
@@ -5078,29 +5080,27 @@
     </row>
     <row r="54" ht="17.25" customHeight="1" s="103">
       <c r="A54" s="59" t="n"/>
-      <c r="B54" s="60" t="inlineStr">
-        <is>
-          <t>3.2.1</t>
-        </is>
-      </c>
-      <c r="C54" s="82" t="inlineStr">
-        <is>
-          <t>거래 분류: 기준선→학습·확신도 보정·기준값</t>
+      <c r="B54" s="60" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C54" s="61" t="inlineStr">
+        <is>
+          <t>[4주] ML/DL 학습결과서</t>
         </is>
       </c>
       <c r="D54" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E54" s="63" t="n">
         <v>46310</v>
       </c>
       <c r="F54" s="63" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="G54" s="64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H54" s="65" t="n">
         <v>0</v>
@@ -5124,7 +5124,7 @@
       <c r="Y54" s="91" t="n"/>
       <c r="Z54" s="91" t="n"/>
       <c r="AA54" s="91" t="n"/>
-      <c r="AB54" s="72" t="n"/>
+      <c r="AB54" s="92" t="n"/>
       <c r="AC54" s="73" t="n"/>
       <c r="AD54" s="73" t="n"/>
       <c r="AE54" s="73" t="n"/>
@@ -5156,17 +5156,17 @@
       <c r="A55" s="59" t="n"/>
       <c r="B55" s="60" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C55" s="82" t="inlineStr">
         <is>
-          <t>카테고리 비율 예측: 기준선 vs 회귀(MAE)</t>
+          <t>거래 분류: 기준선→학습·확신도 보정·기준값</t>
         </is>
       </c>
       <c r="D55" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E55" s="63" t="n">
@@ -5232,27 +5232,27 @@
       <c r="A56" s="59" t="n"/>
       <c r="B56" s="60" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C56" s="82" t="inlineStr">
         <is>
-          <t>(2차) 또래 비교 회귀: 기준선 vs 회귀(R²)</t>
+          <t>카테고리 비율 예측: 기준선 vs 회귀(MAE)</t>
         </is>
       </c>
       <c r="D56" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E56" s="63" t="n">
         <v>46310</v>
       </c>
       <c r="F56" s="63" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="G56" s="64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H56" s="65" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
       <c r="X56" s="91" t="n"/>
       <c r="Y56" s="91" t="n"/>
       <c r="Z56" s="91" t="n"/>
-      <c r="AA56" s="72" t="n"/>
+      <c r="AA56" s="91" t="n"/>
       <c r="AB56" s="72" t="n"/>
       <c r="AC56" s="73" t="n"/>
       <c r="AD56" s="73" t="n"/>
@@ -5308,27 +5308,27 @@
       <c r="A57" s="59" t="n"/>
       <c r="B57" s="60" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C57" s="82" t="inlineStr">
         <is>
-          <t>모델 3종 비교·학습결과서 검토·제출</t>
+          <t>(2차) 또래 비교 회귀: 기준선 vs 회귀(R²)</t>
         </is>
       </c>
       <c r="D57" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E57" s="63" t="n">
-        <v>46317</v>
+        <v>46310</v>
       </c>
       <c r="F57" s="63" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="G57" s="64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H57" s="65" t="n">
         <v>0</v>
@@ -5346,13 +5346,13 @@
       <c r="S57" s="72" t="n"/>
       <c r="T57" s="72" t="n"/>
       <c r="U57" s="72" t="n"/>
-      <c r="V57" s="72" t="n"/>
-      <c r="W57" s="72" t="n"/>
-      <c r="X57" s="72" t="n"/>
-      <c r="Y57" s="72" t="n"/>
-      <c r="Z57" s="72" t="n"/>
-      <c r="AA57" s="91" t="n"/>
-      <c r="AB57" s="91" t="n"/>
+      <c r="V57" s="91" t="n"/>
+      <c r="W57" s="91" t="n"/>
+      <c r="X57" s="91" t="n"/>
+      <c r="Y57" s="91" t="n"/>
+      <c r="Z57" s="91" t="n"/>
+      <c r="AA57" s="72" t="n"/>
+      <c r="AB57" s="72" t="n"/>
       <c r="AC57" s="73" t="n"/>
       <c r="AD57" s="73" t="n"/>
       <c r="AE57" s="73" t="n"/>
@@ -5382,27 +5382,29 @@
     </row>
     <row r="58" ht="17.25" customHeight="1" s="103">
       <c r="A58" s="59" t="n"/>
-      <c r="B58" s="60" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C58" s="61" t="inlineStr">
-        <is>
-          <t>[4주] 모델 저장/로드·API 연계 문서</t>
+      <c r="B58" s="60" t="inlineStr">
+        <is>
+          <t>3.2.4</t>
+        </is>
+      </c>
+      <c r="C58" s="82" t="inlineStr">
+        <is>
+          <t>모델 3종 비교·학습결과서 검토·제출</t>
         </is>
       </c>
       <c r="D58" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E58" s="63" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" s="63" t="n">
         <v>46318</v>
       </c>
       <c r="G58" s="64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" s="65" t="n">
         <v>0</v>
@@ -5424,9 +5426,9 @@
       <c r="W58" s="72" t="n"/>
       <c r="X58" s="72" t="n"/>
       <c r="Y58" s="72" t="n"/>
-      <c r="Z58" s="91" t="n"/>
+      <c r="Z58" s="72" t="n"/>
       <c r="AA58" s="91" t="n"/>
-      <c r="AB58" s="92" t="n"/>
+      <c r="AB58" s="91" t="n"/>
       <c r="AC58" s="73" t="n"/>
       <c r="AD58" s="73" t="n"/>
       <c r="AE58" s="73" t="n"/>
@@ -5455,159 +5457,157 @@
       <c r="BB58" s="75" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1" s="103">
-      <c r="A59" s="47" t="n"/>
-      <c r="B59" s="48" t="n">
+      <c r="A59" s="59" t="n"/>
+      <c r="B59" s="60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C59" s="61" t="inlineStr">
+        <is>
+          <t>[4주] 모델 저장/로드·API 연계 문서</t>
+        </is>
+      </c>
+      <c r="D59" s="96" t="inlineStr">
+        <is>
+          <t>김혜리</t>
+        </is>
+      </c>
+      <c r="E59" s="63" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F59" s="63" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G59" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="77" t="n"/>
+      <c r="J59" s="79" t="n"/>
+      <c r="K59" s="72" t="n"/>
+      <c r="L59" s="72" t="n"/>
+      <c r="M59" s="72" t="n"/>
+      <c r="N59" s="70" t="n"/>
+      <c r="O59" s="71" t="n"/>
+      <c r="P59" s="71" t="n"/>
+      <c r="Q59" s="71" t="n"/>
+      <c r="R59" s="70" t="n"/>
+      <c r="S59" s="72" t="n"/>
+      <c r="T59" s="72" t="n"/>
+      <c r="U59" s="72" t="n"/>
+      <c r="V59" s="72" t="n"/>
+      <c r="W59" s="72" t="n"/>
+      <c r="X59" s="72" t="n"/>
+      <c r="Y59" s="72" t="n"/>
+      <c r="Z59" s="91" t="n"/>
+      <c r="AA59" s="91" t="n"/>
+      <c r="AB59" s="92" t="n"/>
+      <c r="AC59" s="73" t="n"/>
+      <c r="AD59" s="73" t="n"/>
+      <c r="AE59" s="73" t="n"/>
+      <c r="AF59" s="73" t="n"/>
+      <c r="AG59" s="73" t="n"/>
+      <c r="AH59" s="72" t="n"/>
+      <c r="AI59" s="72" t="n"/>
+      <c r="AJ59" s="72" t="n"/>
+      <c r="AK59" s="72" t="n"/>
+      <c r="AL59" s="72" t="n"/>
+      <c r="AM59" s="72" t="n"/>
+      <c r="AN59" s="72" t="n"/>
+      <c r="AO59" s="72" t="n"/>
+      <c r="AP59" s="72" t="n"/>
+      <c r="AQ59" s="72" t="n"/>
+      <c r="AR59" s="74" t="n"/>
+      <c r="AS59" s="74" t="n"/>
+      <c r="AT59" s="74" t="n"/>
+      <c r="AU59" s="74" t="n"/>
+      <c r="AV59" s="74" t="n"/>
+      <c r="AW59" s="72" t="n"/>
+      <c r="AX59" s="72" t="n"/>
+      <c r="AY59" s="72" t="n"/>
+      <c r="AZ59" s="72" t="n"/>
+      <c r="BA59" s="72" t="n"/>
+      <c r="BB59" s="75" t="n"/>
+    </row>
+    <row r="60" ht="17.25" customHeight="1" s="103">
+      <c r="A60" s="47" t="n"/>
+      <c r="B60" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="C59" s="49" t="inlineStr">
+      <c r="C60" s="49" t="inlineStr">
         <is>
           <t>모델링 및 평가</t>
         </is>
       </c>
-      <c r="D59" s="50" t="n"/>
-      <c r="E59" s="51" t="n">
+      <c r="D60" s="50" t="n"/>
+      <c r="E60" s="51" t="n">
         <v>46310</v>
       </c>
-      <c r="F59" s="51" t="n">
+      <c r="F60" s="51" t="n">
         <v>46339</v>
       </c>
-      <c r="G59" s="52" t="n">
+      <c r="G60" s="52" t="n">
         <v>22</v>
       </c>
-      <c r="H59" s="53" t="n">
+      <c r="H60" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="58" t="n"/>
-      <c r="J59" s="84" t="n"/>
-      <c r="K59" s="111" t="n"/>
-      <c r="L59" s="111" t="n"/>
-      <c r="M59" s="58" t="n"/>
-      <c r="N59" s="57" t="n"/>
-      <c r="O59" s="58" t="n"/>
-      <c r="P59" s="58" t="n"/>
-      <c r="Q59" s="58" t="n"/>
-      <c r="R59" s="57" t="n"/>
-      <c r="S59" s="58" t="n"/>
-      <c r="T59" s="58" t="n"/>
-      <c r="U59" s="58" t="n"/>
-      <c r="V59" s="93" t="n"/>
-      <c r="W59" s="93" t="n"/>
-      <c r="X59" s="93" t="n"/>
-      <c r="Y59" s="93" t="n"/>
-      <c r="Z59" s="93" t="n"/>
-      <c r="AA59" s="93" t="n"/>
-      <c r="AB59" s="93" t="n"/>
-      <c r="AC59" s="93" t="n"/>
-      <c r="AD59" s="93" t="n"/>
-      <c r="AE59" s="93" t="n"/>
-      <c r="AF59" s="93" t="n"/>
-      <c r="AG59" s="93" t="n"/>
-      <c r="AH59" s="93" t="n"/>
-      <c r="AI59" s="93" t="n"/>
-      <c r="AJ59" s="93" t="n"/>
-      <c r="AK59" s="93" t="n"/>
-      <c r="AL59" s="93" t="n"/>
-      <c r="AM59" s="93" t="n"/>
-      <c r="AN59" s="93" t="n"/>
-      <c r="AO59" s="93" t="n"/>
-      <c r="AP59" s="93" t="n"/>
-      <c r="AQ59" s="93" t="n"/>
-      <c r="AR59" s="58" t="n"/>
-      <c r="AS59" s="58" t="n"/>
-      <c r="AT59" s="58" t="n"/>
-      <c r="AU59" s="58" t="n"/>
-      <c r="AV59" s="58" t="n"/>
-      <c r="AW59" s="58" t="n"/>
-      <c r="AX59" s="58" t="n"/>
-      <c r="AY59" s="58" t="n"/>
-      <c r="AZ59" s="58" t="n"/>
-      <c r="BA59" s="58" t="n"/>
-      <c r="BB59" s="29" t="n"/>
-    </row>
-    <row r="60" ht="17.25" customHeight="1" s="103">
-      <c r="A60" s="59" t="n"/>
-      <c r="B60" s="60" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C60" s="61" t="inlineStr">
-        <is>
-          <t>[4주] 벡터DB/GraphDB 구축 결과서</t>
-        </is>
-      </c>
-      <c r="D60" s="96" t="inlineStr">
-        <is>
-          <t>권세진</t>
-        </is>
-      </c>
-      <c r="E60" s="63" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F60" s="63" t="n">
-        <v>46318</v>
-      </c>
-      <c r="G60" s="64" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="77" t="n"/>
-      <c r="J60" s="79" t="n"/>
-      <c r="K60" s="72" t="n"/>
-      <c r="L60" s="72" t="n"/>
-      <c r="M60" s="72" t="n"/>
-      <c r="N60" s="70" t="n"/>
-      <c r="O60" s="71" t="n"/>
-      <c r="P60" s="71" t="n"/>
-      <c r="Q60" s="71" t="n"/>
-      <c r="R60" s="70" t="n"/>
-      <c r="S60" s="72" t="n"/>
-      <c r="T60" s="72" t="n"/>
-      <c r="U60" s="72" t="n"/>
-      <c r="V60" s="94" t="n"/>
-      <c r="W60" s="94" t="n"/>
-      <c r="X60" s="94" t="n"/>
-      <c r="Y60" s="94" t="n"/>
-      <c r="Z60" s="94" t="n"/>
-      <c r="AA60" s="94" t="n"/>
-      <c r="AB60" s="95" t="n"/>
-      <c r="AC60" s="73" t="n"/>
-      <c r="AD60" s="73" t="n"/>
-      <c r="AE60" s="73" t="n"/>
-      <c r="AF60" s="73" t="n"/>
-      <c r="AG60" s="73" t="n"/>
-      <c r="AH60" s="72" t="n"/>
-      <c r="AI60" s="72" t="n"/>
-      <c r="AJ60" s="72" t="n"/>
-      <c r="AK60" s="72" t="n"/>
-      <c r="AL60" s="72" t="n"/>
-      <c r="AM60" s="72" t="n"/>
-      <c r="AN60" s="72" t="n"/>
-      <c r="AO60" s="72" t="n"/>
-      <c r="AP60" s="72" t="n"/>
-      <c r="AQ60" s="72" t="n"/>
-      <c r="AR60" s="74" t="n"/>
-      <c r="AS60" s="74" t="n"/>
-      <c r="AT60" s="74" t="n"/>
-      <c r="AU60" s="74" t="n"/>
-      <c r="AV60" s="74" t="n"/>
-      <c r="AW60" s="72" t="n"/>
-      <c r="AX60" s="72" t="n"/>
-      <c r="AY60" s="72" t="n"/>
-      <c r="AZ60" s="72" t="n"/>
-      <c r="BA60" s="72" t="n"/>
-      <c r="BB60" s="75" t="n"/>
+      <c r="I60" s="58" t="n"/>
+      <c r="J60" s="84" t="n"/>
+      <c r="K60" s="111" t="n"/>
+      <c r="L60" s="111" t="n"/>
+      <c r="M60" s="58" t="n"/>
+      <c r="N60" s="57" t="n"/>
+      <c r="O60" s="58" t="n"/>
+      <c r="P60" s="58" t="n"/>
+      <c r="Q60" s="58" t="n"/>
+      <c r="R60" s="57" t="n"/>
+      <c r="S60" s="58" t="n"/>
+      <c r="T60" s="58" t="n"/>
+      <c r="U60" s="58" t="n"/>
+      <c r="V60" s="93" t="n"/>
+      <c r="W60" s="93" t="n"/>
+      <c r="X60" s="93" t="n"/>
+      <c r="Y60" s="93" t="n"/>
+      <c r="Z60" s="93" t="n"/>
+      <c r="AA60" s="93" t="n"/>
+      <c r="AB60" s="93" t="n"/>
+      <c r="AC60" s="93" t="n"/>
+      <c r="AD60" s="93" t="n"/>
+      <c r="AE60" s="93" t="n"/>
+      <c r="AF60" s="93" t="n"/>
+      <c r="AG60" s="93" t="n"/>
+      <c r="AH60" s="93" t="n"/>
+      <c r="AI60" s="93" t="n"/>
+      <c r="AJ60" s="93" t="n"/>
+      <c r="AK60" s="93" t="n"/>
+      <c r="AL60" s="93" t="n"/>
+      <c r="AM60" s="93" t="n"/>
+      <c r="AN60" s="93" t="n"/>
+      <c r="AO60" s="93" t="n"/>
+      <c r="AP60" s="93" t="n"/>
+      <c r="AQ60" s="93" t="n"/>
+      <c r="AR60" s="58" t="n"/>
+      <c r="AS60" s="58" t="n"/>
+      <c r="AT60" s="58" t="n"/>
+      <c r="AU60" s="58" t="n"/>
+      <c r="AV60" s="58" t="n"/>
+      <c r="AW60" s="58" t="n"/>
+      <c r="AX60" s="58" t="n"/>
+      <c r="AY60" s="58" t="n"/>
+      <c r="AZ60" s="58" t="n"/>
+      <c r="BA60" s="58" t="n"/>
+      <c r="BB60" s="29" t="n"/>
     </row>
     <row r="61" ht="17.25" customHeight="1" s="103">
       <c r="A61" s="59" t="n"/>
-      <c r="B61" s="60" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="C61" s="82" t="inlineStr">
-        <is>
-          <t>금융 용어·가이드 지식원·임베딩 기준 선정</t>
+      <c r="B61" s="60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C61" s="61" t="inlineStr">
+        <is>
+          <t>[4주] 벡터DB/GraphDB 구축 결과서</t>
         </is>
       </c>
       <c r="D61" s="96" t="inlineStr">
@@ -5619,10 +5619,10 @@
         <v>46310</v>
       </c>
       <c r="F61" s="63" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="G61" s="64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H61" s="65" t="n">
         <v>0</v>
@@ -5643,10 +5643,10 @@
       <c r="V61" s="94" t="n"/>
       <c r="W61" s="94" t="n"/>
       <c r="X61" s="94" t="n"/>
-      <c r="Y61" s="72" t="n"/>
-      <c r="Z61" s="72" t="n"/>
-      <c r="AA61" s="72" t="n"/>
-      <c r="AB61" s="72" t="n"/>
+      <c r="Y61" s="94" t="n"/>
+      <c r="Z61" s="94" t="n"/>
+      <c r="AA61" s="94" t="n"/>
+      <c r="AB61" s="95" t="n"/>
       <c r="AC61" s="73" t="n"/>
       <c r="AD61" s="73" t="n"/>
       <c r="AE61" s="73" t="n"/>
@@ -5678,12 +5678,12 @@
       <c r="A62" s="59" t="n"/>
       <c r="B62" s="60" t="inlineStr">
         <is>
-          <t>4.1.2</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="C62" s="82" t="inlineStr">
         <is>
-          <t>벡터DB 구축·검색 품질·지연 검증</t>
+          <t>금융 용어·가이드 지식원·임베딩 기준 선정</t>
         </is>
       </c>
       <c r="D62" s="96" t="inlineStr">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="E62" s="63" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F62" s="63" t="n">
         <v>46314</v>
       </c>
-      <c r="F62" s="63" t="n">
-        <v>46317</v>
-      </c>
       <c r="G62" s="64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" s="65" t="n">
         <v>0</v>
@@ -5716,12 +5716,12 @@
       <c r="S62" s="72" t="n"/>
       <c r="T62" s="72" t="n"/>
       <c r="U62" s="72" t="n"/>
-      <c r="V62" s="72" t="n"/>
-      <c r="W62" s="72" t="n"/>
+      <c r="V62" s="94" t="n"/>
+      <c r="W62" s="94" t="n"/>
       <c r="X62" s="94" t="n"/>
-      <c r="Y62" s="94" t="n"/>
-      <c r="Z62" s="94" t="n"/>
-      <c r="AA62" s="94" t="n"/>
+      <c r="Y62" s="72" t="n"/>
+      <c r="Z62" s="72" t="n"/>
+      <c r="AA62" s="72" t="n"/>
       <c r="AB62" s="72" t="n"/>
       <c r="AC62" s="73" t="n"/>
       <c r="AD62" s="73" t="n"/>
@@ -5754,27 +5754,27 @@
       <c r="A63" s="59" t="n"/>
       <c r="B63" s="60" t="inlineStr">
         <is>
-          <t>4.1.3</t>
+          <t>4.1.2</t>
         </is>
       </c>
       <c r="C63" s="82" t="inlineStr">
         <is>
-          <t>검색·갱신 결과서 검토·제출</t>
+          <t>벡터DB 구축·검색 품질·지연 검증</t>
         </is>
       </c>
       <c r="D63" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E63" s="63" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F63" s="63" t="n">
         <v>46317</v>
       </c>
-      <c r="F63" s="63" t="n">
-        <v>46318</v>
-      </c>
       <c r="G63" s="64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63" s="65" t="n">
         <v>0</v>
@@ -5794,11 +5794,11 @@
       <c r="U63" s="72" t="n"/>
       <c r="V63" s="72" t="n"/>
       <c r="W63" s="72" t="n"/>
-      <c r="X63" s="72" t="n"/>
-      <c r="Y63" s="72" t="n"/>
-      <c r="Z63" s="72" t="n"/>
+      <c r="X63" s="94" t="n"/>
+      <c r="Y63" s="94" t="n"/>
+      <c r="Z63" s="94" t="n"/>
       <c r="AA63" s="94" t="n"/>
-      <c r="AB63" s="94" t="n"/>
+      <c r="AB63" s="72" t="n"/>
       <c r="AC63" s="73" t="n"/>
       <c r="AD63" s="73" t="n"/>
       <c r="AE63" s="73" t="n"/>
@@ -5828,12 +5828,14 @@
     </row>
     <row r="64" ht="17.25" customHeight="1" s="103">
       <c r="A64" s="59" t="n"/>
-      <c r="B64" s="60" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C64" s="61" t="inlineStr">
-        <is>
-          <t>[5주] AI·멀티에이전트 아키텍처</t>
+      <c r="B64" s="60" t="inlineStr">
+        <is>
+          <t>4.1.3</t>
+        </is>
+      </c>
+      <c r="C64" s="82" t="inlineStr">
+        <is>
+          <t>검색·갱신 결과서 검토·제출</t>
         </is>
       </c>
       <c r="D64" s="96" t="inlineStr">
@@ -5842,13 +5844,13 @@
         </is>
       </c>
       <c r="E64" s="63" t="n">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="F64" s="63" t="n">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="G64" s="64" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H64" s="65" t="n">
         <v>0</v>
@@ -5868,16 +5870,16 @@
       <c r="U64" s="72" t="n"/>
       <c r="V64" s="72" t="n"/>
       <c r="W64" s="72" t="n"/>
-      <c r="X64" s="94" t="n"/>
-      <c r="Y64" s="94" t="n"/>
-      <c r="Z64" s="94" t="n"/>
+      <c r="X64" s="72" t="n"/>
+      <c r="Y64" s="72" t="n"/>
+      <c r="Z64" s="72" t="n"/>
       <c r="AA64" s="94" t="n"/>
       <c r="AB64" s="94" t="n"/>
-      <c r="AC64" s="94" t="n"/>
-      <c r="AD64" s="94" t="n"/>
-      <c r="AE64" s="94" t="n"/>
-      <c r="AF64" s="94" t="n"/>
-      <c r="AG64" s="95" t="n"/>
+      <c r="AC64" s="73" t="n"/>
+      <c r="AD64" s="73" t="n"/>
+      <c r="AE64" s="73" t="n"/>
+      <c r="AF64" s="73" t="n"/>
+      <c r="AG64" s="73" t="n"/>
       <c r="AH64" s="72" t="n"/>
       <c r="AI64" s="72" t="n"/>
       <c r="AJ64" s="72" t="n"/>
@@ -5902,29 +5904,27 @@
     </row>
     <row r="65" ht="17.25" customHeight="1" s="103">
       <c r="A65" s="59" t="n"/>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>4.2.1</t>
-        </is>
-      </c>
-      <c r="C65" s="82" t="inlineStr">
-        <is>
-          <t>라우터 진입점→에이전트·조정 모드 매핑 상세화</t>
+      <c r="B65" s="60" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C65" s="61" t="inlineStr">
+        <is>
+          <t>[5주] AI·멀티에이전트 아키텍처</t>
         </is>
       </c>
       <c r="D65" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E65" s="63" t="n">
         <v>46314</v>
       </c>
       <c r="F65" s="63" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="G65" s="64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H65" s="65" t="n">
         <v>0</v>
@@ -5949,11 +5949,11 @@
       <c r="Z65" s="94" t="n"/>
       <c r="AA65" s="94" t="n"/>
       <c r="AB65" s="94" t="n"/>
-      <c r="AC65" s="73" t="n"/>
-      <c r="AD65" s="73" t="n"/>
-      <c r="AE65" s="73" t="n"/>
-      <c r="AF65" s="73" t="n"/>
-      <c r="AG65" s="73" t="n"/>
+      <c r="AC65" s="94" t="n"/>
+      <c r="AD65" s="94" t="n"/>
+      <c r="AE65" s="94" t="n"/>
+      <c r="AF65" s="94" t="n"/>
+      <c r="AG65" s="95" t="n"/>
       <c r="AH65" s="72" t="n"/>
       <c r="AI65" s="72" t="n"/>
       <c r="AJ65" s="72" t="n"/>
@@ -5980,27 +5980,27 @@
       <c r="A66" s="59" t="n"/>
       <c r="B66" s="60" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="C66" s="82" t="inlineStr">
         <is>
-          <t>엔진 검수·재생성 3회·승인·권한 상세화</t>
+          <t>라우터 진입점→에이전트·조정 모드 매핑 상세화</t>
         </is>
       </c>
       <c r="D66" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E66" s="63" t="n">
-        <v>46317</v>
+        <v>46314</v>
       </c>
       <c r="F66" s="63" t="n">
-        <v>46322</v>
+        <v>46318</v>
       </c>
       <c r="G66" s="64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H66" s="65" t="n">
         <v>0</v>
@@ -6020,13 +6020,13 @@
       <c r="U66" s="72" t="n"/>
       <c r="V66" s="72" t="n"/>
       <c r="W66" s="72" t="n"/>
-      <c r="X66" s="72" t="n"/>
-      <c r="Y66" s="72" t="n"/>
-      <c r="Z66" s="72" t="n"/>
+      <c r="X66" s="94" t="n"/>
+      <c r="Y66" s="94" t="n"/>
+      <c r="Z66" s="94" t="n"/>
       <c r="AA66" s="94" t="n"/>
       <c r="AB66" s="94" t="n"/>
-      <c r="AC66" s="94" t="n"/>
-      <c r="AD66" s="94" t="n"/>
+      <c r="AC66" s="73" t="n"/>
+      <c r="AD66" s="73" t="n"/>
       <c r="AE66" s="73" t="n"/>
       <c r="AF66" s="73" t="n"/>
       <c r="AG66" s="73" t="n"/>
@@ -6056,17 +6056,17 @@
       <c r="A67" s="59" t="n"/>
       <c r="B67" s="60" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="C67" s="82" t="inlineStr">
         <is>
-          <t>(3차) ④ 하위 에이전트·동의 흐름 상세화</t>
+          <t>엔진 검수·재생성 3회·승인·권한 상세화</t>
         </is>
       </c>
       <c r="D67" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E67" s="63" t="n">
@@ -6132,24 +6132,24 @@
       <c r="A68" s="59" t="n"/>
       <c r="B68" s="60" t="inlineStr">
         <is>
-          <t>4.2.4</t>
+          <t>4.2.3</t>
         </is>
       </c>
       <c r="C68" s="82" t="inlineStr">
         <is>
-          <t>아키텍처 공동 검토·버전·제출</t>
+          <t>(3차) ④ 하위 에이전트·동의 흐름 상세화</t>
         </is>
       </c>
       <c r="D68" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E68" s="63" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F68" s="63" t="n">
         <v>46322</v>
-      </c>
-      <c r="F68" s="63" t="n">
-        <v>46325</v>
       </c>
       <c r="G68" s="64" t="n">
         <v>4</v>
@@ -6175,13 +6175,13 @@
       <c r="X68" s="72" t="n"/>
       <c r="Y68" s="72" t="n"/>
       <c r="Z68" s="72" t="n"/>
-      <c r="AA68" s="72" t="n"/>
-      <c r="AB68" s="72" t="n"/>
-      <c r="AC68" s="73" t="n"/>
+      <c r="AA68" s="94" t="n"/>
+      <c r="AB68" s="94" t="n"/>
+      <c r="AC68" s="94" t="n"/>
       <c r="AD68" s="94" t="n"/>
-      <c r="AE68" s="94" t="n"/>
-      <c r="AF68" s="94" t="n"/>
-      <c r="AG68" s="94" t="n"/>
+      <c r="AE68" s="73" t="n"/>
+      <c r="AF68" s="73" t="n"/>
+      <c r="AG68" s="73" t="n"/>
       <c r="AH68" s="72" t="n"/>
       <c r="AI68" s="72" t="n"/>
       <c r="AJ68" s="72" t="n"/>
@@ -6206,12 +6206,14 @@
     </row>
     <row r="69" ht="17.25" customHeight="1" s="103">
       <c r="A69" s="59" t="n"/>
-      <c r="B69" s="60" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="C69" s="61" t="inlineStr">
-        <is>
-          <t>[산출물] LLM 구현(2.2 v1 합의 후)</t>
+      <c r="B69" s="60" t="inlineStr">
+        <is>
+          <t>4.2.4</t>
+        </is>
+      </c>
+      <c r="C69" s="82" t="inlineStr">
+        <is>
+          <t>아키텍처 공동 검토·버전·제출</t>
         </is>
       </c>
       <c r="D69" s="96" t="inlineStr">
@@ -6220,13 +6222,13 @@
         </is>
       </c>
       <c r="E69" s="63" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="F69" s="63" t="n">
-        <v>46339</v>
+        <v>46325</v>
       </c>
       <c r="G69" s="64" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H69" s="65" t="n">
         <v>0</v>
@@ -6248,24 +6250,24 @@
       <c r="W69" s="72" t="n"/>
       <c r="X69" s="72" t="n"/>
       <c r="Y69" s="72" t="n"/>
-      <c r="Z69" s="94" t="n"/>
-      <c r="AA69" s="94" t="n"/>
-      <c r="AB69" s="94" t="n"/>
-      <c r="AC69" s="94" t="n"/>
+      <c r="Z69" s="72" t="n"/>
+      <c r="AA69" s="72" t="n"/>
+      <c r="AB69" s="72" t="n"/>
+      <c r="AC69" s="73" t="n"/>
       <c r="AD69" s="94" t="n"/>
       <c r="AE69" s="94" t="n"/>
       <c r="AF69" s="94" t="n"/>
       <c r="AG69" s="94" t="n"/>
-      <c r="AH69" s="94" t="n"/>
-      <c r="AI69" s="94" t="n"/>
-      <c r="AJ69" s="94" t="n"/>
-      <c r="AK69" s="94" t="n"/>
-      <c r="AL69" s="94" t="n"/>
-      <c r="AM69" s="94" t="n"/>
-      <c r="AN69" s="94" t="n"/>
-      <c r="AO69" s="94" t="n"/>
-      <c r="AP69" s="94" t="n"/>
-      <c r="AQ69" s="95" t="n"/>
+      <c r="AH69" s="72" t="n"/>
+      <c r="AI69" s="72" t="n"/>
+      <c r="AJ69" s="72" t="n"/>
+      <c r="AK69" s="72" t="n"/>
+      <c r="AL69" s="72" t="n"/>
+      <c r="AM69" s="72" t="n"/>
+      <c r="AN69" s="72" t="n"/>
+      <c r="AO69" s="72" t="n"/>
+      <c r="AP69" s="72" t="n"/>
+      <c r="AQ69" s="72" t="n"/>
       <c r="AR69" s="74" t="n"/>
       <c r="AS69" s="74" t="n"/>
       <c r="AT69" s="74" t="n"/>
@@ -6280,29 +6282,27 @@
     </row>
     <row r="70" ht="17.25" customHeight="1" s="103">
       <c r="A70" s="59" t="n"/>
-      <c r="B70" s="60" t="inlineStr">
-        <is>
-          <t>4.3.1</t>
-        </is>
-      </c>
-      <c r="C70" s="82" t="inlineStr">
-        <is>
-          <t>(1차) 라우터·통합 챗봇 선택지·전환</t>
+      <c r="B70" s="60" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C70" s="61" t="inlineStr">
+        <is>
+          <t>[산출물] LLM 구현(2.2 v1 합의 후)</t>
         </is>
       </c>
       <c r="D70" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E70" s="63" t="n">
         <v>46316</v>
       </c>
       <c r="F70" s="63" t="n">
-        <v>46323</v>
+        <v>46339</v>
       </c>
       <c r="G70" s="64" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H70" s="65" t="n">
         <v>0</v>
@@ -6330,18 +6330,18 @@
       <c r="AC70" s="94" t="n"/>
       <c r="AD70" s="94" t="n"/>
       <c r="AE70" s="94" t="n"/>
-      <c r="AF70" s="73" t="n"/>
-      <c r="AG70" s="73" t="n"/>
-      <c r="AH70" s="72" t="n"/>
-      <c r="AI70" s="72" t="n"/>
-      <c r="AJ70" s="72" t="n"/>
-      <c r="AK70" s="72" t="n"/>
-      <c r="AL70" s="72" t="n"/>
-      <c r="AM70" s="72" t="n"/>
-      <c r="AN70" s="72" t="n"/>
-      <c r="AO70" s="72" t="n"/>
-      <c r="AP70" s="72" t="n"/>
-      <c r="AQ70" s="72" t="n"/>
+      <c r="AF70" s="94" t="n"/>
+      <c r="AG70" s="94" t="n"/>
+      <c r="AH70" s="94" t="n"/>
+      <c r="AI70" s="94" t="n"/>
+      <c r="AJ70" s="94" t="n"/>
+      <c r="AK70" s="94" t="n"/>
+      <c r="AL70" s="94" t="n"/>
+      <c r="AM70" s="94" t="n"/>
+      <c r="AN70" s="94" t="n"/>
+      <c r="AO70" s="94" t="n"/>
+      <c r="AP70" s="94" t="n"/>
+      <c r="AQ70" s="95" t="n"/>
       <c r="AR70" s="74" t="n"/>
       <c r="AS70" s="74" t="n"/>
       <c r="AT70" s="74" t="n"/>
@@ -6358,12 +6358,12 @@
       <c r="A71" s="59" t="n"/>
       <c r="B71" s="60" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C71" s="82" t="inlineStr">
         <is>
-          <t>(1차) ① 거래 분류: 검색·지도+LLM·확인</t>
+          <t>(1차) 라우터·통합 챗봇 선택지·전환</t>
         </is>
       </c>
       <c r="D71" s="96" t="inlineStr">
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="E71" s="63" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="F71" s="63" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="G71" s="64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H71" s="65" t="n">
         <v>0</v>
@@ -6400,14 +6400,14 @@
       <c r="W71" s="72" t="n"/>
       <c r="X71" s="72" t="n"/>
       <c r="Y71" s="72" t="n"/>
-      <c r="Z71" s="72" t="n"/>
-      <c r="AA71" s="72" t="n"/>
-      <c r="AB71" s="72" t="n"/>
+      <c r="Z71" s="94" t="n"/>
+      <c r="AA71" s="94" t="n"/>
+      <c r="AB71" s="94" t="n"/>
       <c r="AC71" s="94" t="n"/>
       <c r="AD71" s="94" t="n"/>
       <c r="AE71" s="94" t="n"/>
-      <c r="AF71" s="94" t="n"/>
-      <c r="AG71" s="94" t="n"/>
+      <c r="AF71" s="73" t="n"/>
+      <c r="AG71" s="73" t="n"/>
       <c r="AH71" s="72" t="n"/>
       <c r="AI71" s="72" t="n"/>
       <c r="AJ71" s="72" t="n"/>
@@ -6434,27 +6434,27 @@
       <c r="A72" s="59" t="n"/>
       <c r="B72" s="60" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C72" s="82" t="inlineStr">
         <is>
-          <t>(1차) ② 예산 설계: 비율→ML→LLM→엔진</t>
+          <t>(1차) ① 거래 분류: 검색·지도+LLM·확인</t>
         </is>
       </c>
       <c r="D72" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E72" s="63" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="F72" s="63" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="G72" s="64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H72" s="65" t="n">
         <v>0</v>
@@ -6476,14 +6476,14 @@
       <c r="W72" s="72" t="n"/>
       <c r="X72" s="72" t="n"/>
       <c r="Y72" s="72" t="n"/>
-      <c r="Z72" s="94" t="n"/>
-      <c r="AA72" s="94" t="n"/>
-      <c r="AB72" s="94" t="n"/>
+      <c r="Z72" s="72" t="n"/>
+      <c r="AA72" s="72" t="n"/>
+      <c r="AB72" s="72" t="n"/>
       <c r="AC72" s="94" t="n"/>
       <c r="AD72" s="94" t="n"/>
       <c r="AE72" s="94" t="n"/>
-      <c r="AF72" s="73" t="n"/>
-      <c r="AG72" s="73" t="n"/>
+      <c r="AF72" s="94" t="n"/>
+      <c r="AG72" s="94" t="n"/>
       <c r="AH72" s="72" t="n"/>
       <c r="AI72" s="72" t="n"/>
       <c r="AJ72" s="72" t="n"/>
@@ -6510,12 +6510,12 @@
       <c r="A73" s="59" t="n"/>
       <c r="B73" s="60" t="inlineStr">
         <is>
-          <t>4.3.4</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C73" s="82" t="inlineStr">
         <is>
-          <t>(1차) ③ 예산 조정: 모드 4개·7항목·재생성</t>
+          <t>(1차) ② 예산 설계: 비율→ML→LLM→엔진</t>
         </is>
       </c>
       <c r="D73" s="96" t="inlineStr">
@@ -6524,13 +6524,13 @@
         </is>
       </c>
       <c r="E73" s="63" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="F73" s="63" t="n">
-        <v>46329</v>
+        <v>46323</v>
       </c>
       <c r="G73" s="64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H73" s="65" t="n">
         <v>0</v>
@@ -6552,16 +6552,16 @@
       <c r="W73" s="72" t="n"/>
       <c r="X73" s="72" t="n"/>
       <c r="Y73" s="72" t="n"/>
-      <c r="Z73" s="72" t="n"/>
-      <c r="AA73" s="72" t="n"/>
-      <c r="AB73" s="72" t="n"/>
+      <c r="Z73" s="94" t="n"/>
+      <c r="AA73" s="94" t="n"/>
+      <c r="AB73" s="94" t="n"/>
       <c r="AC73" s="94" t="n"/>
       <c r="AD73" s="94" t="n"/>
       <c r="AE73" s="94" t="n"/>
-      <c r="AF73" s="94" t="n"/>
-      <c r="AG73" s="94" t="n"/>
-      <c r="AH73" s="94" t="n"/>
-      <c r="AI73" s="94" t="n"/>
+      <c r="AF73" s="73" t="n"/>
+      <c r="AG73" s="73" t="n"/>
+      <c r="AH73" s="72" t="n"/>
+      <c r="AI73" s="72" t="n"/>
       <c r="AJ73" s="72" t="n"/>
       <c r="AK73" s="72" t="n"/>
       <c r="AL73" s="72" t="n"/>
@@ -6586,27 +6586,27 @@
       <c r="A74" s="59" t="n"/>
       <c r="B74" s="60" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>4.3.4</t>
         </is>
       </c>
       <c r="C74" s="82" t="inlineStr">
         <is>
-          <t>(3차) ④ 큰 지출 상담: 자금 계산·동의·통합</t>
+          <t>(1차) ③ 예산 조정: 초안·평소 모드·7항목·재생성</t>
         </is>
       </c>
       <c r="D74" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E74" s="63" t="n">
-        <v>46330</v>
+        <v>46321</v>
       </c>
       <c r="F74" s="63" t="n">
-        <v>46336</v>
+        <v>46329</v>
       </c>
       <c r="G74" s="64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H74" s="65" t="n">
         <v>0</v>
@@ -6631,18 +6631,18 @@
       <c r="Z74" s="72" t="n"/>
       <c r="AA74" s="72" t="n"/>
       <c r="AB74" s="72" t="n"/>
-      <c r="AC74" s="73" t="n"/>
-      <c r="AD74" s="73" t="n"/>
-      <c r="AE74" s="73" t="n"/>
-      <c r="AF74" s="73" t="n"/>
-      <c r="AG74" s="73" t="n"/>
-      <c r="AH74" s="72" t="n"/>
-      <c r="AI74" s="72" t="n"/>
-      <c r="AJ74" s="94" t="n"/>
-      <c r="AK74" s="94" t="n"/>
-      <c r="AL74" s="94" t="n"/>
-      <c r="AM74" s="94" t="n"/>
-      <c r="AN74" s="94" t="n"/>
+      <c r="AC74" s="94" t="n"/>
+      <c r="AD74" s="94" t="n"/>
+      <c r="AE74" s="94" t="n"/>
+      <c r="AF74" s="94" t="n"/>
+      <c r="AG74" s="94" t="n"/>
+      <c r="AH74" s="94" t="n"/>
+      <c r="AI74" s="94" t="n"/>
+      <c r="AJ74" s="72" t="n"/>
+      <c r="AK74" s="72" t="n"/>
+      <c r="AL74" s="72" t="n"/>
+      <c r="AM74" s="72" t="n"/>
+      <c r="AN74" s="72" t="n"/>
       <c r="AO74" s="72" t="n"/>
       <c r="AP74" s="72" t="n"/>
       <c r="AQ74" s="72" t="n"/>
@@ -6662,27 +6662,27 @@
       <c r="A75" s="59" t="n"/>
       <c r="B75" s="60" t="inlineStr">
         <is>
-          <t>4.3.6</t>
+          <t>4.3.5</t>
         </is>
       </c>
       <c r="C75" s="82" t="inlineStr">
         <is>
-          <t>(3차) ④-1 복지 검색·④-2 대출 비교</t>
+          <t>(2차) ③ 예산 조정: 돌발·초과 감지·모드 2개</t>
         </is>
       </c>
       <c r="D75" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E75" s="63" t="n">
+        <v>46330</v>
+      </c>
+      <c r="F75" s="63" t="n">
         <v>46332</v>
       </c>
-      <c r="F75" s="63" t="n">
-        <v>46339</v>
-      </c>
       <c r="G75" s="64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H75" s="65" t="n">
         <v>0</v>
@@ -6714,14 +6714,14 @@
       <c r="AG75" s="73" t="n"/>
       <c r="AH75" s="72" t="n"/>
       <c r="AI75" s="72" t="n"/>
-      <c r="AJ75" s="72" t="n"/>
-      <c r="AK75" s="72" t="n"/>
+      <c r="AJ75" s="94" t="n"/>
+      <c r="AK75" s="94" t="n"/>
       <c r="AL75" s="94" t="n"/>
-      <c r="AM75" s="94" t="n"/>
-      <c r="AN75" s="94" t="n"/>
-      <c r="AO75" s="94" t="n"/>
-      <c r="AP75" s="94" t="n"/>
-      <c r="AQ75" s="94" t="n"/>
+      <c r="AM75" s="72" t="n"/>
+      <c r="AN75" s="72" t="n"/>
+      <c r="AO75" s="72" t="n"/>
+      <c r="AP75" s="72" t="n"/>
+      <c r="AQ75" s="72" t="n"/>
       <c r="AR75" s="74" t="n"/>
       <c r="AS75" s="74" t="n"/>
       <c r="AT75" s="74" t="n"/>
@@ -6736,24 +6736,26 @@
     </row>
     <row r="76" ht="17.25" customHeight="1" s="103">
       <c r="A76" s="59" t="n"/>
-      <c r="B76" s="60" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C76" s="61" t="inlineStr">
-        <is>
-          <t>[5주] sLLM 비적용·계산 엔진 검수 검증</t>
+      <c r="B76" s="60" t="inlineStr">
+        <is>
+          <t>4.3.6</t>
+        </is>
+      </c>
+      <c r="C76" s="82" t="inlineStr">
+        <is>
+          <t>(3차) ④ 큰 지출 상담: 자금 계산·동의·통합</t>
         </is>
       </c>
       <c r="D76" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E76" s="63" t="n">
-        <v>46321</v>
+        <v>46330</v>
       </c>
       <c r="F76" s="63" t="n">
-        <v>46325</v>
+        <v>46336</v>
       </c>
       <c r="G76" s="64" t="n">
         <v>5</v>
@@ -6781,18 +6783,18 @@
       <c r="Z76" s="72" t="n"/>
       <c r="AA76" s="72" t="n"/>
       <c r="AB76" s="72" t="n"/>
-      <c r="AC76" s="94" t="n"/>
-      <c r="AD76" s="94" t="n"/>
-      <c r="AE76" s="94" t="n"/>
-      <c r="AF76" s="94" t="n"/>
-      <c r="AG76" s="95" t="n"/>
+      <c r="AC76" s="73" t="n"/>
+      <c r="AD76" s="73" t="n"/>
+      <c r="AE76" s="73" t="n"/>
+      <c r="AF76" s="73" t="n"/>
+      <c r="AG76" s="73" t="n"/>
       <c r="AH76" s="72" t="n"/>
       <c r="AI76" s="72" t="n"/>
-      <c r="AJ76" s="72" t="n"/>
-      <c r="AK76" s="72" t="n"/>
-      <c r="AL76" s="72" t="n"/>
-      <c r="AM76" s="72" t="n"/>
-      <c r="AN76" s="72" t="n"/>
+      <c r="AJ76" s="94" t="n"/>
+      <c r="AK76" s="94" t="n"/>
+      <c r="AL76" s="94" t="n"/>
+      <c r="AM76" s="94" t="n"/>
+      <c r="AN76" s="94" t="n"/>
       <c r="AO76" s="72" t="n"/>
       <c r="AP76" s="72" t="n"/>
       <c r="AQ76" s="72" t="n"/>
@@ -6810,27 +6812,29 @@
     </row>
     <row r="77" ht="17.25" customHeight="1" s="103">
       <c r="A77" s="59" t="n"/>
-      <c r="B77" s="60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C77" s="61" t="inlineStr">
-        <is>
-          <t>[6주] 멀티에이전트 테스트 계획·결과</t>
+      <c r="B77" s="60" t="inlineStr">
+        <is>
+          <t>4.3.7</t>
+        </is>
+      </c>
+      <c r="C77" s="82" t="inlineStr">
+        <is>
+          <t>(3차) ④-1 복지 검색·④-2 대출 비교</t>
         </is>
       </c>
       <c r="D77" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E77" s="63" t="n">
-        <v>46321</v>
+        <v>46332</v>
       </c>
       <c r="F77" s="63" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="G77" s="64" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H77" s="65" t="n">
         <v>0</v>
@@ -6855,21 +6859,21 @@
       <c r="Z77" s="72" t="n"/>
       <c r="AA77" s="72" t="n"/>
       <c r="AB77" s="72" t="n"/>
-      <c r="AC77" s="94" t="n"/>
-      <c r="AD77" s="94" t="n"/>
-      <c r="AE77" s="94" t="n"/>
-      <c r="AF77" s="94" t="n"/>
-      <c r="AG77" s="94" t="n"/>
-      <c r="AH77" s="94" t="n"/>
-      <c r="AI77" s="94" t="n"/>
-      <c r="AJ77" s="94" t="n"/>
-      <c r="AK77" s="94" t="n"/>
-      <c r="AL77" s="95" t="n"/>
-      <c r="AM77" s="72" t="n"/>
-      <c r="AN77" s="72" t="n"/>
-      <c r="AO77" s="72" t="n"/>
-      <c r="AP77" s="72" t="n"/>
-      <c r="AQ77" s="72" t="n"/>
+      <c r="AC77" s="73" t="n"/>
+      <c r="AD77" s="73" t="n"/>
+      <c r="AE77" s="73" t="n"/>
+      <c r="AF77" s="73" t="n"/>
+      <c r="AG77" s="73" t="n"/>
+      <c r="AH77" s="72" t="n"/>
+      <c r="AI77" s="72" t="n"/>
+      <c r="AJ77" s="72" t="n"/>
+      <c r="AK77" s="72" t="n"/>
+      <c r="AL77" s="94" t="n"/>
+      <c r="AM77" s="94" t="n"/>
+      <c r="AN77" s="94" t="n"/>
+      <c r="AO77" s="94" t="n"/>
+      <c r="AP77" s="94" t="n"/>
+      <c r="AQ77" s="94" t="n"/>
       <c r="AR77" s="74" t="n"/>
       <c r="AS77" s="74" t="n"/>
       <c r="AT77" s="74" t="n"/>
@@ -6884,29 +6888,27 @@
     </row>
     <row r="78" ht="17.25" customHeight="1" s="103">
       <c r="A78" s="59" t="n"/>
-      <c r="B78" s="60" t="inlineStr">
-        <is>
-          <t>4.5.1</t>
-        </is>
-      </c>
-      <c r="C78" s="82" t="inlineStr">
-        <is>
-          <t>단일 LLM 비교 시나리오·라우팅 테스트 계획</t>
+      <c r="B78" s="60" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C78" s="61" t="inlineStr">
+        <is>
+          <t>[5주] sLLM 비적용·계산 엔진 검수 검증</t>
         </is>
       </c>
       <c r="D78" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E78" s="63" t="n">
         <v>46321</v>
       </c>
       <c r="F78" s="63" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="G78" s="64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H78" s="65" t="n">
         <v>0</v>
@@ -6935,7 +6937,7 @@
       <c r="AD78" s="94" t="n"/>
       <c r="AE78" s="94" t="n"/>
       <c r="AF78" s="94" t="n"/>
-      <c r="AG78" s="73" t="n"/>
+      <c r="AG78" s="95" t="n"/>
       <c r="AH78" s="72" t="n"/>
       <c r="AI78" s="72" t="n"/>
       <c r="AJ78" s="72" t="n"/>
@@ -6960,14 +6962,12 @@
     </row>
     <row r="79" ht="17.25" customHeight="1" s="103">
       <c r="A79" s="59" t="n"/>
-      <c r="B79" s="60" t="inlineStr">
-        <is>
-          <t>4.5.2</t>
-        </is>
-      </c>
-      <c r="C79" s="82" t="inlineStr">
-        <is>
-          <t>1차 에이전트 모드별 검수·재생성·승인 회귀</t>
+      <c r="B79" s="60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C79" s="61" t="inlineStr">
+        <is>
+          <t>[6주] 멀티에이전트 테스트 계획·결과</t>
         </is>
       </c>
       <c r="D79" s="96" t="inlineStr">
@@ -6976,13 +6976,13 @@
         </is>
       </c>
       <c r="E79" s="63" t="n">
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="F79" s="63" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="G79" s="64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H79" s="65" t="n">
         <v>0</v>
@@ -7007,16 +7007,16 @@
       <c r="Z79" s="72" t="n"/>
       <c r="AA79" s="72" t="n"/>
       <c r="AB79" s="72" t="n"/>
-      <c r="AC79" s="73" t="n"/>
-      <c r="AD79" s="73" t="n"/>
-      <c r="AE79" s="73" t="n"/>
-      <c r="AF79" s="73" t="n"/>
-      <c r="AG79" s="73" t="n"/>
+      <c r="AC79" s="94" t="n"/>
+      <c r="AD79" s="94" t="n"/>
+      <c r="AE79" s="94" t="n"/>
+      <c r="AF79" s="94" t="n"/>
+      <c r="AG79" s="94" t="n"/>
       <c r="AH79" s="94" t="n"/>
       <c r="AI79" s="94" t="n"/>
       <c r="AJ79" s="94" t="n"/>
       <c r="AK79" s="94" t="n"/>
-      <c r="AL79" s="72" t="n"/>
+      <c r="AL79" s="95" t="n"/>
       <c r="AM79" s="72" t="n"/>
       <c r="AN79" s="72" t="n"/>
       <c r="AO79" s="72" t="n"/>
@@ -7038,27 +7038,27 @@
       <c r="A80" s="59" t="n"/>
       <c r="B80" s="60" t="inlineStr">
         <is>
-          <t>4.5.3</t>
+          <t>4.5.1</t>
         </is>
       </c>
       <c r="C80" s="82" t="inlineStr">
         <is>
-          <t>에이전트 테스트 결과 검토·제출</t>
+          <t>단일 LLM 비교 시나리오·라우팅 테스트 계획</t>
         </is>
       </c>
       <c r="D80" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E80" s="63" t="n">
-        <v>46331</v>
+        <v>46321</v>
       </c>
       <c r="F80" s="63" t="n">
-        <v>46332</v>
+        <v>46324</v>
       </c>
       <c r="G80" s="64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H80" s="65" t="n">
         <v>0</v>
@@ -7083,16 +7083,16 @@
       <c r="Z80" s="72" t="n"/>
       <c r="AA80" s="72" t="n"/>
       <c r="AB80" s="72" t="n"/>
-      <c r="AC80" s="73" t="n"/>
-      <c r="AD80" s="73" t="n"/>
-      <c r="AE80" s="73" t="n"/>
-      <c r="AF80" s="73" t="n"/>
+      <c r="AC80" s="94" t="n"/>
+      <c r="AD80" s="94" t="n"/>
+      <c r="AE80" s="94" t="n"/>
+      <c r="AF80" s="94" t="n"/>
       <c r="AG80" s="73" t="n"/>
       <c r="AH80" s="72" t="n"/>
       <c r="AI80" s="72" t="n"/>
       <c r="AJ80" s="72" t="n"/>
-      <c r="AK80" s="94" t="n"/>
-      <c r="AL80" s="94" t="n"/>
+      <c r="AK80" s="72" t="n"/>
+      <c r="AL80" s="72" t="n"/>
       <c r="AM80" s="72" t="n"/>
       <c r="AN80" s="72" t="n"/>
       <c r="AO80" s="72" t="n"/>
@@ -7111,83 +7111,91 @@
       <c r="BB80" s="75" t="n"/>
     </row>
     <row r="81" ht="21" customHeight="1" s="103">
-      <c r="A81" s="47" t="n"/>
-      <c r="B81" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="49" t="inlineStr">
-        <is>
-          <t>모델 배포</t>
-        </is>
-      </c>
-      <c r="D81" s="50" t="n"/>
-      <c r="E81" s="51" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F81" s="51" t="n">
-        <v>46346</v>
-      </c>
-      <c r="G81" s="52" t="n">
-        <v>36</v>
-      </c>
-      <c r="H81" s="53" t="n">
+      <c r="A81" s="59" t="n"/>
+      <c r="B81" s="60" t="inlineStr">
+        <is>
+          <t>4.5.2</t>
+        </is>
+      </c>
+      <c r="C81" s="82" t="inlineStr">
+        <is>
+          <t>1차 에이전트 모드별 검수·재생성·승인 회귀</t>
+        </is>
+      </c>
+      <c r="D81" s="96" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+      <c r="E81" s="63" t="n">
+        <v>46328</v>
+      </c>
+      <c r="F81" s="63" t="n">
+        <v>46331</v>
+      </c>
+      <c r="G81" s="64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="58" t="n"/>
-      <c r="J81" s="84" t="n"/>
-      <c r="K81" s="113" t="n"/>
-      <c r="L81" s="113" t="n"/>
-      <c r="M81" s="97" t="n"/>
-      <c r="N81" s="97" t="n"/>
-      <c r="O81" s="97" t="n"/>
-      <c r="P81" s="97" t="n"/>
-      <c r="Q81" s="97" t="n"/>
-      <c r="R81" s="97" t="n"/>
-      <c r="S81" s="97" t="n"/>
-      <c r="T81" s="97" t="n"/>
-      <c r="U81" s="97" t="n"/>
-      <c r="V81" s="97" t="n"/>
-      <c r="W81" s="97" t="n"/>
-      <c r="X81" s="97" t="n"/>
-      <c r="Y81" s="97" t="n"/>
-      <c r="Z81" s="97" t="n"/>
-      <c r="AA81" s="97" t="n"/>
-      <c r="AB81" s="97" t="n"/>
-      <c r="AC81" s="97" t="n"/>
-      <c r="AD81" s="97" t="n"/>
-      <c r="AE81" s="97" t="n"/>
-      <c r="AF81" s="97" t="n"/>
-      <c r="AG81" s="97" t="n"/>
-      <c r="AH81" s="97" t="n"/>
-      <c r="AI81" s="97" t="n"/>
-      <c r="AJ81" s="97" t="n"/>
-      <c r="AK81" s="97" t="n"/>
-      <c r="AL81" s="97" t="n"/>
-      <c r="AM81" s="97" t="n"/>
-      <c r="AN81" s="97" t="n"/>
-      <c r="AO81" s="97" t="n"/>
-      <c r="AP81" s="97" t="n"/>
-      <c r="AQ81" s="97" t="n"/>
-      <c r="AR81" s="97" t="n"/>
-      <c r="AS81" s="97" t="n"/>
-      <c r="AT81" s="97" t="n"/>
-      <c r="AU81" s="97" t="n"/>
-      <c r="AV81" s="97" t="n"/>
-      <c r="AW81" s="58" t="n"/>
-      <c r="AX81" s="58" t="n"/>
-      <c r="AY81" s="58" t="n"/>
-      <c r="AZ81" s="58" t="n"/>
-      <c r="BA81" s="58" t="n"/>
-      <c r="BB81" s="29" t="n"/>
+      <c r="I81" s="77" t="n"/>
+      <c r="J81" s="79" t="n"/>
+      <c r="K81" s="72" t="n"/>
+      <c r="L81" s="72" t="n"/>
+      <c r="M81" s="72" t="n"/>
+      <c r="N81" s="70" t="n"/>
+      <c r="O81" s="71" t="n"/>
+      <c r="P81" s="71" t="n"/>
+      <c r="Q81" s="71" t="n"/>
+      <c r="R81" s="70" t="n"/>
+      <c r="S81" s="72" t="n"/>
+      <c r="T81" s="72" t="n"/>
+      <c r="U81" s="72" t="n"/>
+      <c r="V81" s="72" t="n"/>
+      <c r="W81" s="72" t="n"/>
+      <c r="X81" s="72" t="n"/>
+      <c r="Y81" s="72" t="n"/>
+      <c r="Z81" s="72" t="n"/>
+      <c r="AA81" s="72" t="n"/>
+      <c r="AB81" s="72" t="n"/>
+      <c r="AC81" s="73" t="n"/>
+      <c r="AD81" s="73" t="n"/>
+      <c r="AE81" s="73" t="n"/>
+      <c r="AF81" s="73" t="n"/>
+      <c r="AG81" s="73" t="n"/>
+      <c r="AH81" s="94" t="n"/>
+      <c r="AI81" s="94" t="n"/>
+      <c r="AJ81" s="94" t="n"/>
+      <c r="AK81" s="94" t="n"/>
+      <c r="AL81" s="72" t="n"/>
+      <c r="AM81" s="72" t="n"/>
+      <c r="AN81" s="72" t="n"/>
+      <c r="AO81" s="72" t="n"/>
+      <c r="AP81" s="72" t="n"/>
+      <c r="AQ81" s="72" t="n"/>
+      <c r="AR81" s="74" t="n"/>
+      <c r="AS81" s="74" t="n"/>
+      <c r="AT81" s="74" t="n"/>
+      <c r="AU81" s="74" t="n"/>
+      <c r="AV81" s="74" t="n"/>
+      <c r="AW81" s="72" t="n"/>
+      <c r="AX81" s="72" t="n"/>
+      <c r="AY81" s="72" t="n"/>
+      <c r="AZ81" s="72" t="n"/>
+      <c r="BA81" s="72" t="n"/>
+      <c r="BB81" s="75" t="n"/>
     </row>
     <row r="82" ht="17.25" customHeight="1" s="103">
       <c r="A82" s="59" t="n"/>
-      <c r="B82" s="60" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C82" s="61" t="inlineStr">
-        <is>
-          <t>[2주] 화면설계서</t>
+      <c r="B82" s="60" t="inlineStr">
+        <is>
+          <t>4.5.3</t>
+        </is>
+      </c>
+      <c r="C82" s="82" t="inlineStr">
+        <is>
+          <t>에이전트 테스트 결과 검토·제출</t>
         </is>
       </c>
       <c r="D82" s="96" t="inlineStr">
@@ -7196,26 +7204,26 @@
         </is>
       </c>
       <c r="E82" s="63" t="n">
-        <v>46295</v>
+        <v>46331</v>
       </c>
       <c r="F82" s="63" t="n">
-        <v>46303</v>
+        <v>46332</v>
       </c>
       <c r="G82" s="64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H82" s="65" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="77" t="n"/>
       <c r="J82" s="79" t="n"/>
-      <c r="K82" s="98" t="n"/>
-      <c r="L82" s="98" t="n"/>
-      <c r="M82" s="98" t="n"/>
-      <c r="N82" s="98" t="n"/>
-      <c r="O82" s="98" t="n"/>
-      <c r="P82" s="98" t="n"/>
-      <c r="Q82" s="99" t="n"/>
+      <c r="K82" s="72" t="n"/>
+      <c r="L82" s="72" t="n"/>
+      <c r="M82" s="72" t="n"/>
+      <c r="N82" s="70" t="n"/>
+      <c r="O82" s="71" t="n"/>
+      <c r="P82" s="71" t="n"/>
+      <c r="Q82" s="71" t="n"/>
       <c r="R82" s="70" t="n"/>
       <c r="S82" s="72" t="n"/>
       <c r="T82" s="72" t="n"/>
@@ -7235,8 +7243,8 @@
       <c r="AH82" s="72" t="n"/>
       <c r="AI82" s="72" t="n"/>
       <c r="AJ82" s="72" t="n"/>
-      <c r="AK82" s="72" t="n"/>
-      <c r="AL82" s="72" t="n"/>
+      <c r="AK82" s="94" t="n"/>
+      <c r="AL82" s="94" t="n"/>
       <c r="AM82" s="72" t="n"/>
       <c r="AN82" s="72" t="n"/>
       <c r="AO82" s="72" t="n"/>
@@ -7255,91 +7263,83 @@
       <c r="BB82" s="75" t="n"/>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="103">
-      <c r="A83" s="59" t="n"/>
-      <c r="B83" s="60" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="C83" s="82" t="inlineStr">
-        <is>
-          <t>모바일 웹: 인증→원장→예산→승인 설계</t>
-        </is>
-      </c>
-      <c r="D83" s="96" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="E83" s="63" t="n">
+      <c r="A83" s="47" t="n"/>
+      <c r="B83" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="49" t="inlineStr">
+        <is>
+          <t>모델 배포</t>
+        </is>
+      </c>
+      <c r="D83" s="50" t="n"/>
+      <c r="E83" s="51" t="n">
         <v>46295</v>
       </c>
-      <c r="F83" s="63" t="n">
-        <v>46297</v>
-      </c>
-      <c r="G83" s="64" t="n">
-        <v>3</v>
-      </c>
-      <c r="H83" s="65" t="n">
+      <c r="F83" s="51" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G83" s="52" t="n">
+        <v>36</v>
+      </c>
+      <c r="H83" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="77" t="n"/>
-      <c r="J83" s="79" t="n"/>
-      <c r="K83" s="98" t="n"/>
-      <c r="L83" s="98" t="n"/>
-      <c r="M83" s="98" t="n"/>
-      <c r="N83" s="70" t="n"/>
-      <c r="O83" s="71" t="n"/>
-      <c r="P83" s="71" t="n"/>
-      <c r="Q83" s="71" t="n"/>
-      <c r="R83" s="70" t="n"/>
-      <c r="S83" s="72" t="n"/>
-      <c r="T83" s="72" t="n"/>
-      <c r="U83" s="72" t="n"/>
-      <c r="V83" s="72" t="n"/>
-      <c r="W83" s="72" t="n"/>
-      <c r="X83" s="72" t="n"/>
-      <c r="Y83" s="72" t="n"/>
-      <c r="Z83" s="72" t="n"/>
-      <c r="AA83" s="72" t="n"/>
-      <c r="AB83" s="72" t="n"/>
-      <c r="AC83" s="73" t="n"/>
-      <c r="AD83" s="73" t="n"/>
-      <c r="AE83" s="73" t="n"/>
-      <c r="AF83" s="73" t="n"/>
-      <c r="AG83" s="73" t="n"/>
-      <c r="AH83" s="72" t="n"/>
-      <c r="AI83" s="72" t="n"/>
-      <c r="AJ83" s="72" t="n"/>
-      <c r="AK83" s="72" t="n"/>
-      <c r="AL83" s="72" t="n"/>
-      <c r="AM83" s="72" t="n"/>
-      <c r="AN83" s="72" t="n"/>
-      <c r="AO83" s="72" t="n"/>
-      <c r="AP83" s="72" t="n"/>
-      <c r="AQ83" s="72" t="n"/>
-      <c r="AR83" s="74" t="n"/>
-      <c r="AS83" s="74" t="n"/>
-      <c r="AT83" s="74" t="n"/>
-      <c r="AU83" s="74" t="n"/>
-      <c r="AV83" s="74" t="n"/>
-      <c r="AW83" s="72" t="n"/>
-      <c r="AX83" s="72" t="n"/>
-      <c r="AY83" s="72" t="n"/>
-      <c r="AZ83" s="72" t="n"/>
-      <c r="BA83" s="72" t="n"/>
-      <c r="BB83" s="75" t="n"/>
+      <c r="I83" s="58" t="n"/>
+      <c r="J83" s="84" t="n"/>
+      <c r="K83" s="113" t="n"/>
+      <c r="L83" s="113" t="n"/>
+      <c r="M83" s="97" t="n"/>
+      <c r="N83" s="97" t="n"/>
+      <c r="O83" s="97" t="n"/>
+      <c r="P83" s="97" t="n"/>
+      <c r="Q83" s="97" t="n"/>
+      <c r="R83" s="97" t="n"/>
+      <c r="S83" s="97" t="n"/>
+      <c r="T83" s="97" t="n"/>
+      <c r="U83" s="97" t="n"/>
+      <c r="V83" s="97" t="n"/>
+      <c r="W83" s="97" t="n"/>
+      <c r="X83" s="97" t="n"/>
+      <c r="Y83" s="97" t="n"/>
+      <c r="Z83" s="97" t="n"/>
+      <c r="AA83" s="97" t="n"/>
+      <c r="AB83" s="97" t="n"/>
+      <c r="AC83" s="97" t="n"/>
+      <c r="AD83" s="97" t="n"/>
+      <c r="AE83" s="97" t="n"/>
+      <c r="AF83" s="97" t="n"/>
+      <c r="AG83" s="97" t="n"/>
+      <c r="AH83" s="97" t="n"/>
+      <c r="AI83" s="97" t="n"/>
+      <c r="AJ83" s="97" t="n"/>
+      <c r="AK83" s="97" t="n"/>
+      <c r="AL83" s="97" t="n"/>
+      <c r="AM83" s="97" t="n"/>
+      <c r="AN83" s="97" t="n"/>
+      <c r="AO83" s="97" t="n"/>
+      <c r="AP83" s="97" t="n"/>
+      <c r="AQ83" s="97" t="n"/>
+      <c r="AR83" s="97" t="n"/>
+      <c r="AS83" s="97" t="n"/>
+      <c r="AT83" s="97" t="n"/>
+      <c r="AU83" s="97" t="n"/>
+      <c r="AV83" s="97" t="n"/>
+      <c r="AW83" s="58" t="n"/>
+      <c r="AX83" s="58" t="n"/>
+      <c r="AY83" s="58" t="n"/>
+      <c r="AZ83" s="58" t="n"/>
+      <c r="BA83" s="58" t="n"/>
+      <c r="BB83" s="29" t="n"/>
     </row>
     <row r="84" ht="17.25" customHeight="1" s="103">
       <c r="A84" s="59" t="n"/>
-      <c r="B84" s="60" t="inlineStr">
-        <is>
-          <t>5.1.2</t>
-        </is>
-      </c>
-      <c r="C84" s="82" t="inlineStr">
-        <is>
-          <t>입출력·이동·예외·오류 화면 설계</t>
+      <c r="B84" s="60" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C84" s="61" t="inlineStr">
+        <is>
+          <t>[2주] 화면설계서</t>
         </is>
       </c>
       <c r="D84" s="96" t="inlineStr">
@@ -7348,26 +7348,26 @@
         </is>
       </c>
       <c r="E84" s="63" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="F84" s="63" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="G84" s="64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H84" s="65" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="77" t="n"/>
       <c r="J84" s="79" t="n"/>
-      <c r="K84" s="72" t="n"/>
-      <c r="L84" s="72" t="n"/>
+      <c r="K84" s="98" t="n"/>
+      <c r="L84" s="98" t="n"/>
       <c r="M84" s="98" t="n"/>
       <c r="N84" s="98" t="n"/>
       <c r="O84" s="98" t="n"/>
       <c r="P84" s="98" t="n"/>
-      <c r="Q84" s="71" t="n"/>
+      <c r="Q84" s="99" t="n"/>
       <c r="R84" s="70" t="n"/>
       <c r="S84" s="72" t="n"/>
       <c r="T84" s="72" t="n"/>
@@ -7410,12 +7410,12 @@
       <c r="A85" s="59" t="n"/>
       <c r="B85" s="60" t="inlineStr">
         <is>
-          <t>5.1.3</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C85" s="82" t="inlineStr">
         <is>
-          <t>화면설계서 작성·팀 검토·제출</t>
+          <t>모바일 웹: 인증→원장→예산→승인 설계</t>
         </is>
       </c>
       <c r="D85" s="96" t="inlineStr">
@@ -7424,26 +7424,26 @@
         </is>
       </c>
       <c r="E85" s="63" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="F85" s="63" t="n">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="G85" s="64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" s="65" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="77" t="n"/>
       <c r="J85" s="79" t="n"/>
-      <c r="K85" s="72" t="n"/>
-      <c r="L85" s="72" t="n"/>
-      <c r="M85" s="72" t="n"/>
+      <c r="K85" s="98" t="n"/>
+      <c r="L85" s="98" t="n"/>
+      <c r="M85" s="98" t="n"/>
       <c r="N85" s="70" t="n"/>
       <c r="O85" s="71" t="n"/>
-      <c r="P85" s="98" t="n"/>
-      <c r="Q85" s="98" t="n"/>
+      <c r="P85" s="71" t="n"/>
+      <c r="Q85" s="71" t="n"/>
       <c r="R85" s="70" t="n"/>
       <c r="S85" s="72" t="n"/>
       <c r="T85" s="72" t="n"/>
@@ -7484,27 +7484,29 @@
     </row>
     <row r="86" ht="17.25" customHeight="1" s="103">
       <c r="A86" s="59" t="n"/>
-      <c r="B86" s="60" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C86" s="61" t="inlineStr">
-        <is>
-          <t>[6주] 시스템 구성도·기술 스택</t>
+      <c r="B86" s="60" t="inlineStr">
+        <is>
+          <t>5.1.2</t>
+        </is>
+      </c>
+      <c r="C86" s="82" t="inlineStr">
+        <is>
+          <t>입출력·이동·예외·오류 화면 설계</t>
         </is>
       </c>
       <c r="D86" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E86" s="63" t="n">
-        <v>46321</v>
+        <v>46297</v>
       </c>
       <c r="F86" s="63" t="n">
-        <v>46332</v>
+        <v>46302</v>
       </c>
       <c r="G86" s="64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H86" s="65" t="n">
         <v>0</v>
@@ -7513,10 +7515,10 @@
       <c r="J86" s="79" t="n"/>
       <c r="K86" s="72" t="n"/>
       <c r="L86" s="72" t="n"/>
-      <c r="M86" s="72" t="n"/>
-      <c r="N86" s="70" t="n"/>
-      <c r="O86" s="71" t="n"/>
-      <c r="P86" s="71" t="n"/>
+      <c r="M86" s="98" t="n"/>
+      <c r="N86" s="98" t="n"/>
+      <c r="O86" s="98" t="n"/>
+      <c r="P86" s="98" t="n"/>
       <c r="Q86" s="71" t="n"/>
       <c r="R86" s="70" t="n"/>
       <c r="S86" s="72" t="n"/>
@@ -7529,16 +7531,16 @@
       <c r="Z86" s="72" t="n"/>
       <c r="AA86" s="72" t="n"/>
       <c r="AB86" s="72" t="n"/>
-      <c r="AC86" s="98" t="n"/>
-      <c r="AD86" s="98" t="n"/>
-      <c r="AE86" s="98" t="n"/>
-      <c r="AF86" s="98" t="n"/>
-      <c r="AG86" s="98" t="n"/>
-      <c r="AH86" s="98" t="n"/>
-      <c r="AI86" s="98" t="n"/>
-      <c r="AJ86" s="98" t="n"/>
-      <c r="AK86" s="98" t="n"/>
-      <c r="AL86" s="99" t="n"/>
+      <c r="AC86" s="73" t="n"/>
+      <c r="AD86" s="73" t="n"/>
+      <c r="AE86" s="73" t="n"/>
+      <c r="AF86" s="73" t="n"/>
+      <c r="AG86" s="73" t="n"/>
+      <c r="AH86" s="72" t="n"/>
+      <c r="AI86" s="72" t="n"/>
+      <c r="AJ86" s="72" t="n"/>
+      <c r="AK86" s="72" t="n"/>
+      <c r="AL86" s="72" t="n"/>
       <c r="AM86" s="72" t="n"/>
       <c r="AN86" s="72" t="n"/>
       <c r="AO86" s="72" t="n"/>
@@ -7558,12 +7560,14 @@
     </row>
     <row r="87" ht="17.25" customHeight="1" s="103">
       <c r="A87" s="59" t="n"/>
-      <c r="B87" s="60" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="C87" s="61" t="inlineStr">
-        <is>
-          <t>[7주] 서비스 테스트 계획·결과서</t>
+      <c r="B87" s="60" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="C87" s="82" t="inlineStr">
+        <is>
+          <t>화면설계서 작성·팀 검토·제출</t>
         </is>
       </c>
       <c r="D87" s="96" t="inlineStr">
@@ -7572,13 +7576,13 @@
         </is>
       </c>
       <c r="E87" s="63" t="n">
-        <v>46330</v>
+        <v>46302</v>
       </c>
       <c r="F87" s="63" t="n">
-        <v>46339</v>
+        <v>46303</v>
       </c>
       <c r="G87" s="64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H87" s="65" t="n">
         <v>0</v>
@@ -7590,8 +7594,8 @@
       <c r="M87" s="72" t="n"/>
       <c r="N87" s="70" t="n"/>
       <c r="O87" s="71" t="n"/>
-      <c r="P87" s="71" t="n"/>
-      <c r="Q87" s="71" t="n"/>
+      <c r="P87" s="98" t="n"/>
+      <c r="Q87" s="98" t="n"/>
       <c r="R87" s="70" t="n"/>
       <c r="S87" s="72" t="n"/>
       <c r="T87" s="72" t="n"/>
@@ -7610,14 +7614,14 @@
       <c r="AG87" s="73" t="n"/>
       <c r="AH87" s="72" t="n"/>
       <c r="AI87" s="72" t="n"/>
-      <c r="AJ87" s="98" t="n"/>
-      <c r="AK87" s="98" t="n"/>
-      <c r="AL87" s="98" t="n"/>
-      <c r="AM87" s="98" t="n"/>
-      <c r="AN87" s="98" t="n"/>
-      <c r="AO87" s="98" t="n"/>
-      <c r="AP87" s="98" t="n"/>
-      <c r="AQ87" s="99" t="n"/>
+      <c r="AJ87" s="72" t="n"/>
+      <c r="AK87" s="72" t="n"/>
+      <c r="AL87" s="72" t="n"/>
+      <c r="AM87" s="72" t="n"/>
+      <c r="AN87" s="72" t="n"/>
+      <c r="AO87" s="72" t="n"/>
+      <c r="AP87" s="72" t="n"/>
+      <c r="AQ87" s="72" t="n"/>
       <c r="AR87" s="74" t="n"/>
       <c r="AS87" s="74" t="n"/>
       <c r="AT87" s="74" t="n"/>
@@ -7632,29 +7636,27 @@
     </row>
     <row r="88" ht="17.25" customHeight="1" s="103">
       <c r="A88" s="59" t="n"/>
-      <c r="B88" s="60" t="inlineStr">
-        <is>
-          <t>5.3.1</t>
-        </is>
-      </c>
-      <c r="C88" s="82" t="inlineStr">
-        <is>
-          <t>10/14 요구사항·경계·보안 시험 설계</t>
+      <c r="B88" s="60" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C88" s="61" t="inlineStr">
+        <is>
+          <t>[6주] 시스템 구성도·기술 스택</t>
         </is>
       </c>
       <c r="D88" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E88" s="63" t="n">
-        <v>46330</v>
+        <v>46321</v>
       </c>
       <c r="F88" s="63" t="n">
         <v>46332</v>
       </c>
       <c r="G88" s="64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H88" s="65" t="n">
         <v>0</v>
@@ -7679,16 +7681,16 @@
       <c r="Z88" s="72" t="n"/>
       <c r="AA88" s="72" t="n"/>
       <c r="AB88" s="72" t="n"/>
-      <c r="AC88" s="73" t="n"/>
-      <c r="AD88" s="73" t="n"/>
-      <c r="AE88" s="73" t="n"/>
-      <c r="AF88" s="73" t="n"/>
-      <c r="AG88" s="73" t="n"/>
-      <c r="AH88" s="72" t="n"/>
-      <c r="AI88" s="72" t="n"/>
+      <c r="AC88" s="98" t="n"/>
+      <c r="AD88" s="98" t="n"/>
+      <c r="AE88" s="98" t="n"/>
+      <c r="AF88" s="98" t="n"/>
+      <c r="AG88" s="98" t="n"/>
+      <c r="AH88" s="98" t="n"/>
+      <c r="AI88" s="98" t="n"/>
       <c r="AJ88" s="98" t="n"/>
       <c r="AK88" s="98" t="n"/>
-      <c r="AL88" s="98" t="n"/>
+      <c r="AL88" s="99" t="n"/>
       <c r="AM88" s="72" t="n"/>
       <c r="AN88" s="72" t="n"/>
       <c r="AO88" s="72" t="n"/>
@@ -7708,14 +7710,12 @@
     </row>
     <row r="89" ht="17.25" customHeight="1" s="103">
       <c r="A89" s="59" t="n"/>
-      <c r="B89" s="60" t="inlineStr">
-        <is>
-          <t>5.3.2</t>
-        </is>
-      </c>
-      <c r="C89" s="82" t="inlineStr">
-        <is>
-          <t>금액·검수·승인·권한·2~3차 동의 흐름 검증</t>
+      <c r="B89" s="60" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C89" s="61" t="inlineStr">
+        <is>
+          <t>[7주] 서비스 테스트 계획·결과서</t>
         </is>
       </c>
       <c r="D89" s="96" t="inlineStr">
@@ -7724,13 +7724,13 @@
         </is>
       </c>
       <c r="E89" s="63" t="n">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="F89" s="63" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="G89" s="64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H89" s="65" t="n">
         <v>0</v>
@@ -7762,14 +7762,14 @@
       <c r="AG89" s="73" t="n"/>
       <c r="AH89" s="72" t="n"/>
       <c r="AI89" s="72" t="n"/>
-      <c r="AJ89" s="72" t="n"/>
-      <c r="AK89" s="72" t="n"/>
-      <c r="AL89" s="72" t="n"/>
+      <c r="AJ89" s="98" t="n"/>
+      <c r="AK89" s="98" t="n"/>
+      <c r="AL89" s="98" t="n"/>
       <c r="AM89" s="98" t="n"/>
       <c r="AN89" s="98" t="n"/>
       <c r="AO89" s="98" t="n"/>
       <c r="AP89" s="98" t="n"/>
-      <c r="AQ89" s="72" t="n"/>
+      <c r="AQ89" s="99" t="n"/>
       <c r="AR89" s="74" t="n"/>
       <c r="AS89" s="74" t="n"/>
       <c r="AT89" s="74" t="n"/>
@@ -7786,27 +7786,27 @@
       <c r="A90" s="59" t="n"/>
       <c r="B90" s="60" t="inlineStr">
         <is>
-          <t>5.3.3</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="C90" s="82" t="inlineStr">
         <is>
-          <t>버그 수정·회귀·결과서 검토·제출</t>
+          <t>10/15 요구사항·경계·보안 시험 설계</t>
         </is>
       </c>
       <c r="D90" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E90" s="63" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F90" s="63" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="G90" s="64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H90" s="65" t="n">
         <v>0</v>
@@ -7838,14 +7838,14 @@
       <c r="AG90" s="73" t="n"/>
       <c r="AH90" s="72" t="n"/>
       <c r="AI90" s="72" t="n"/>
-      <c r="AJ90" s="72" t="n"/>
-      <c r="AK90" s="72" t="n"/>
-      <c r="AL90" s="72" t="n"/>
+      <c r="AJ90" s="98" t="n"/>
+      <c r="AK90" s="98" t="n"/>
+      <c r="AL90" s="98" t="n"/>
       <c r="AM90" s="72" t="n"/>
       <c r="AN90" s="72" t="n"/>
       <c r="AO90" s="72" t="n"/>
-      <c r="AP90" s="98" t="n"/>
-      <c r="AQ90" s="98" t="n"/>
+      <c r="AP90" s="72" t="n"/>
+      <c r="AQ90" s="72" t="n"/>
       <c r="AR90" s="74" t="n"/>
       <c r="AS90" s="74" t="n"/>
       <c r="AT90" s="74" t="n"/>
@@ -7860,12 +7860,14 @@
     </row>
     <row r="91" ht="17.25" customHeight="1" s="103">
       <c r="A91" s="59" t="n"/>
-      <c r="B91" s="60" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="C91" s="61" t="inlineStr">
-        <is>
-          <t>[8주] LLM 연동 웹 애플리케이션</t>
+      <c r="B91" s="60" t="inlineStr">
+        <is>
+          <t>5.3.2</t>
+        </is>
+      </c>
+      <c r="C91" s="82" t="inlineStr">
+        <is>
+          <t>금액·검수·승인·권한·2~3차 동의 흐름 검증</t>
         </is>
       </c>
       <c r="D91" s="96" t="inlineStr">
@@ -7874,13 +7876,13 @@
         </is>
       </c>
       <c r="E91" s="63" t="n">
-        <v>46314</v>
+        <v>46335</v>
       </c>
       <c r="F91" s="63" t="n">
-        <v>46346</v>
+        <v>46338</v>
       </c>
       <c r="G91" s="64" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H91" s="65" t="n">
         <v>0</v>
@@ -7900,31 +7902,31 @@
       <c r="U91" s="72" t="n"/>
       <c r="V91" s="72" t="n"/>
       <c r="W91" s="72" t="n"/>
-      <c r="X91" s="98" t="n"/>
-      <c r="Y91" s="98" t="n"/>
-      <c r="Z91" s="98" t="n"/>
-      <c r="AA91" s="98" t="n"/>
-      <c r="AB91" s="98" t="n"/>
-      <c r="AC91" s="98" t="n"/>
-      <c r="AD91" s="98" t="n"/>
-      <c r="AE91" s="98" t="n"/>
-      <c r="AF91" s="98" t="n"/>
-      <c r="AG91" s="98" t="n"/>
-      <c r="AH91" s="98" t="n"/>
-      <c r="AI91" s="98" t="n"/>
-      <c r="AJ91" s="98" t="n"/>
-      <c r="AK91" s="98" t="n"/>
-      <c r="AL91" s="98" t="n"/>
+      <c r="X91" s="72" t="n"/>
+      <c r="Y91" s="72" t="n"/>
+      <c r="Z91" s="72" t="n"/>
+      <c r="AA91" s="72" t="n"/>
+      <c r="AB91" s="72" t="n"/>
+      <c r="AC91" s="73" t="n"/>
+      <c r="AD91" s="73" t="n"/>
+      <c r="AE91" s="73" t="n"/>
+      <c r="AF91" s="73" t="n"/>
+      <c r="AG91" s="73" t="n"/>
+      <c r="AH91" s="72" t="n"/>
+      <c r="AI91" s="72" t="n"/>
+      <c r="AJ91" s="72" t="n"/>
+      <c r="AK91" s="72" t="n"/>
+      <c r="AL91" s="72" t="n"/>
       <c r="AM91" s="98" t="n"/>
       <c r="AN91" s="98" t="n"/>
       <c r="AO91" s="98" t="n"/>
       <c r="AP91" s="98" t="n"/>
-      <c r="AQ91" s="98" t="n"/>
-      <c r="AR91" s="98" t="n"/>
-      <c r="AS91" s="98" t="n"/>
-      <c r="AT91" s="98" t="n"/>
-      <c r="AU91" s="98" t="n"/>
-      <c r="AV91" s="99" t="n"/>
+      <c r="AQ91" s="72" t="n"/>
+      <c r="AR91" s="74" t="n"/>
+      <c r="AS91" s="74" t="n"/>
+      <c r="AT91" s="74" t="n"/>
+      <c r="AU91" s="74" t="n"/>
+      <c r="AV91" s="74" t="n"/>
       <c r="AW91" s="72" t="n"/>
       <c r="AX91" s="72" t="n"/>
       <c r="AY91" s="72" t="n"/>
@@ -7936,27 +7938,27 @@
       <c r="A92" s="59" t="n"/>
       <c r="B92" s="60" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.3.3</t>
         </is>
       </c>
       <c r="C92" s="82" t="inlineStr">
         <is>
-          <t>(1차) React 초기 설정·공통 컴포넌트·배포</t>
+          <t>버그 수정·회귀·결과서 검토·제출</t>
         </is>
       </c>
       <c r="D92" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E92" s="63" t="n">
-        <v>46314</v>
+        <v>46338</v>
       </c>
       <c r="F92" s="63" t="n">
-        <v>46318</v>
+        <v>46339</v>
       </c>
       <c r="G92" s="64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H92" s="65" t="n">
         <v>0</v>
@@ -7976,11 +7978,11 @@
       <c r="U92" s="72" t="n"/>
       <c r="V92" s="72" t="n"/>
       <c r="W92" s="72" t="n"/>
-      <c r="X92" s="98" t="n"/>
-      <c r="Y92" s="98" t="n"/>
-      <c r="Z92" s="98" t="n"/>
-      <c r="AA92" s="98" t="n"/>
-      <c r="AB92" s="98" t="n"/>
+      <c r="X92" s="72" t="n"/>
+      <c r="Y92" s="72" t="n"/>
+      <c r="Z92" s="72" t="n"/>
+      <c r="AA92" s="72" t="n"/>
+      <c r="AB92" s="72" t="n"/>
       <c r="AC92" s="73" t="n"/>
       <c r="AD92" s="73" t="n"/>
       <c r="AE92" s="73" t="n"/>
@@ -7994,8 +7996,8 @@
       <c r="AM92" s="72" t="n"/>
       <c r="AN92" s="72" t="n"/>
       <c r="AO92" s="72" t="n"/>
-      <c r="AP92" s="72" t="n"/>
-      <c r="AQ92" s="72" t="n"/>
+      <c r="AP92" s="98" t="n"/>
+      <c r="AQ92" s="98" t="n"/>
       <c r="AR92" s="74" t="n"/>
       <c r="AS92" s="74" t="n"/>
       <c r="AT92" s="74" t="n"/>
@@ -8010,29 +8012,27 @@
     </row>
     <row r="93" ht="17.25" customHeight="1" s="103">
       <c r="A93" s="59" t="n"/>
-      <c r="B93" s="60" t="inlineStr">
-        <is>
-          <t>5.4.2</t>
-        </is>
-      </c>
-      <c r="C93" s="82" t="inlineStr">
-        <is>
-          <t>(1차) 회원·CODEF 계좌·카드 연결·거래 내역 화면</t>
+      <c r="B93" s="60" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C93" s="61" t="inlineStr">
+        <is>
+          <t>[8주] LLM 연동 웹 애플리케이션</t>
         </is>
       </c>
       <c r="D93" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E93" s="63" t="n">
         <v>46314</v>
       </c>
       <c r="F93" s="63" t="n">
-        <v>46325</v>
+        <v>46346</v>
       </c>
       <c r="G93" s="64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H93" s="65" t="n">
         <v>0</v>
@@ -8062,21 +8062,21 @@
       <c r="AE93" s="98" t="n"/>
       <c r="AF93" s="98" t="n"/>
       <c r="AG93" s="98" t="n"/>
-      <c r="AH93" s="72" t="n"/>
-      <c r="AI93" s="72" t="n"/>
-      <c r="AJ93" s="72" t="n"/>
-      <c r="AK93" s="72" t="n"/>
-      <c r="AL93" s="72" t="n"/>
-      <c r="AM93" s="72" t="n"/>
-      <c r="AN93" s="72" t="n"/>
-      <c r="AO93" s="72" t="n"/>
-      <c r="AP93" s="72" t="n"/>
-      <c r="AQ93" s="72" t="n"/>
-      <c r="AR93" s="74" t="n"/>
-      <c r="AS93" s="74" t="n"/>
-      <c r="AT93" s="74" t="n"/>
-      <c r="AU93" s="74" t="n"/>
-      <c r="AV93" s="74" t="n"/>
+      <c r="AH93" s="98" t="n"/>
+      <c r="AI93" s="98" t="n"/>
+      <c r="AJ93" s="98" t="n"/>
+      <c r="AK93" s="98" t="n"/>
+      <c r="AL93" s="98" t="n"/>
+      <c r="AM93" s="98" t="n"/>
+      <c r="AN93" s="98" t="n"/>
+      <c r="AO93" s="98" t="n"/>
+      <c r="AP93" s="98" t="n"/>
+      <c r="AQ93" s="98" t="n"/>
+      <c r="AR93" s="98" t="n"/>
+      <c r="AS93" s="98" t="n"/>
+      <c r="AT93" s="98" t="n"/>
+      <c r="AU93" s="98" t="n"/>
+      <c r="AV93" s="99" t="n"/>
       <c r="AW93" s="72" t="n"/>
       <c r="AX93" s="72" t="n"/>
       <c r="AY93" s="72" t="n"/>
@@ -8088,27 +8088,27 @@
       <c r="A94" s="59" t="n"/>
       <c r="B94" s="60" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C94" s="82" t="inlineStr">
         <is>
-          <t>(1차) 온보딩(고정지출·구독 확인)·추천 예산·예산 조정·승인 화면</t>
+          <t>(1차) React 초기 설정·공통 컴포넌트·배포</t>
         </is>
       </c>
       <c r="D94" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E94" s="63" t="n">
-        <v>46316</v>
+        <v>46314</v>
       </c>
       <c r="F94" s="63" t="n">
-        <v>46329</v>
+        <v>46318</v>
       </c>
       <c r="G94" s="64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H94" s="65" t="n">
         <v>0</v>
@@ -8128,18 +8128,18 @@
       <c r="U94" s="72" t="n"/>
       <c r="V94" s="72" t="n"/>
       <c r="W94" s="72" t="n"/>
-      <c r="X94" s="72" t="n"/>
-      <c r="Y94" s="72" t="n"/>
+      <c r="X94" s="98" t="n"/>
+      <c r="Y94" s="98" t="n"/>
       <c r="Z94" s="98" t="n"/>
       <c r="AA94" s="98" t="n"/>
       <c r="AB94" s="98" t="n"/>
-      <c r="AC94" s="98" t="n"/>
-      <c r="AD94" s="98" t="n"/>
-      <c r="AE94" s="98" t="n"/>
-      <c r="AF94" s="98" t="n"/>
-      <c r="AG94" s="98" t="n"/>
-      <c r="AH94" s="98" t="n"/>
-      <c r="AI94" s="98" t="n"/>
+      <c r="AC94" s="73" t="n"/>
+      <c r="AD94" s="73" t="n"/>
+      <c r="AE94" s="73" t="n"/>
+      <c r="AF94" s="73" t="n"/>
+      <c r="AG94" s="73" t="n"/>
+      <c r="AH94" s="72" t="n"/>
+      <c r="AI94" s="72" t="n"/>
       <c r="AJ94" s="72" t="n"/>
       <c r="AK94" s="72" t="n"/>
       <c r="AL94" s="72" t="n"/>
@@ -8164,27 +8164,27 @@
       <c r="A95" s="59" t="n"/>
       <c r="B95" s="60" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C95" s="82" t="inlineStr">
         <is>
-          <t>(1차) 홈·머니 쿠션(월급×3 판정·설정 선택)</t>
+          <t>(1차) 회원·CODEF 계좌·카드 연결·거래 내역 화면</t>
         </is>
       </c>
       <c r="D95" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E95" s="63" t="n">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="F95" s="63" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="G95" s="64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H95" s="65" t="n">
         <v>0</v>
@@ -8204,18 +8204,18 @@
       <c r="U95" s="72" t="n"/>
       <c r="V95" s="72" t="n"/>
       <c r="W95" s="72" t="n"/>
-      <c r="X95" s="72" t="n"/>
-      <c r="Y95" s="72" t="n"/>
-      <c r="Z95" s="72" t="n"/>
-      <c r="AA95" s="72" t="n"/>
-      <c r="AB95" s="72" t="n"/>
+      <c r="X95" s="98" t="n"/>
+      <c r="Y95" s="98" t="n"/>
+      <c r="Z95" s="98" t="n"/>
+      <c r="AA95" s="98" t="n"/>
+      <c r="AB95" s="98" t="n"/>
       <c r="AC95" s="98" t="n"/>
       <c r="AD95" s="98" t="n"/>
       <c r="AE95" s="98" t="n"/>
       <c r="AF95" s="98" t="n"/>
       <c r="AG95" s="98" t="n"/>
-      <c r="AH95" s="98" t="n"/>
-      <c r="AI95" s="98" t="n"/>
+      <c r="AH95" s="72" t="n"/>
+      <c r="AI95" s="72" t="n"/>
       <c r="AJ95" s="72" t="n"/>
       <c r="AK95" s="72" t="n"/>
       <c r="AL95" s="72" t="n"/>
@@ -8240,27 +8240,27 @@
       <c r="A96" s="59" t="n"/>
       <c r="B96" s="60" t="inlineStr">
         <is>
-          <t>5.4.5</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C96" s="82" t="inlineStr">
         <is>
-          <t>(1차) 통합 챗봇 화면·에이전트 연동</t>
+          <t>(1차) 온보딩·추천 예산(자물쇠·초안 수정)·조정·승인 화면</t>
         </is>
       </c>
       <c r="D96" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E96" s="63" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="F96" s="63" t="n">
         <v>46329</v>
       </c>
       <c r="G96" s="64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H96" s="65" t="n">
         <v>0</v>
@@ -8282,9 +8282,9 @@
       <c r="W96" s="72" t="n"/>
       <c r="X96" s="72" t="n"/>
       <c r="Y96" s="72" t="n"/>
-      <c r="Z96" s="72" t="n"/>
-      <c r="AA96" s="72" t="n"/>
-      <c r="AB96" s="72" t="n"/>
+      <c r="Z96" s="98" t="n"/>
+      <c r="AA96" s="98" t="n"/>
+      <c r="AB96" s="98" t="n"/>
       <c r="AC96" s="98" t="n"/>
       <c r="AD96" s="98" t="n"/>
       <c r="AE96" s="98" t="n"/>
@@ -8316,27 +8316,27 @@
       <c r="A97" s="59" t="n"/>
       <c r="B97" s="60" t="inlineStr">
         <is>
-          <t>5.4.6</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C97" s="82" t="inlineStr">
         <is>
-          <t>1차 MVP 통합 점검(핵심 흐름 E2E)</t>
+          <t>(1차) 홈(더 써도 되는 돈)·머니 쿠션(월급×3)</t>
         </is>
       </c>
       <c r="D97" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E97" s="63" t="n">
-        <v>46330</v>
+        <v>46321</v>
       </c>
       <c r="F97" s="63" t="n">
-        <v>46331</v>
+        <v>46329</v>
       </c>
       <c r="G97" s="64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H97" s="65" t="n">
         <v>0</v>
@@ -8361,15 +8361,15 @@
       <c r="Z97" s="72" t="n"/>
       <c r="AA97" s="72" t="n"/>
       <c r="AB97" s="72" t="n"/>
-      <c r="AC97" s="73" t="n"/>
-      <c r="AD97" s="73" t="n"/>
-      <c r="AE97" s="73" t="n"/>
-      <c r="AF97" s="73" t="n"/>
-      <c r="AG97" s="73" t="n"/>
-      <c r="AH97" s="72" t="n"/>
-      <c r="AI97" s="72" t="n"/>
-      <c r="AJ97" s="98" t="n"/>
-      <c r="AK97" s="98" t="n"/>
+      <c r="AC97" s="98" t="n"/>
+      <c r="AD97" s="98" t="n"/>
+      <c r="AE97" s="98" t="n"/>
+      <c r="AF97" s="98" t="n"/>
+      <c r="AG97" s="98" t="n"/>
+      <c r="AH97" s="98" t="n"/>
+      <c r="AI97" s="98" t="n"/>
+      <c r="AJ97" s="72" t="n"/>
+      <c r="AK97" s="72" t="n"/>
       <c r="AL97" s="72" t="n"/>
       <c r="AM97" s="72" t="n"/>
       <c r="AN97" s="72" t="n"/>
@@ -8392,27 +8392,27 @@
       <c r="A98" s="59" t="n"/>
       <c r="B98" s="60" t="inlineStr">
         <is>
-          <t>5.4.7</t>
+          <t>5.4.5</t>
         </is>
       </c>
       <c r="C98" s="82" t="inlineStr">
         <is>
-          <t>(2차) 소비 분석: 서버 계산·템플릿·또래 비교</t>
+          <t>(1차) 통합 챗봇 화면·에이전트 연동·챗봇 소비 분석</t>
         </is>
       </c>
       <c r="D98" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E98" s="63" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="F98" s="63" t="n">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="G98" s="64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H98" s="65" t="n">
         <v>0</v>
@@ -8437,16 +8437,16 @@
       <c r="Z98" s="72" t="n"/>
       <c r="AA98" s="72" t="n"/>
       <c r="AB98" s="72" t="n"/>
-      <c r="AC98" s="73" t="n"/>
-      <c r="AD98" s="73" t="n"/>
+      <c r="AC98" s="98" t="n"/>
+      <c r="AD98" s="98" t="n"/>
       <c r="AE98" s="98" t="n"/>
       <c r="AF98" s="98" t="n"/>
       <c r="AG98" s="98" t="n"/>
       <c r="AH98" s="98" t="n"/>
       <c r="AI98" s="98" t="n"/>
-      <c r="AJ98" s="98" t="n"/>
-      <c r="AK98" s="98" t="n"/>
-      <c r="AL98" s="98" t="n"/>
+      <c r="AJ98" s="72" t="n"/>
+      <c r="AK98" s="72" t="n"/>
+      <c r="AL98" s="72" t="n"/>
       <c r="AM98" s="72" t="n"/>
       <c r="AN98" s="72" t="n"/>
       <c r="AO98" s="72" t="n"/>
@@ -8468,27 +8468,27 @@
       <c r="A99" s="59" t="n"/>
       <c r="B99" s="60" t="inlineStr">
         <is>
-          <t>5.4.8</t>
+          <t>5.4.6</t>
         </is>
       </c>
       <c r="C99" s="82" t="inlineStr">
         <is>
-          <t>(2차) 소액 돌발지출 처리 화면</t>
+          <t>(1차) 소비 집계 서버 계산(챗봇 소비 분석)</t>
         </is>
       </c>
       <c r="D99" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E99" s="63" t="n">
-        <v>46330</v>
+        <v>46321</v>
       </c>
       <c r="F99" s="63" t="n">
-        <v>46335</v>
+        <v>46325</v>
       </c>
       <c r="G99" s="64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H99" s="65" t="n">
         <v>0</v>
@@ -8513,17 +8513,17 @@
       <c r="Z99" s="72" t="n"/>
       <c r="AA99" s="72" t="n"/>
       <c r="AB99" s="72" t="n"/>
-      <c r="AC99" s="73" t="n"/>
-      <c r="AD99" s="73" t="n"/>
-      <c r="AE99" s="73" t="n"/>
-      <c r="AF99" s="73" t="n"/>
-      <c r="AG99" s="73" t="n"/>
+      <c r="AC99" s="98" t="n"/>
+      <c r="AD99" s="98" t="n"/>
+      <c r="AE99" s="98" t="n"/>
+      <c r="AF99" s="98" t="n"/>
+      <c r="AG99" s="98" t="n"/>
       <c r="AH99" s="72" t="n"/>
       <c r="AI99" s="72" t="n"/>
-      <c r="AJ99" s="98" t="n"/>
-      <c r="AK99" s="98" t="n"/>
-      <c r="AL99" s="98" t="n"/>
-      <c r="AM99" s="98" t="n"/>
+      <c r="AJ99" s="72" t="n"/>
+      <c r="AK99" s="72" t="n"/>
+      <c r="AL99" s="72" t="n"/>
+      <c r="AM99" s="72" t="n"/>
       <c r="AN99" s="72" t="n"/>
       <c r="AO99" s="72" t="n"/>
       <c r="AP99" s="72" t="n"/>
@@ -8544,27 +8544,27 @@
       <c r="A100" s="59" t="n"/>
       <c r="B100" s="60" t="inlineStr">
         <is>
-          <t>5.4.9</t>
+          <t>5.4.7</t>
         </is>
       </c>
       <c r="C100" s="82" t="inlineStr">
         <is>
-          <t>(2차) 알림·처리 화면 연결</t>
+          <t>1차 MVP 통합 점검(핵심 흐름 E2E)</t>
         </is>
       </c>
       <c r="D100" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E100" s="63" t="n">
         <v>46330</v>
       </c>
       <c r="F100" s="63" t="n">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="G100" s="64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H100" s="65" t="n">
         <v>0</v>
@@ -8598,8 +8598,8 @@
       <c r="AI100" s="72" t="n"/>
       <c r="AJ100" s="98" t="n"/>
       <c r="AK100" s="98" t="n"/>
-      <c r="AL100" s="98" t="n"/>
-      <c r="AM100" s="98" t="n"/>
+      <c r="AL100" s="72" t="n"/>
+      <c r="AM100" s="72" t="n"/>
       <c r="AN100" s="72" t="n"/>
       <c r="AO100" s="72" t="n"/>
       <c r="AP100" s="72" t="n"/>
@@ -8620,12 +8620,12 @@
       <c r="A101" s="59" t="n"/>
       <c r="B101" s="60" t="inlineStr">
         <is>
-          <t>5.4.10</t>
+          <t>5.4.8</t>
         </is>
       </c>
       <c r="C101" s="82" t="inlineStr">
         <is>
-          <t>(3차) 큰 지출 상담 화면·결과 카드</t>
+          <t>(2차) 소비 분석 화면·변경 이력·또래 비교</t>
         </is>
       </c>
       <c r="D101" s="96" t="inlineStr">
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="E101" s="63" t="n">
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="F101" s="63" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="G101" s="64" t="n">
         <v>5</v>
@@ -8670,16 +8670,16 @@
       <c r="AE101" s="73" t="n"/>
       <c r="AF101" s="73" t="n"/>
       <c r="AG101" s="73" t="n"/>
-      <c r="AH101" s="72" t="n"/>
-      <c r="AI101" s="72" t="n"/>
-      <c r="AJ101" s="72" t="n"/>
-      <c r="AK101" s="72" t="n"/>
-      <c r="AL101" s="72" t="n"/>
-      <c r="AM101" s="98" t="n"/>
-      <c r="AN101" s="98" t="n"/>
-      <c r="AO101" s="98" t="n"/>
-      <c r="AP101" s="98" t="n"/>
-      <c r="AQ101" s="98" t="n"/>
+      <c r="AH101" s="98" t="n"/>
+      <c r="AI101" s="98" t="n"/>
+      <c r="AJ101" s="98" t="n"/>
+      <c r="AK101" s="98" t="n"/>
+      <c r="AL101" s="98" t="n"/>
+      <c r="AM101" s="72" t="n"/>
+      <c r="AN101" s="72" t="n"/>
+      <c r="AO101" s="72" t="n"/>
+      <c r="AP101" s="72" t="n"/>
+      <c r="AQ101" s="72" t="n"/>
       <c r="AR101" s="74" t="n"/>
       <c r="AS101" s="74" t="n"/>
       <c r="AT101" s="74" t="n"/>
@@ -8696,24 +8696,24 @@
       <c r="A102" s="59" t="n"/>
       <c r="B102" s="60" t="inlineStr">
         <is>
-          <t>5.4.11</t>
+          <t>5.4.9</t>
         </is>
       </c>
       <c r="C102" s="82" t="inlineStr">
         <is>
-          <t>중요 결함 수정·회귀·시연 환경 점검</t>
+          <t>(2차) 소액 돌발·카테고리 초과 감지→조정 화면</t>
         </is>
       </c>
       <c r="D102" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E102" s="63" t="n">
-        <v>46339</v>
+        <v>46330</v>
       </c>
       <c r="F102" s="63" t="n">
-        <v>46344</v>
+        <v>46335</v>
       </c>
       <c r="G102" s="64" t="n">
         <v>4</v>
@@ -8748,17 +8748,17 @@
       <c r="AG102" s="73" t="n"/>
       <c r="AH102" s="72" t="n"/>
       <c r="AI102" s="72" t="n"/>
-      <c r="AJ102" s="72" t="n"/>
-      <c r="AK102" s="72" t="n"/>
-      <c r="AL102" s="72" t="n"/>
-      <c r="AM102" s="72" t="n"/>
+      <c r="AJ102" s="98" t="n"/>
+      <c r="AK102" s="98" t="n"/>
+      <c r="AL102" s="98" t="n"/>
+      <c r="AM102" s="98" t="n"/>
       <c r="AN102" s="72" t="n"/>
       <c r="AO102" s="72" t="n"/>
       <c r="AP102" s="72" t="n"/>
-      <c r="AQ102" s="98" t="n"/>
-      <c r="AR102" s="98" t="n"/>
-      <c r="AS102" s="98" t="n"/>
-      <c r="AT102" s="98" t="n"/>
+      <c r="AQ102" s="72" t="n"/>
+      <c r="AR102" s="74" t="n"/>
+      <c r="AS102" s="74" t="n"/>
+      <c r="AT102" s="74" t="n"/>
       <c r="AU102" s="74" t="n"/>
       <c r="AV102" s="74" t="n"/>
       <c r="AW102" s="72" t="n"/>
@@ -8772,27 +8772,27 @@
       <c r="A103" s="59" t="n"/>
       <c r="B103" s="60" t="inlineStr">
         <is>
-          <t>5.4.12</t>
+          <t>5.4.10</t>
         </is>
       </c>
       <c r="C103" s="82" t="inlineStr">
         <is>
-          <t>보안키 점검·최종 배포·안정화</t>
+          <t>(2차) 알림(지난주 대비 포함)·처리 화면 연결</t>
         </is>
       </c>
       <c r="D103" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E103" s="63" t="n">
-        <v>46345</v>
+        <v>46330</v>
       </c>
       <c r="F103" s="63" t="n">
-        <v>46346</v>
+        <v>46335</v>
       </c>
       <c r="G103" s="64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H103" s="65" t="n">
         <v>0</v>
@@ -8824,10 +8824,10 @@
       <c r="AG103" s="73" t="n"/>
       <c r="AH103" s="72" t="n"/>
       <c r="AI103" s="72" t="n"/>
-      <c r="AJ103" s="72" t="n"/>
-      <c r="AK103" s="72" t="n"/>
-      <c r="AL103" s="72" t="n"/>
-      <c r="AM103" s="72" t="n"/>
+      <c r="AJ103" s="98" t="n"/>
+      <c r="AK103" s="98" t="n"/>
+      <c r="AL103" s="98" t="n"/>
+      <c r="AM103" s="98" t="n"/>
       <c r="AN103" s="72" t="n"/>
       <c r="AO103" s="72" t="n"/>
       <c r="AP103" s="72" t="n"/>
@@ -8835,8 +8835,8 @@
       <c r="AR103" s="74" t="n"/>
       <c r="AS103" s="74" t="n"/>
       <c r="AT103" s="74" t="n"/>
-      <c r="AU103" s="98" t="n"/>
-      <c r="AV103" s="98" t="n"/>
+      <c r="AU103" s="74" t="n"/>
+      <c r="AV103" s="74" t="n"/>
       <c r="AW103" s="72" t="n"/>
       <c r="AX103" s="72" t="n"/>
       <c r="AY103" s="72" t="n"/>
@@ -8845,83 +8845,91 @@
       <c r="BB103" s="75" t="n"/>
     </row>
     <row r="104" ht="21" customHeight="1" s="103">
-      <c r="A104" s="47" t="n"/>
-      <c r="B104" s="48" t="n">
-        <v>6</v>
-      </c>
-      <c r="C104" s="49" t="inlineStr">
-        <is>
-          <t>발표 및 시연</t>
-        </is>
-      </c>
-      <c r="D104" s="50" t="n"/>
-      <c r="E104" s="51" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F104" s="51" t="n">
-        <v>46346</v>
-      </c>
-      <c r="G104" s="52" t="n">
-        <v>30</v>
-      </c>
-      <c r="H104" s="53" t="n">
+      <c r="A104" s="59" t="n"/>
+      <c r="B104" s="60" t="inlineStr">
+        <is>
+          <t>5.4.11</t>
+        </is>
+      </c>
+      <c r="C104" s="82" t="inlineStr">
+        <is>
+          <t>(3차) 큰 지출 상담 화면·결과 카드</t>
+        </is>
+      </c>
+      <c r="D104" s="96" t="inlineStr">
+        <is>
+          <t>권세진</t>
+        </is>
+      </c>
+      <c r="E104" s="63" t="n">
+        <v>46335</v>
+      </c>
+      <c r="F104" s="63" t="n">
+        <v>46339</v>
+      </c>
+      <c r="G104" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H104" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="I104" s="58" t="n"/>
-      <c r="J104" s="84" t="n"/>
-      <c r="K104" s="111" t="n"/>
-      <c r="L104" s="111" t="n"/>
-      <c r="M104" s="58" t="n"/>
-      <c r="N104" s="57" t="n"/>
-      <c r="O104" s="58" t="n"/>
-      <c r="P104" s="58" t="n"/>
-      <c r="Q104" s="58" t="n"/>
-      <c r="R104" s="57" t="n"/>
-      <c r="S104" s="100" t="n"/>
-      <c r="T104" s="100" t="n"/>
-      <c r="U104" s="100" t="n"/>
-      <c r="V104" s="100" t="n"/>
-      <c r="W104" s="100" t="n"/>
-      <c r="X104" s="100" t="n"/>
-      <c r="Y104" s="100" t="n"/>
-      <c r="Z104" s="100" t="n"/>
-      <c r="AA104" s="100" t="n"/>
-      <c r="AB104" s="100" t="n"/>
-      <c r="AC104" s="100" t="n"/>
-      <c r="AD104" s="100" t="n"/>
-      <c r="AE104" s="100" t="n"/>
-      <c r="AF104" s="100" t="n"/>
-      <c r="AG104" s="100" t="n"/>
-      <c r="AH104" s="100" t="n"/>
-      <c r="AI104" s="100" t="n"/>
-      <c r="AJ104" s="100" t="n"/>
-      <c r="AK104" s="100" t="n"/>
-      <c r="AL104" s="100" t="n"/>
-      <c r="AM104" s="100" t="n"/>
-      <c r="AN104" s="100" t="n"/>
-      <c r="AO104" s="100" t="n"/>
-      <c r="AP104" s="100" t="n"/>
-      <c r="AQ104" s="100" t="n"/>
-      <c r="AR104" s="100" t="n"/>
-      <c r="AS104" s="100" t="n"/>
-      <c r="AT104" s="100" t="n"/>
-      <c r="AU104" s="100" t="n"/>
-      <c r="AV104" s="100" t="n"/>
-      <c r="AW104" s="58" t="n"/>
-      <c r="AX104" s="58" t="n"/>
-      <c r="AY104" s="58" t="n"/>
-      <c r="AZ104" s="58" t="n"/>
-      <c r="BA104" s="58" t="n"/>
-      <c r="BB104" s="29" t="n"/>
+      <c r="I104" s="77" t="n"/>
+      <c r="J104" s="79" t="n"/>
+      <c r="K104" s="72" t="n"/>
+      <c r="L104" s="72" t="n"/>
+      <c r="M104" s="72" t="n"/>
+      <c r="N104" s="70" t="n"/>
+      <c r="O104" s="71" t="n"/>
+      <c r="P104" s="71" t="n"/>
+      <c r="Q104" s="71" t="n"/>
+      <c r="R104" s="70" t="n"/>
+      <c r="S104" s="72" t="n"/>
+      <c r="T104" s="72" t="n"/>
+      <c r="U104" s="72" t="n"/>
+      <c r="V104" s="72" t="n"/>
+      <c r="W104" s="72" t="n"/>
+      <c r="X104" s="72" t="n"/>
+      <c r="Y104" s="72" t="n"/>
+      <c r="Z104" s="72" t="n"/>
+      <c r="AA104" s="72" t="n"/>
+      <c r="AB104" s="72" t="n"/>
+      <c r="AC104" s="73" t="n"/>
+      <c r="AD104" s="73" t="n"/>
+      <c r="AE104" s="73" t="n"/>
+      <c r="AF104" s="73" t="n"/>
+      <c r="AG104" s="73" t="n"/>
+      <c r="AH104" s="72" t="n"/>
+      <c r="AI104" s="72" t="n"/>
+      <c r="AJ104" s="72" t="n"/>
+      <c r="AK104" s="72" t="n"/>
+      <c r="AL104" s="72" t="n"/>
+      <c r="AM104" s="98" t="n"/>
+      <c r="AN104" s="98" t="n"/>
+      <c r="AO104" s="98" t="n"/>
+      <c r="AP104" s="98" t="n"/>
+      <c r="AQ104" s="98" t="n"/>
+      <c r="AR104" s="74" t="n"/>
+      <c r="AS104" s="74" t="n"/>
+      <c r="AT104" s="74" t="n"/>
+      <c r="AU104" s="74" t="n"/>
+      <c r="AV104" s="74" t="n"/>
+      <c r="AW104" s="72" t="n"/>
+      <c r="AX104" s="72" t="n"/>
+      <c r="AY104" s="72" t="n"/>
+      <c r="AZ104" s="72" t="n"/>
+      <c r="BA104" s="72" t="n"/>
+      <c r="BB104" s="75" t="n"/>
     </row>
     <row r="105" ht="17.25" customHeight="1" s="103">
       <c r="A105" s="59" t="n"/>
-      <c r="B105" s="60" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="C105" s="61" t="inlineStr">
-        <is>
-          <t>[안내4주] 중간 PT(10/16 우선)</t>
+      <c r="B105" s="60" t="inlineStr">
+        <is>
+          <t>5.4.12</t>
+        </is>
+      </c>
+      <c r="C105" s="82" t="inlineStr">
+        <is>
+          <t>중요 결함 수정·회귀·시연 환경 점검</t>
         </is>
       </c>
       <c r="D105" s="96" t="inlineStr">
@@ -8930,13 +8938,13 @@
         </is>
       </c>
       <c r="E105" s="63" t="n">
-        <v>46307</v>
+        <v>46339</v>
       </c>
       <c r="F105" s="63" t="n">
-        <v>46311</v>
+        <v>46344</v>
       </c>
       <c r="G105" s="64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H105" s="65" t="n">
         <v>0</v>
@@ -8951,11 +8959,11 @@
       <c r="P105" s="71" t="n"/>
       <c r="Q105" s="71" t="n"/>
       <c r="R105" s="70" t="n"/>
-      <c r="S105" s="101" t="n"/>
-      <c r="T105" s="101" t="n"/>
-      <c r="U105" s="101" t="n"/>
-      <c r="V105" s="101" t="n"/>
-      <c r="W105" s="102" t="n"/>
+      <c r="S105" s="72" t="n"/>
+      <c r="T105" s="72" t="n"/>
+      <c r="U105" s="72" t="n"/>
+      <c r="V105" s="72" t="n"/>
+      <c r="W105" s="72" t="n"/>
       <c r="X105" s="72" t="n"/>
       <c r="Y105" s="72" t="n"/>
       <c r="Z105" s="72" t="n"/>
@@ -8975,10 +8983,10 @@
       <c r="AN105" s="72" t="n"/>
       <c r="AO105" s="72" t="n"/>
       <c r="AP105" s="72" t="n"/>
-      <c r="AQ105" s="72" t="n"/>
-      <c r="AR105" s="74" t="n"/>
-      <c r="AS105" s="74" t="n"/>
-      <c r="AT105" s="74" t="n"/>
+      <c r="AQ105" s="98" t="n"/>
+      <c r="AR105" s="98" t="n"/>
+      <c r="AS105" s="98" t="n"/>
+      <c r="AT105" s="98" t="n"/>
       <c r="AU105" s="74" t="n"/>
       <c r="AV105" s="74" t="n"/>
       <c r="AW105" s="72" t="n"/>
@@ -8992,27 +9000,27 @@
       <c r="A106" s="59" t="n"/>
       <c r="B106" s="60" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>5.4.13</t>
         </is>
       </c>
       <c r="C106" s="82" t="inlineStr">
         <is>
-          <t>중간 PT·v5 기획·화면 프로토타입 준비</t>
+          <t>보안키 점검·최종 배포·안정화</t>
         </is>
       </c>
       <c r="D106" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E106" s="63" t="n">
-        <v>46307</v>
+        <v>46345</v>
       </c>
       <c r="F106" s="63" t="n">
-        <v>46310</v>
+        <v>46346</v>
       </c>
       <c r="G106" s="64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H106" s="65" t="n">
         <v>0</v>
@@ -9027,10 +9035,10 @@
       <c r="P106" s="71" t="n"/>
       <c r="Q106" s="71" t="n"/>
       <c r="R106" s="70" t="n"/>
-      <c r="S106" s="101" t="n"/>
-      <c r="T106" s="101" t="n"/>
-      <c r="U106" s="101" t="n"/>
-      <c r="V106" s="101" t="n"/>
+      <c r="S106" s="72" t="n"/>
+      <c r="T106" s="72" t="n"/>
+      <c r="U106" s="72" t="n"/>
+      <c r="V106" s="72" t="n"/>
       <c r="W106" s="72" t="n"/>
       <c r="X106" s="72" t="n"/>
       <c r="Y106" s="72" t="n"/>
@@ -9055,8 +9063,8 @@
       <c r="AR106" s="74" t="n"/>
       <c r="AS106" s="74" t="n"/>
       <c r="AT106" s="74" t="n"/>
-      <c r="AU106" s="74" t="n"/>
-      <c r="AV106" s="74" t="n"/>
+      <c r="AU106" s="98" t="n"/>
+      <c r="AV106" s="98" t="n"/>
       <c r="AW106" s="72" t="n"/>
       <c r="AX106" s="72" t="n"/>
       <c r="AY106" s="72" t="n"/>
@@ -9065,89 +9073,83 @@
       <c r="BB106" s="75" t="n"/>
     </row>
     <row r="107" ht="17.25" customHeight="1" s="103">
-      <c r="A107" s="59" t="n"/>
-      <c r="B107" s="60" t="inlineStr">
-        <is>
-          <t>6.1.2</t>
-        </is>
-      </c>
-      <c r="C107" s="82" t="inlineStr">
-        <is>
-          <t>중간 리허설·발표(10/16 확정)</t>
-        </is>
-      </c>
-      <c r="D107" s="96" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="E107" s="63" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F107" s="63" t="n">
-        <v>46311</v>
-      </c>
-      <c r="G107" s="64" t="n">
-        <v>2</v>
-      </c>
-      <c r="H107" s="65" t="n">
+      <c r="A107" s="47" t="n"/>
+      <c r="B107" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" s="49" t="inlineStr">
+        <is>
+          <t>발표 및 시연</t>
+        </is>
+      </c>
+      <c r="D107" s="50" t="n"/>
+      <c r="E107" s="51" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F107" s="51" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G107" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I107" s="77" t="n"/>
-      <c r="J107" s="79" t="n"/>
-      <c r="K107" s="72" t="n"/>
-      <c r="L107" s="72" t="n"/>
-      <c r="M107" s="72" t="n"/>
-      <c r="N107" s="70" t="n"/>
-      <c r="O107" s="71" t="n"/>
-      <c r="P107" s="71" t="n"/>
-      <c r="Q107" s="71" t="n"/>
-      <c r="R107" s="70" t="n"/>
-      <c r="S107" s="72" t="n"/>
-      <c r="T107" s="72" t="n"/>
-      <c r="U107" s="72" t="n"/>
-      <c r="V107" s="101" t="n"/>
-      <c r="W107" s="101" t="n"/>
-      <c r="X107" s="72" t="n"/>
-      <c r="Y107" s="72" t="n"/>
-      <c r="Z107" s="72" t="n"/>
-      <c r="AA107" s="72" t="n"/>
-      <c r="AB107" s="72" t="n"/>
-      <c r="AC107" s="73" t="n"/>
-      <c r="AD107" s="73" t="n"/>
-      <c r="AE107" s="73" t="n"/>
-      <c r="AF107" s="73" t="n"/>
-      <c r="AG107" s="73" t="n"/>
-      <c r="AH107" s="72" t="n"/>
-      <c r="AI107" s="72" t="n"/>
-      <c r="AJ107" s="72" t="n"/>
-      <c r="AK107" s="72" t="n"/>
-      <c r="AL107" s="72" t="n"/>
-      <c r="AM107" s="72" t="n"/>
-      <c r="AN107" s="72" t="n"/>
-      <c r="AO107" s="72" t="n"/>
-      <c r="AP107" s="72" t="n"/>
-      <c r="AQ107" s="72" t="n"/>
-      <c r="AR107" s="74" t="n"/>
-      <c r="AS107" s="74" t="n"/>
-      <c r="AT107" s="74" t="n"/>
-      <c r="AU107" s="74" t="n"/>
-      <c r="AV107" s="74" t="n"/>
-      <c r="AW107" s="72" t="n"/>
-      <c r="AX107" s="72" t="n"/>
-      <c r="AY107" s="72" t="n"/>
-      <c r="AZ107" s="72" t="n"/>
-      <c r="BA107" s="72" t="n"/>
-      <c r="BB107" s="75" t="n"/>
+      <c r="I107" s="58" t="n"/>
+      <c r="J107" s="84" t="n"/>
+      <c r="K107" s="111" t="n"/>
+      <c r="L107" s="111" t="n"/>
+      <c r="M107" s="58" t="n"/>
+      <c r="N107" s="57" t="n"/>
+      <c r="O107" s="58" t="n"/>
+      <c r="P107" s="58" t="n"/>
+      <c r="Q107" s="58" t="n"/>
+      <c r="R107" s="57" t="n"/>
+      <c r="S107" s="100" t="n"/>
+      <c r="T107" s="100" t="n"/>
+      <c r="U107" s="100" t="n"/>
+      <c r="V107" s="100" t="n"/>
+      <c r="W107" s="100" t="n"/>
+      <c r="X107" s="100" t="n"/>
+      <c r="Y107" s="100" t="n"/>
+      <c r="Z107" s="100" t="n"/>
+      <c r="AA107" s="100" t="n"/>
+      <c r="AB107" s="100" t="n"/>
+      <c r="AC107" s="100" t="n"/>
+      <c r="AD107" s="100" t="n"/>
+      <c r="AE107" s="100" t="n"/>
+      <c r="AF107" s="100" t="n"/>
+      <c r="AG107" s="100" t="n"/>
+      <c r="AH107" s="100" t="n"/>
+      <c r="AI107" s="100" t="n"/>
+      <c r="AJ107" s="100" t="n"/>
+      <c r="AK107" s="100" t="n"/>
+      <c r="AL107" s="100" t="n"/>
+      <c r="AM107" s="100" t="n"/>
+      <c r="AN107" s="100" t="n"/>
+      <c r="AO107" s="100" t="n"/>
+      <c r="AP107" s="100" t="n"/>
+      <c r="AQ107" s="100" t="n"/>
+      <c r="AR107" s="100" t="n"/>
+      <c r="AS107" s="100" t="n"/>
+      <c r="AT107" s="100" t="n"/>
+      <c r="AU107" s="100" t="n"/>
+      <c r="AV107" s="100" t="n"/>
+      <c r="AW107" s="58" t="n"/>
+      <c r="AX107" s="58" t="n"/>
+      <c r="AY107" s="58" t="n"/>
+      <c r="AZ107" s="58" t="n"/>
+      <c r="BA107" s="58" t="n"/>
+      <c r="BB107" s="29" t="n"/>
     </row>
     <row r="108" ht="17.25" customHeight="1" s="103">
       <c r="A108" s="59" t="n"/>
       <c r="B108" s="60" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C108" s="82" t="inlineStr">
-        <is>
-          <t>중간 피드백·우선순위·일정 반영</t>
+        <v>6.1</v>
+      </c>
+      <c r="C108" s="61" t="inlineStr">
+        <is>
+          <t>[안내4주] 중간 PT(10/16 우선)</t>
         </is>
       </c>
       <c r="D108" s="96" t="inlineStr">
@@ -9156,13 +9158,13 @@
         </is>
       </c>
       <c r="E108" s="63" t="n">
-        <v>46321</v>
+        <v>46307</v>
       </c>
       <c r="F108" s="63" t="n">
-        <v>46322</v>
+        <v>46311</v>
       </c>
       <c r="G108" s="64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H108" s="65" t="n">
         <v>0</v>
@@ -9177,18 +9179,18 @@
       <c r="P108" s="71" t="n"/>
       <c r="Q108" s="71" t="n"/>
       <c r="R108" s="70" t="n"/>
-      <c r="S108" s="72" t="n"/>
-      <c r="T108" s="72" t="n"/>
-      <c r="U108" s="72" t="n"/>
-      <c r="V108" s="72" t="n"/>
-      <c r="W108" s="72" t="n"/>
+      <c r="S108" s="101" t="n"/>
+      <c r="T108" s="101" t="n"/>
+      <c r="U108" s="101" t="n"/>
+      <c r="V108" s="101" t="n"/>
+      <c r="W108" s="102" t="n"/>
       <c r="X108" s="72" t="n"/>
       <c r="Y108" s="72" t="n"/>
       <c r="Z108" s="72" t="n"/>
       <c r="AA108" s="72" t="n"/>
       <c r="AB108" s="72" t="n"/>
-      <c r="AC108" s="101" t="n"/>
-      <c r="AD108" s="101" t="n"/>
+      <c r="AC108" s="73" t="n"/>
+      <c r="AD108" s="73" t="n"/>
       <c r="AE108" s="73" t="n"/>
       <c r="AF108" s="73" t="n"/>
       <c r="AG108" s="73" t="n"/>
@@ -9216,12 +9218,14 @@
     </row>
     <row r="109" ht="17.25" customHeight="1" s="103">
       <c r="A109" s="59" t="n"/>
-      <c r="B109" s="60" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C109" s="61" t="inlineStr">
-        <is>
-          <t>[8주] 최종 발표 PT 자료</t>
+      <c r="B109" s="60" t="inlineStr">
+        <is>
+          <t>6.1.1</t>
+        </is>
+      </c>
+      <c r="C109" s="82" t="inlineStr">
+        <is>
+          <t>중간 PT·v5 기획·화면 프로토타입 준비</t>
         </is>
       </c>
       <c r="D109" s="96" t="inlineStr">
@@ -9230,13 +9234,13 @@
         </is>
       </c>
       <c r="E109" s="63" t="n">
-        <v>46335</v>
+        <v>46307</v>
       </c>
       <c r="F109" s="63" t="n">
-        <v>46346</v>
+        <v>46310</v>
       </c>
       <c r="G109" s="64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H109" s="65" t="n">
         <v>0</v>
@@ -9251,10 +9255,10 @@
       <c r="P109" s="71" t="n"/>
       <c r="Q109" s="71" t="n"/>
       <c r="R109" s="70" t="n"/>
-      <c r="S109" s="72" t="n"/>
-      <c r="T109" s="72" t="n"/>
-      <c r="U109" s="72" t="n"/>
-      <c r="V109" s="72" t="n"/>
+      <c r="S109" s="101" t="n"/>
+      <c r="T109" s="101" t="n"/>
+      <c r="U109" s="101" t="n"/>
+      <c r="V109" s="101" t="n"/>
       <c r="W109" s="72" t="n"/>
       <c r="X109" s="72" t="n"/>
       <c r="Y109" s="72" t="n"/>
@@ -9271,16 +9275,16 @@
       <c r="AJ109" s="72" t="n"/>
       <c r="AK109" s="72" t="n"/>
       <c r="AL109" s="72" t="n"/>
-      <c r="AM109" s="101" t="n"/>
-      <c r="AN109" s="101" t="n"/>
-      <c r="AO109" s="101" t="n"/>
-      <c r="AP109" s="101" t="n"/>
-      <c r="AQ109" s="101" t="n"/>
-      <c r="AR109" s="101" t="n"/>
-      <c r="AS109" s="101" t="n"/>
-      <c r="AT109" s="101" t="n"/>
-      <c r="AU109" s="101" t="n"/>
-      <c r="AV109" s="102" t="n"/>
+      <c r="AM109" s="72" t="n"/>
+      <c r="AN109" s="72" t="n"/>
+      <c r="AO109" s="72" t="n"/>
+      <c r="AP109" s="72" t="n"/>
+      <c r="AQ109" s="72" t="n"/>
+      <c r="AR109" s="74" t="n"/>
+      <c r="AS109" s="74" t="n"/>
+      <c r="AT109" s="74" t="n"/>
+      <c r="AU109" s="74" t="n"/>
+      <c r="AV109" s="74" t="n"/>
       <c r="AW109" s="72" t="n"/>
       <c r="AX109" s="72" t="n"/>
       <c r="AY109" s="72" t="n"/>
@@ -9292,12 +9296,12 @@
       <c r="A110" s="59" t="n"/>
       <c r="B110" s="60" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C110" s="82" t="inlineStr">
         <is>
-          <t>평가 결과·성과·한계 PT 검토·제출</t>
+          <t>중간 리허설·발표(10/16 확정)</t>
         </is>
       </c>
       <c r="D110" s="96" t="inlineStr">
@@ -9306,13 +9310,13 @@
         </is>
       </c>
       <c r="E110" s="63" t="n">
-        <v>46335</v>
+        <v>46310</v>
       </c>
       <c r="F110" s="63" t="n">
-        <v>46344</v>
+        <v>46311</v>
       </c>
       <c r="G110" s="64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H110" s="65" t="n">
         <v>0</v>
@@ -9330,8 +9334,8 @@
       <c r="S110" s="72" t="n"/>
       <c r="T110" s="72" t="n"/>
       <c r="U110" s="72" t="n"/>
-      <c r="V110" s="72" t="n"/>
-      <c r="W110" s="72" t="n"/>
+      <c r="V110" s="101" t="n"/>
+      <c r="W110" s="101" t="n"/>
       <c r="X110" s="72" t="n"/>
       <c r="Y110" s="72" t="n"/>
       <c r="Z110" s="72" t="n"/>
@@ -9347,14 +9351,14 @@
       <c r="AJ110" s="72" t="n"/>
       <c r="AK110" s="72" t="n"/>
       <c r="AL110" s="72" t="n"/>
-      <c r="AM110" s="101" t="n"/>
-      <c r="AN110" s="101" t="n"/>
-      <c r="AO110" s="101" t="n"/>
-      <c r="AP110" s="101" t="n"/>
-      <c r="AQ110" s="101" t="n"/>
-      <c r="AR110" s="101" t="n"/>
-      <c r="AS110" s="101" t="n"/>
-      <c r="AT110" s="101" t="n"/>
+      <c r="AM110" s="72" t="n"/>
+      <c r="AN110" s="72" t="n"/>
+      <c r="AO110" s="72" t="n"/>
+      <c r="AP110" s="72" t="n"/>
+      <c r="AQ110" s="72" t="n"/>
+      <c r="AR110" s="74" t="n"/>
+      <c r="AS110" s="74" t="n"/>
+      <c r="AT110" s="74" t="n"/>
       <c r="AU110" s="74" t="n"/>
       <c r="AV110" s="74" t="n"/>
       <c r="AW110" s="72" t="n"/>
@@ -9366,14 +9370,12 @@
     </row>
     <row r="111" ht="17.25" customHeight="1" s="103">
       <c r="A111" s="59" t="n"/>
-      <c r="B111" s="60" t="inlineStr">
-        <is>
-          <t>6.3.2</t>
-        </is>
+      <c r="B111" s="60" t="n">
+        <v>6.2</v>
       </c>
       <c r="C111" s="82" t="inlineStr">
         <is>
-          <t>최종 리허설·발표(11/20)</t>
+          <t>중간 피드백·우선순위·일정 반영</t>
         </is>
       </c>
       <c r="D111" s="96" t="inlineStr">
@@ -9382,10 +9384,10 @@
         </is>
       </c>
       <c r="E111" s="63" t="n">
-        <v>46345</v>
+        <v>46321</v>
       </c>
       <c r="F111" s="63" t="n">
-        <v>46346</v>
+        <v>46322</v>
       </c>
       <c r="G111" s="64" t="n">
         <v>2</v>
@@ -9413,8 +9415,8 @@
       <c r="Z111" s="72" t="n"/>
       <c r="AA111" s="72" t="n"/>
       <c r="AB111" s="72" t="n"/>
-      <c r="AC111" s="73" t="n"/>
-      <c r="AD111" s="73" t="n"/>
+      <c r="AC111" s="101" t="n"/>
+      <c r="AD111" s="101" t="n"/>
       <c r="AE111" s="73" t="n"/>
       <c r="AF111" s="73" t="n"/>
       <c r="AG111" s="73" t="n"/>
@@ -9431,8 +9433,8 @@
       <c r="AR111" s="74" t="n"/>
       <c r="AS111" s="74" t="n"/>
       <c r="AT111" s="74" t="n"/>
-      <c r="AU111" s="101" t="n"/>
-      <c r="AV111" s="101" t="n"/>
+      <c r="AU111" s="74" t="n"/>
+      <c r="AV111" s="74" t="n"/>
       <c r="AW111" s="72" t="n"/>
       <c r="AX111" s="72" t="n"/>
       <c r="AY111" s="72" t="n"/>
@@ -9443,26 +9445,26 @@
     <row r="112" ht="17.25" customHeight="1" s="103">
       <c r="A112" s="59" t="n"/>
       <c r="B112" s="60" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C112" s="61" t="inlineStr">
         <is>
-          <t>[8주] 정상·실패 시연영상(MP4)</t>
+          <t>[8주] 최종 발표 PT 자료</t>
         </is>
       </c>
       <c r="D112" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E112" s="63" t="n">
-        <v>46339</v>
+        <v>46335</v>
       </c>
       <c r="F112" s="63" t="n">
         <v>46346</v>
       </c>
       <c r="G112" s="64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H112" s="65" t="n">
         <v>0</v>
@@ -9497,10 +9499,10 @@
       <c r="AJ112" s="72" t="n"/>
       <c r="AK112" s="72" t="n"/>
       <c r="AL112" s="72" t="n"/>
-      <c r="AM112" s="72" t="n"/>
-      <c r="AN112" s="72" t="n"/>
-      <c r="AO112" s="72" t="n"/>
-      <c r="AP112" s="72" t="n"/>
+      <c r="AM112" s="101" t="n"/>
+      <c r="AN112" s="101" t="n"/>
+      <c r="AO112" s="101" t="n"/>
+      <c r="AP112" s="101" t="n"/>
       <c r="AQ112" s="101" t="n"/>
       <c r="AR112" s="101" t="n"/>
       <c r="AS112" s="101" t="n"/>
@@ -9516,27 +9518,29 @@
     </row>
     <row r="113" ht="17.25" customHeight="1" s="103">
       <c r="A113" s="59" t="n"/>
-      <c r="B113" s="60" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="C113" s="61" t="inlineStr">
-        <is>
-          <t>[8주] 소스코드·실행가이드 제출</t>
+      <c r="B113" s="60" t="inlineStr">
+        <is>
+          <t>6.3.1</t>
+        </is>
+      </c>
+      <c r="C113" s="82" t="inlineStr">
+        <is>
+          <t>평가 결과·성과·한계 PT 검토·제출</t>
         </is>
       </c>
       <c r="D113" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E113" s="63" t="n">
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="F113" s="63" t="n">
-        <v>46346</v>
+        <v>46344</v>
       </c>
       <c r="G113" s="64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H113" s="65" t="n">
         <v>0</v>
@@ -9571,16 +9575,16 @@
       <c r="AJ113" s="72" t="n"/>
       <c r="AK113" s="72" t="n"/>
       <c r="AL113" s="72" t="n"/>
-      <c r="AM113" s="72" t="n"/>
-      <c r="AN113" s="72" t="n"/>
-      <c r="AO113" s="72" t="n"/>
-      <c r="AP113" s="72" t="n"/>
-      <c r="AQ113" s="72" t="n"/>
+      <c r="AM113" s="101" t="n"/>
+      <c r="AN113" s="101" t="n"/>
+      <c r="AO113" s="101" t="n"/>
+      <c r="AP113" s="101" t="n"/>
+      <c r="AQ113" s="101" t="n"/>
       <c r="AR113" s="101" t="n"/>
       <c r="AS113" s="101" t="n"/>
       <c r="AT113" s="101" t="n"/>
-      <c r="AU113" s="101" t="n"/>
-      <c r="AV113" s="102" t="n"/>
+      <c r="AU113" s="74" t="n"/>
+      <c r="AV113" s="74" t="n"/>
       <c r="AW113" s="72" t="n"/>
       <c r="AX113" s="72" t="n"/>
       <c r="AY113" s="72" t="n"/>
@@ -9590,12 +9594,14 @@
     </row>
     <row r="114" ht="17.25" customHeight="1" s="103">
       <c r="A114" s="59" t="n"/>
-      <c r="B114" s="60" t="n">
-        <v>6.6</v>
+      <c r="B114" s="60" t="inlineStr">
+        <is>
+          <t>6.3.2</t>
+        </is>
       </c>
       <c r="C114" s="82" t="inlineStr">
         <is>
-          <t>리소스·비용·API 정리(일정 제안)</t>
+          <t>최종 리허설·발표(11/20)</t>
         </is>
       </c>
       <c r="D114" s="96" t="inlineStr">
@@ -9604,13 +9610,13 @@
         </is>
       </c>
       <c r="E114" s="63" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="F114" s="63" t="n">
         <v>46346</v>
       </c>
       <c r="G114" s="64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114" s="65" t="n">
         <v>0</v>
@@ -9652,7 +9658,7 @@
       <c r="AQ114" s="72" t="n"/>
       <c r="AR114" s="74" t="n"/>
       <c r="AS114" s="74" t="n"/>
-      <c r="AT114" s="101" t="n"/>
+      <c r="AT114" s="74" t="n"/>
       <c r="AU114" s="101" t="n"/>
       <c r="AV114" s="101" t="n"/>
       <c r="AW114" s="72" t="n"/>
@@ -9662,9 +9668,228 @@
       <c r="BA114" s="72" t="n"/>
       <c r="BB114" s="75" t="n"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" s="103"/>
-    <row r="116" ht="15.75" customHeight="1" s="103"/>
-    <row r="117" ht="15.75" customHeight="1" s="103"/>
+    <row r="115" ht="15.75" customHeight="1" s="103">
+      <c r="A115" s="59" t="n"/>
+      <c r="B115" s="60" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C115" s="61" t="inlineStr">
+        <is>
+          <t>[8주] 정상·실패 시연영상(MP4)</t>
+        </is>
+      </c>
+      <c r="D115" s="96" t="inlineStr">
+        <is>
+          <t>권세진</t>
+        </is>
+      </c>
+      <c r="E115" s="63" t="n">
+        <v>46339</v>
+      </c>
+      <c r="F115" s="63" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G115" s="64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H115" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="77" t="n"/>
+      <c r="J115" s="79" t="n"/>
+      <c r="K115" s="72" t="n"/>
+      <c r="L115" s="72" t="n"/>
+      <c r="M115" s="72" t="n"/>
+      <c r="N115" s="70" t="n"/>
+      <c r="O115" s="71" t="n"/>
+      <c r="P115" s="71" t="n"/>
+      <c r="Q115" s="71" t="n"/>
+      <c r="R115" s="70" t="n"/>
+      <c r="S115" s="72" t="n"/>
+      <c r="T115" s="72" t="n"/>
+      <c r="U115" s="72" t="n"/>
+      <c r="V115" s="72" t="n"/>
+      <c r="W115" s="72" t="n"/>
+      <c r="X115" s="72" t="n"/>
+      <c r="Y115" s="72" t="n"/>
+      <c r="Z115" s="72" t="n"/>
+      <c r="AA115" s="72" t="n"/>
+      <c r="AB115" s="72" t="n"/>
+      <c r="AC115" s="73" t="n"/>
+      <c r="AD115" s="73" t="n"/>
+      <c r="AE115" s="73" t="n"/>
+      <c r="AF115" s="73" t="n"/>
+      <c r="AG115" s="73" t="n"/>
+      <c r="AH115" s="72" t="n"/>
+      <c r="AI115" s="72" t="n"/>
+      <c r="AJ115" s="72" t="n"/>
+      <c r="AK115" s="72" t="n"/>
+      <c r="AL115" s="72" t="n"/>
+      <c r="AM115" s="72" t="n"/>
+      <c r="AN115" s="72" t="n"/>
+      <c r="AO115" s="72" t="n"/>
+      <c r="AP115" s="72" t="n"/>
+      <c r="AQ115" s="101" t="n"/>
+      <c r="AR115" s="101" t="n"/>
+      <c r="AS115" s="101" t="n"/>
+      <c r="AT115" s="101" t="n"/>
+      <c r="AU115" s="101" t="n"/>
+      <c r="AV115" s="102" t="n"/>
+      <c r="AW115" s="72" t="n"/>
+      <c r="AX115" s="72" t="n"/>
+      <c r="AY115" s="72" t="n"/>
+      <c r="AZ115" s="72" t="n"/>
+      <c r="BA115" s="72" t="n"/>
+      <c r="BB115" s="75" t="n"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1" s="103">
+      <c r="A116" s="59" t="n"/>
+      <c r="B116" s="60" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C116" s="61" t="inlineStr">
+        <is>
+          <t>[8주] 소스코드·실행가이드 제출</t>
+        </is>
+      </c>
+      <c r="D116" s="96" t="inlineStr">
+        <is>
+          <t>김혜리</t>
+        </is>
+      </c>
+      <c r="E116" s="63" t="n">
+        <v>46342</v>
+      </c>
+      <c r="F116" s="63" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G116" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H116" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="77" t="n"/>
+      <c r="J116" s="79" t="n"/>
+      <c r="K116" s="72" t="n"/>
+      <c r="L116" s="72" t="n"/>
+      <c r="M116" s="72" t="n"/>
+      <c r="N116" s="70" t="n"/>
+      <c r="O116" s="71" t="n"/>
+      <c r="P116" s="71" t="n"/>
+      <c r="Q116" s="71" t="n"/>
+      <c r="R116" s="70" t="n"/>
+      <c r="S116" s="72" t="n"/>
+      <c r="T116" s="72" t="n"/>
+      <c r="U116" s="72" t="n"/>
+      <c r="V116" s="72" t="n"/>
+      <c r="W116" s="72" t="n"/>
+      <c r="X116" s="72" t="n"/>
+      <c r="Y116" s="72" t="n"/>
+      <c r="Z116" s="72" t="n"/>
+      <c r="AA116" s="72" t="n"/>
+      <c r="AB116" s="72" t="n"/>
+      <c r="AC116" s="73" t="n"/>
+      <c r="AD116" s="73" t="n"/>
+      <c r="AE116" s="73" t="n"/>
+      <c r="AF116" s="73" t="n"/>
+      <c r="AG116" s="73" t="n"/>
+      <c r="AH116" s="72" t="n"/>
+      <c r="AI116" s="72" t="n"/>
+      <c r="AJ116" s="72" t="n"/>
+      <c r="AK116" s="72" t="n"/>
+      <c r="AL116" s="72" t="n"/>
+      <c r="AM116" s="72" t="n"/>
+      <c r="AN116" s="72" t="n"/>
+      <c r="AO116" s="72" t="n"/>
+      <c r="AP116" s="72" t="n"/>
+      <c r="AQ116" s="72" t="n"/>
+      <c r="AR116" s="101" t="n"/>
+      <c r="AS116" s="101" t="n"/>
+      <c r="AT116" s="101" t="n"/>
+      <c r="AU116" s="101" t="n"/>
+      <c r="AV116" s="102" t="n"/>
+      <c r="AW116" s="72" t="n"/>
+      <c r="AX116" s="72" t="n"/>
+      <c r="AY116" s="72" t="n"/>
+      <c r="AZ116" s="72" t="n"/>
+      <c r="BA116" s="72" t="n"/>
+      <c r="BB116" s="75" t="n"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1" s="103">
+      <c r="A117" s="59" t="n"/>
+      <c r="B117" s="60" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C117" s="82" t="inlineStr">
+        <is>
+          <t>리소스·비용·API 정리(일정 제안)</t>
+        </is>
+      </c>
+      <c r="D117" s="96" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+      <c r="E117" s="63" t="n">
+        <v>46344</v>
+      </c>
+      <c r="F117" s="63" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G117" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H117" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="77" t="n"/>
+      <c r="J117" s="79" t="n"/>
+      <c r="K117" s="72" t="n"/>
+      <c r="L117" s="72" t="n"/>
+      <c r="M117" s="72" t="n"/>
+      <c r="N117" s="70" t="n"/>
+      <c r="O117" s="71" t="n"/>
+      <c r="P117" s="71" t="n"/>
+      <c r="Q117" s="71" t="n"/>
+      <c r="R117" s="70" t="n"/>
+      <c r="S117" s="72" t="n"/>
+      <c r="T117" s="72" t="n"/>
+      <c r="U117" s="72" t="n"/>
+      <c r="V117" s="72" t="n"/>
+      <c r="W117" s="72" t="n"/>
+      <c r="X117" s="72" t="n"/>
+      <c r="Y117" s="72" t="n"/>
+      <c r="Z117" s="72" t="n"/>
+      <c r="AA117" s="72" t="n"/>
+      <c r="AB117" s="72" t="n"/>
+      <c r="AC117" s="73" t="n"/>
+      <c r="AD117" s="73" t="n"/>
+      <c r="AE117" s="73" t="n"/>
+      <c r="AF117" s="73" t="n"/>
+      <c r="AG117" s="73" t="n"/>
+      <c r="AH117" s="72" t="n"/>
+      <c r="AI117" s="72" t="n"/>
+      <c r="AJ117" s="72" t="n"/>
+      <c r="AK117" s="72" t="n"/>
+      <c r="AL117" s="72" t="n"/>
+      <c r="AM117" s="72" t="n"/>
+      <c r="AN117" s="72" t="n"/>
+      <c r="AO117" s="72" t="n"/>
+      <c r="AP117" s="72" t="n"/>
+      <c r="AQ117" s="72" t="n"/>
+      <c r="AR117" s="74" t="n"/>
+      <c r="AS117" s="74" t="n"/>
+      <c r="AT117" s="101" t="n"/>
+      <c r="AU117" s="101" t="n"/>
+      <c r="AV117" s="101" t="n"/>
+      <c r="AW117" s="72" t="n"/>
+      <c r="AX117" s="72" t="n"/>
+      <c r="AY117" s="72" t="n"/>
+      <c r="AZ117" s="72" t="n"/>
+      <c r="BA117" s="72" t="n"/>
+      <c r="BB117" s="75" t="n"/>
+    </row>
     <row r="118" ht="15.75" customHeight="1" s="103"/>
     <row r="119" ht="15.75" customHeight="1" s="103"/>
     <row r="120" ht="15.75" customHeight="1" s="103"/>
@@ -10582,7 +10807,7 @@
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H12:H114">
+  <conditionalFormatting sqref="H12:H117">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10593,7 +10818,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D12:D114" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D12:D117" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"-,김혜리,김나은,권세진,전원,신진호,김유진"</formula1>
     </dataValidation>
   </dataValidations>

--- a/산출물/01_기획/4팀_WBS.xlsx
+++ b/산출물/01_기획/4팀_WBS.xlsx
@@ -8093,7 +8093,7 @@
       </c>
       <c r="C94" s="82" t="inlineStr">
         <is>
-          <t>(1차) React 초기 설정·공통 컴포넌트·배포</t>
+          <t>(1차) Django 화면 초기 설정·공통 템플릿·배포</t>
         </is>
       </c>
       <c r="D94" s="96" t="inlineStr">

--- a/산출물/01_기획/4팀_WBS.xlsx
+++ b/산출물/01_기획/4팀_WBS.xlsx
@@ -8093,7 +8093,7 @@
       </c>
       <c r="C94" s="82" t="inlineStr">
         <is>
-          <t>(1차) Django 화면 초기 설정·공통 템플릿·배포</t>
+          <t>(1차) React 화면 · Django API 초기 설정·공통 컴포넌트·배포</t>
         </is>
       </c>
       <c r="D94" s="96" t="inlineStr">

--- a/산출물/01_기획/4팀_WBS.xlsx
+++ b/산출물/01_기획/4팀_WBS.xlsx
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C66" s="82" t="inlineStr">
         <is>
-          <t>라우터 진입점→에이전트·조정 모드 매핑 상세화</t>
+          <t xml:space="preserve">라우터 매핑·의도 목록·요청 정보 형식 정의</t>
         </is>
       </c>
       <c r="D66" s="96" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="C71" s="82" t="inlineStr">
         <is>
-          <t>(1차) 라우터·통합 챗봇 선택지·전환</t>
+          <t xml:space="preserve">(1차) LLM 라우터·통합 챗봇 입력창·선택지·전환</t>
         </is>
       </c>
       <c r="D71" s="96" t="inlineStr">

--- a/산출물/01_기획/4팀_WBS.xlsx
+++ b/산출물/01_기획/4팀_WBS.xlsx
@@ -200,7 +200,7 @@
       <color rgb="FF434343"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -375,6 +375,11 @@
         <bgColor rgb="FFEAD1DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border/>
@@ -470,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -769,6 +774,9 @@
     <xf numFmtId="3" fontId="27" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1325,7 +1333,7 @@
       <c r="N5" s="105" t="n"/>
       <c r="O5" s="105" t="n"/>
       <c r="P5" s="26" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="Q5" s="105" t="n"/>
       <c r="R5" s="105" t="n"/>
@@ -1867,7 +1875,7 @@
         <v>13</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="54" t="n"/>
       <c r="J11" s="55" t="n"/>
@@ -3447,7 +3455,7 @@
         <v>18</v>
       </c>
       <c r="H32" s="53" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I32" s="58" t="n"/>
       <c r="J32" s="84" t="n"/>
@@ -3893,13 +3901,13 @@
         <v>46301</v>
       </c>
       <c r="F38" s="63" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="G38" s="64" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H38" s="65" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I38" s="77" t="n"/>
       <c r="J38" s="79" t="n"/>
@@ -3915,12 +3923,12 @@
       <c r="T38" s="88" t="n"/>
       <c r="U38" s="88" t="n"/>
       <c r="V38" s="88" t="n"/>
-      <c r="W38" s="89" t="n"/>
-      <c r="X38" s="72" t="n"/>
-      <c r="Y38" s="72" t="n"/>
-      <c r="Z38" s="72" t="n"/>
-      <c r="AA38" s="72" t="n"/>
-      <c r="AB38" s="72" t="n"/>
+      <c r="W38" s="114" t="n"/>
+      <c r="X38" s="114" t="n"/>
+      <c r="Y38" s="114" t="n"/>
+      <c r="Z38" s="114" t="n"/>
+      <c r="AA38" s="114" t="n"/>
+      <c r="AB38" s="89" t="n"/>
       <c r="AC38" s="73" t="n"/>
       <c r="AD38" s="73" t="n"/>
       <c r="AE38" s="73" t="n"/>
@@ -4051,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="77" t="n"/>
       <c r="J40" s="79" t="n"/>
@@ -4203,7 +4211,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="77" t="n"/>
       <c r="J42" s="79" t="n"/>
@@ -4254,12 +4262,14 @@
     </row>
     <row r="43" outlineLevel="1" ht="17.25" customHeight="1" s="103">
       <c r="A43" s="59" t="n"/>
-      <c r="B43" s="60" t="n">
-        <v>2.3</v>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t>2.2.5</t>
+        </is>
       </c>
       <c r="C43" s="82" t="inlineStr">
         <is>
-          <t>v5 추가 데이터 확보·검증 과제</t>
+          <t>화면 API 명세 작성·합의(주소·요청·응답)</t>
         </is>
       </c>
       <c r="D43" s="96" t="inlineStr">
@@ -4268,13 +4278,13 @@
         </is>
       </c>
       <c r="E43" s="63" t="n">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="F43" s="63" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="G43" s="64" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H43" s="65" t="n">
         <v>0</v>
@@ -4289,19 +4299,19 @@
       <c r="P43" s="71" t="n"/>
       <c r="Q43" s="71" t="n"/>
       <c r="R43" s="70" t="n"/>
-      <c r="S43" s="88" t="n"/>
-      <c r="T43" s="88" t="n"/>
-      <c r="U43" s="88" t="n"/>
-      <c r="V43" s="88" t="n"/>
-      <c r="W43" s="88" t="n"/>
-      <c r="X43" s="88" t="n"/>
-      <c r="Y43" s="88" t="n"/>
-      <c r="Z43" s="88" t="n"/>
-      <c r="AA43" s="88" t="n"/>
-      <c r="AB43" s="88" t="n"/>
-      <c r="AC43" s="88" t="n"/>
-      <c r="AD43" s="88" t="n"/>
-      <c r="AE43" s="88" t="n"/>
+      <c r="S43" s="72" t="n"/>
+      <c r="T43" s="72" t="n"/>
+      <c r="U43" s="72" t="n"/>
+      <c r="V43" s="72" t="n"/>
+      <c r="W43" s="72" t="n"/>
+      <c r="X43" s="72" t="n"/>
+      <c r="Y43" s="72" t="n"/>
+      <c r="Z43" s="114" t="n"/>
+      <c r="AA43" s="114" t="n"/>
+      <c r="AB43" s="114" t="n"/>
+      <c r="AC43" s="73" t="n"/>
+      <c r="AD43" s="73" t="n"/>
+      <c r="AE43" s="73" t="n"/>
       <c r="AF43" s="73" t="n"/>
       <c r="AG43" s="73" t="n"/>
       <c r="AH43" s="72" t="n"/>
@@ -4328,29 +4338,27 @@
     </row>
     <row r="44" outlineLevel="1" ht="17.25" customHeight="1" s="103">
       <c r="A44" s="59" t="n"/>
-      <c r="B44" s="60" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
+      <c r="B44" s="60" t="n">
+        <v>2.3</v>
       </c>
       <c r="C44" s="82" t="inlineStr">
         <is>
-          <t>MDIS·KOSIS 가계동향 확보·변수 결합 확인</t>
+          <t>v5 추가 데이터 확보·검증 과제</t>
         </is>
       </c>
       <c r="D44" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E44" s="63" t="n">
         <v>46307</v>
       </c>
       <c r="F44" s="63" t="n">
-        <v>46310</v>
+        <v>46323</v>
       </c>
       <c r="G44" s="64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H44" s="65" t="n">
         <v>0</v>
@@ -4369,15 +4377,15 @@
       <c r="T44" s="88" t="n"/>
       <c r="U44" s="88" t="n"/>
       <c r="V44" s="88" t="n"/>
-      <c r="W44" s="72" t="n"/>
-      <c r="X44" s="72" t="n"/>
-      <c r="Y44" s="72" t="n"/>
-      <c r="Z44" s="72" t="n"/>
-      <c r="AA44" s="72" t="n"/>
-      <c r="AB44" s="72" t="n"/>
-      <c r="AC44" s="73" t="n"/>
-      <c r="AD44" s="73" t="n"/>
-      <c r="AE44" s="73" t="n"/>
+      <c r="W44" s="88" t="n"/>
+      <c r="X44" s="88" t="n"/>
+      <c r="Y44" s="88" t="n"/>
+      <c r="Z44" s="88" t="n"/>
+      <c r="AA44" s="88" t="n"/>
+      <c r="AB44" s="88" t="n"/>
+      <c r="AC44" s="88" t="n"/>
+      <c r="AD44" s="88" t="n"/>
+      <c r="AE44" s="88" t="n"/>
       <c r="AF44" s="73" t="n"/>
       <c r="AG44" s="73" t="n"/>
       <c r="AH44" s="72" t="n"/>
@@ -4406,27 +4414,27 @@
       <c r="A45" s="59" t="n"/>
       <c r="B45" s="60" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C45" s="82" t="inlineStr">
         <is>
-          <t>CODEF 대출 조회 항목·기관 범위 연동 테스트</t>
+          <t>MDIS·KOSIS 가계동향 확보·변수 결합 확인</t>
         </is>
       </c>
       <c r="D45" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E45" s="63" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="F45" s="63" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="G45" s="64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45" s="65" t="n">
         <v>0</v>
@@ -4441,11 +4449,11 @@
       <c r="P45" s="71" t="n"/>
       <c r="Q45" s="71" t="n"/>
       <c r="R45" s="70" t="n"/>
-      <c r="S45" s="72" t="n"/>
-      <c r="T45" s="72" t="n"/>
+      <c r="S45" s="88" t="n"/>
+      <c r="T45" s="88" t="n"/>
       <c r="U45" s="88" t="n"/>
       <c r="V45" s="88" t="n"/>
-      <c r="W45" s="88" t="n"/>
+      <c r="W45" s="72" t="n"/>
       <c r="X45" s="72" t="n"/>
       <c r="Y45" s="72" t="n"/>
       <c r="Z45" s="72" t="n"/>
@@ -4482,17 +4490,17 @@
       <c r="A46" s="59" t="n"/>
       <c r="B46" s="60" t="inlineStr">
         <is>
-          <t>2.3.3</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C46" s="82" t="inlineStr">
         <is>
-          <t>(3차) 복지 API·대출 상품 데이터 범위 확인</t>
+          <t>CODEF 대출 조회 항목·기관 범위 연동 테스트</t>
         </is>
       </c>
       <c r="D46" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E46" s="63" t="n">
@@ -4554,28 +4562,28 @@
       <c r="BA46" s="72" t="n"/>
       <c r="BB46" s="75" t="n"/>
     </row>
-    <row r="47" ht="21" customHeight="1" s="103">
+    <row r="47" ht="17.25" customHeight="1" s="103">
       <c r="A47" s="59" t="n"/>
       <c r="B47" s="60" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.3</t>
         </is>
       </c>
       <c r="C47" s="82" t="inlineStr">
         <is>
-          <t>(검증) 카드 OCR·BIN 식별 지원 범위 검증</t>
+          <t>(3차) 복지 API·대출 상품 데이터 범위 확인</t>
         </is>
       </c>
       <c r="D47" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E47" s="63" t="n">
-        <v>46321</v>
+        <v>46309</v>
       </c>
       <c r="F47" s="63" t="n">
-        <v>46323</v>
+        <v>46311</v>
       </c>
       <c r="G47" s="64" t="n">
         <v>3</v>
@@ -4595,17 +4603,17 @@
       <c r="R47" s="70" t="n"/>
       <c r="S47" s="72" t="n"/>
       <c r="T47" s="72" t="n"/>
-      <c r="U47" s="72" t="n"/>
-      <c r="V47" s="72" t="n"/>
-      <c r="W47" s="72" t="n"/>
+      <c r="U47" s="88" t="n"/>
+      <c r="V47" s="88" t="n"/>
+      <c r="W47" s="88" t="n"/>
       <c r="X47" s="72" t="n"/>
       <c r="Y47" s="72" t="n"/>
       <c r="Z47" s="72" t="n"/>
       <c r="AA47" s="72" t="n"/>
       <c r="AB47" s="72" t="n"/>
-      <c r="AC47" s="88" t="n"/>
-      <c r="AD47" s="88" t="n"/>
-      <c r="AE47" s="88" t="n"/>
+      <c r="AC47" s="73" t="n"/>
+      <c r="AD47" s="73" t="n"/>
+      <c r="AE47" s="73" t="n"/>
       <c r="AF47" s="73" t="n"/>
       <c r="AG47" s="73" t="n"/>
       <c r="AH47" s="72" t="n"/>
@@ -4630,175 +4638,175 @@
       <c r="BA47" s="72" t="n"/>
       <c r="BB47" s="75" t="n"/>
     </row>
-    <row r="48" ht="17.25" customHeight="1" s="103">
-      <c r="A48" s="47" t="n"/>
-      <c r="B48" s="48" t="n">
+    <row r="48" ht="21" customHeight="1" s="103">
+      <c r="A48" s="59" t="n"/>
+      <c r="B48" s="60" t="inlineStr">
+        <is>
+          <t>2.3.4</t>
+        </is>
+      </c>
+      <c r="C48" s="82" t="inlineStr">
+        <is>
+          <t>(검증) 카드 OCR·BIN 식별 지원 범위 검증</t>
+        </is>
+      </c>
+      <c r="D48" s="96" t="inlineStr">
+        <is>
+          <t>김혜리</t>
+        </is>
+      </c>
+      <c r="E48" s="63" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F48" s="63" t="n">
+        <v>46323</v>
+      </c>
+      <c r="G48" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="49" t="inlineStr">
+      <c r="H48" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="77" t="n"/>
+      <c r="J48" s="79" t="n"/>
+      <c r="K48" s="72" t="n"/>
+      <c r="L48" s="72" t="n"/>
+      <c r="M48" s="72" t="n"/>
+      <c r="N48" s="70" t="n"/>
+      <c r="O48" s="71" t="n"/>
+      <c r="P48" s="71" t="n"/>
+      <c r="Q48" s="71" t="n"/>
+      <c r="R48" s="70" t="n"/>
+      <c r="S48" s="72" t="n"/>
+      <c r="T48" s="72" t="n"/>
+      <c r="U48" s="72" t="n"/>
+      <c r="V48" s="72" t="n"/>
+      <c r="W48" s="72" t="n"/>
+      <c r="X48" s="72" t="n"/>
+      <c r="Y48" s="72" t="n"/>
+      <c r="Z48" s="72" t="n"/>
+      <c r="AA48" s="72" t="n"/>
+      <c r="AB48" s="72" t="n"/>
+      <c r="AC48" s="88" t="n"/>
+      <c r="AD48" s="88" t="n"/>
+      <c r="AE48" s="88" t="n"/>
+      <c r="AF48" s="73" t="n"/>
+      <c r="AG48" s="73" t="n"/>
+      <c r="AH48" s="72" t="n"/>
+      <c r="AI48" s="72" t="n"/>
+      <c r="AJ48" s="72" t="n"/>
+      <c r="AK48" s="72" t="n"/>
+      <c r="AL48" s="72" t="n"/>
+      <c r="AM48" s="72" t="n"/>
+      <c r="AN48" s="72" t="n"/>
+      <c r="AO48" s="72" t="n"/>
+      <c r="AP48" s="72" t="n"/>
+      <c r="AQ48" s="72" t="n"/>
+      <c r="AR48" s="74" t="n"/>
+      <c r="AS48" s="74" t="n"/>
+      <c r="AT48" s="74" t="n"/>
+      <c r="AU48" s="74" t="n"/>
+      <c r="AV48" s="74" t="n"/>
+      <c r="AW48" s="72" t="n"/>
+      <c r="AX48" s="72" t="n"/>
+      <c r="AY48" s="72" t="n"/>
+      <c r="AZ48" s="72" t="n"/>
+      <c r="BA48" s="72" t="n"/>
+      <c r="BB48" s="75" t="n"/>
+    </row>
+    <row r="49" ht="17.25" customHeight="1" s="103">
+      <c r="A49" s="47" t="n"/>
+      <c r="B49" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="49" t="inlineStr">
         <is>
           <t>데이터 전처리</t>
         </is>
       </c>
-      <c r="D48" s="50" t="n"/>
-      <c r="E48" s="51" t="n">
+      <c r="D49" s="50" t="n"/>
+      <c r="E49" s="51" t="n">
         <v>46307</v>
       </c>
-      <c r="F48" s="51" t="n">
+      <c r="F49" s="51" t="n">
         <v>46318</v>
       </c>
-      <c r="G48" s="52" t="n">
+      <c r="G49" s="52" t="n">
         <v>10</v>
       </c>
-      <c r="H48" s="53" t="n">
+      <c r="H49" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="58" t="n"/>
-      <c r="J48" s="84" t="n"/>
-      <c r="K48" s="111" t="n"/>
-      <c r="L48" s="111" t="n"/>
-      <c r="M48" s="58" t="n"/>
-      <c r="N48" s="57" t="n"/>
-      <c r="O48" s="58" t="n"/>
-      <c r="P48" s="58" t="n"/>
-      <c r="Q48" s="58" t="n"/>
-      <c r="R48" s="57" t="n"/>
-      <c r="S48" s="90" t="n"/>
-      <c r="T48" s="90" t="n"/>
-      <c r="U48" s="90" t="n"/>
-      <c r="V48" s="90" t="n"/>
-      <c r="W48" s="90" t="n"/>
-      <c r="X48" s="90" t="n"/>
-      <c r="Y48" s="90" t="n"/>
-      <c r="Z48" s="90" t="n"/>
-      <c r="AA48" s="90" t="n"/>
-      <c r="AB48" s="90" t="n"/>
-      <c r="AC48" s="58" t="n"/>
-      <c r="AD48" s="58" t="n"/>
-      <c r="AE48" s="58" t="n"/>
-      <c r="AF48" s="58" t="n"/>
-      <c r="AG48" s="58" t="n"/>
-      <c r="AH48" s="58" t="n"/>
-      <c r="AI48" s="58" t="n"/>
-      <c r="AJ48" s="58" t="n"/>
-      <c r="AK48" s="58" t="n"/>
-      <c r="AL48" s="58" t="n"/>
-      <c r="AM48" s="58" t="n"/>
-      <c r="AN48" s="58" t="n"/>
-      <c r="AO48" s="58" t="n"/>
-      <c r="AP48" s="58" t="n"/>
-      <c r="AQ48" s="58" t="n"/>
-      <c r="AR48" s="58" t="n"/>
-      <c r="AS48" s="58" t="n"/>
-      <c r="AT48" s="58" t="n"/>
-      <c r="AU48" s="58" t="n"/>
-      <c r="AV48" s="58" t="n"/>
-      <c r="AW48" s="58" t="n"/>
-      <c r="AX48" s="58" t="n"/>
-      <c r="AY48" s="58" t="n"/>
-      <c r="AZ48" s="58" t="n"/>
-      <c r="BA48" s="58" t="n"/>
-      <c r="BB48" s="29" t="n"/>
-    </row>
-    <row r="49" ht="17.25" customHeight="1" s="103">
-      <c r="A49" s="59" t="n"/>
-      <c r="B49" s="60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C49" s="61" t="inlineStr">
-        <is>
-          <t>[3주] 데이터 전처리 결과서</t>
-        </is>
-      </c>
-      <c r="D49" s="96" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="E49" s="63" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F49" s="63" t="n">
-        <v>46311</v>
-      </c>
-      <c r="G49" s="64" t="n">
-        <v>5</v>
-      </c>
-      <c r="H49" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="77" t="n"/>
-      <c r="J49" s="79" t="n"/>
-      <c r="K49" s="72" t="n"/>
-      <c r="L49" s="72" t="n"/>
-      <c r="M49" s="72" t="n"/>
-      <c r="N49" s="70" t="n"/>
-      <c r="O49" s="71" t="n"/>
-      <c r="P49" s="71" t="n"/>
-      <c r="Q49" s="71" t="n"/>
-      <c r="R49" s="70" t="n"/>
-      <c r="S49" s="91" t="n"/>
-      <c r="T49" s="91" t="n"/>
-      <c r="U49" s="91" t="n"/>
-      <c r="V49" s="91" t="n"/>
-      <c r="W49" s="92" t="n"/>
-      <c r="X49" s="72" t="n"/>
-      <c r="Y49" s="72" t="n"/>
-      <c r="Z49" s="72" t="n"/>
-      <c r="AA49" s="72" t="n"/>
-      <c r="AB49" s="72" t="n"/>
-      <c r="AC49" s="73" t="n"/>
-      <c r="AD49" s="73" t="n"/>
-      <c r="AE49" s="73" t="n"/>
-      <c r="AF49" s="73" t="n"/>
-      <c r="AG49" s="73" t="n"/>
-      <c r="AH49" s="72" t="n"/>
-      <c r="AI49" s="72" t="n"/>
-      <c r="AJ49" s="72" t="n"/>
-      <c r="AK49" s="72" t="n"/>
-      <c r="AL49" s="72" t="n"/>
-      <c r="AM49" s="72" t="n"/>
-      <c r="AN49" s="72" t="n"/>
-      <c r="AO49" s="72" t="n"/>
-      <c r="AP49" s="72" t="n"/>
-      <c r="AQ49" s="72" t="n"/>
-      <c r="AR49" s="74" t="n"/>
-      <c r="AS49" s="74" t="n"/>
-      <c r="AT49" s="74" t="n"/>
-      <c r="AU49" s="74" t="n"/>
-      <c r="AV49" s="74" t="n"/>
-      <c r="AW49" s="72" t="n"/>
-      <c r="AX49" s="72" t="n"/>
-      <c r="AY49" s="72" t="n"/>
-      <c r="AZ49" s="72" t="n"/>
-      <c r="BA49" s="72" t="n"/>
-      <c r="BB49" s="75" t="n"/>
+      <c r="I49" s="58" t="n"/>
+      <c r="J49" s="84" t="n"/>
+      <c r="K49" s="111" t="n"/>
+      <c r="L49" s="111" t="n"/>
+      <c r="M49" s="58" t="n"/>
+      <c r="N49" s="57" t="n"/>
+      <c r="O49" s="58" t="n"/>
+      <c r="P49" s="58" t="n"/>
+      <c r="Q49" s="58" t="n"/>
+      <c r="R49" s="57" t="n"/>
+      <c r="S49" s="90" t="n"/>
+      <c r="T49" s="90" t="n"/>
+      <c r="U49" s="90" t="n"/>
+      <c r="V49" s="90" t="n"/>
+      <c r="W49" s="90" t="n"/>
+      <c r="X49" s="90" t="n"/>
+      <c r="Y49" s="90" t="n"/>
+      <c r="Z49" s="90" t="n"/>
+      <c r="AA49" s="90" t="n"/>
+      <c r="AB49" s="90" t="n"/>
+      <c r="AC49" s="58" t="n"/>
+      <c r="AD49" s="58" t="n"/>
+      <c r="AE49" s="58" t="n"/>
+      <c r="AF49" s="58" t="n"/>
+      <c r="AG49" s="58" t="n"/>
+      <c r="AH49" s="58" t="n"/>
+      <c r="AI49" s="58" t="n"/>
+      <c r="AJ49" s="58" t="n"/>
+      <c r="AK49" s="58" t="n"/>
+      <c r="AL49" s="58" t="n"/>
+      <c r="AM49" s="58" t="n"/>
+      <c r="AN49" s="58" t="n"/>
+      <c r="AO49" s="58" t="n"/>
+      <c r="AP49" s="58" t="n"/>
+      <c r="AQ49" s="58" t="n"/>
+      <c r="AR49" s="58" t="n"/>
+      <c r="AS49" s="58" t="n"/>
+      <c r="AT49" s="58" t="n"/>
+      <c r="AU49" s="58" t="n"/>
+      <c r="AV49" s="58" t="n"/>
+      <c r="AW49" s="58" t="n"/>
+      <c r="AX49" s="58" t="n"/>
+      <c r="AY49" s="58" t="n"/>
+      <c r="AZ49" s="58" t="n"/>
+      <c r="BA49" s="58" t="n"/>
+      <c r="BB49" s="29" t="n"/>
     </row>
     <row r="50" ht="17.25" customHeight="1" s="103">
       <c r="A50" s="59" t="n"/>
-      <c r="B50" s="60" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="C50" s="82" t="inlineStr">
-        <is>
-          <t>거래 정제·상가정보 업종→카테고리 매핑</t>
+      <c r="B50" s="60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C50" s="61" t="inlineStr">
+        <is>
+          <t>[3주] 데이터 전처리 결과서</t>
         </is>
       </c>
       <c r="D50" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E50" s="63" t="n">
         <v>46307</v>
       </c>
       <c r="F50" s="63" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="G50" s="64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" s="65" t="n">
         <v>0</v>
@@ -4817,7 +4825,7 @@
       <c r="T50" s="91" t="n"/>
       <c r="U50" s="91" t="n"/>
       <c r="V50" s="91" t="n"/>
-      <c r="W50" s="72" t="n"/>
+      <c r="W50" s="92" t="n"/>
       <c r="X50" s="72" t="n"/>
       <c r="Y50" s="72" t="n"/>
       <c r="Z50" s="72" t="n"/>
@@ -4854,17 +4862,17 @@
       <c r="A51" s="59" t="n"/>
       <c r="B51" s="60" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="C51" s="82" t="inlineStr">
         <is>
-          <t>가계동향 카테고리·가구 범위·단위 정리</t>
+          <t>거래 정제·상가정보 업종→카테고리 매핑</t>
         </is>
       </c>
       <c r="D51" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E51" s="63" t="n">
@@ -4930,27 +4938,27 @@
       <c r="A52" s="59" t="n"/>
       <c r="B52" s="60" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="C52" s="82" t="inlineStr">
         <is>
-          <t>가맹점·사용자·시간 단위 분할·누수 검증</t>
+          <t>가계동향 카테고리·가구 범위·단위 정리</t>
         </is>
       </c>
       <c r="D52" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E52" s="63" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F52" s="63" t="n">
         <v>46310</v>
       </c>
       <c r="G52" s="64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H52" s="65" t="n">
         <v>0</v>
@@ -4965,7 +4973,7 @@
       <c r="P52" s="71" t="n"/>
       <c r="Q52" s="71" t="n"/>
       <c r="R52" s="70" t="n"/>
-      <c r="S52" s="72" t="n"/>
+      <c r="S52" s="91" t="n"/>
       <c r="T52" s="91" t="n"/>
       <c r="U52" s="91" t="n"/>
       <c r="V52" s="91" t="n"/>
@@ -5006,27 +5014,27 @@
       <c r="A53" s="59" t="n"/>
       <c r="B53" s="60" t="inlineStr">
         <is>
-          <t>3.1.4</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="C53" s="82" t="inlineStr">
         <is>
-          <t>전처리 결과서 작성·검토·제출</t>
+          <t>가맹점·사용자·시간 단위 분할·누수 검증</t>
         </is>
       </c>
       <c r="D53" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E53" s="63" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F53" s="63" t="n">
         <v>46310</v>
       </c>
-      <c r="F53" s="63" t="n">
-        <v>46311</v>
-      </c>
       <c r="G53" s="64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" s="65" t="n">
         <v>0</v>
@@ -5042,10 +5050,10 @@
       <c r="Q53" s="71" t="n"/>
       <c r="R53" s="70" t="n"/>
       <c r="S53" s="72" t="n"/>
-      <c r="T53" s="72" t="n"/>
-      <c r="U53" s="72" t="n"/>
+      <c r="T53" s="91" t="n"/>
+      <c r="U53" s="91" t="n"/>
       <c r="V53" s="91" t="n"/>
-      <c r="W53" s="91" t="n"/>
+      <c r="W53" s="72" t="n"/>
       <c r="X53" s="72" t="n"/>
       <c r="Y53" s="72" t="n"/>
       <c r="Z53" s="72" t="n"/>
@@ -5080,12 +5088,14 @@
     </row>
     <row r="54" ht="17.25" customHeight="1" s="103">
       <c r="A54" s="59" t="n"/>
-      <c r="B54" s="60" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C54" s="61" t="inlineStr">
-        <is>
-          <t>[4주] ML/DL 학습결과서</t>
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t>3.1.4</t>
+        </is>
+      </c>
+      <c r="C54" s="82" t="inlineStr">
+        <is>
+          <t>전처리 결과서 작성·검토·제출</t>
         </is>
       </c>
       <c r="D54" s="96" t="inlineStr">
@@ -5097,10 +5107,10 @@
         <v>46310</v>
       </c>
       <c r="F54" s="63" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="G54" s="64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H54" s="65" t="n">
         <v>0</v>
@@ -5120,11 +5130,11 @@
       <c r="U54" s="72" t="n"/>
       <c r="V54" s="91" t="n"/>
       <c r="W54" s="91" t="n"/>
-      <c r="X54" s="91" t="n"/>
-      <c r="Y54" s="91" t="n"/>
-      <c r="Z54" s="91" t="n"/>
-      <c r="AA54" s="91" t="n"/>
-      <c r="AB54" s="92" t="n"/>
+      <c r="X54" s="72" t="n"/>
+      <c r="Y54" s="72" t="n"/>
+      <c r="Z54" s="72" t="n"/>
+      <c r="AA54" s="72" t="n"/>
+      <c r="AB54" s="72" t="n"/>
       <c r="AC54" s="73" t="n"/>
       <c r="AD54" s="73" t="n"/>
       <c r="AE54" s="73" t="n"/>
@@ -5154,29 +5164,27 @@
     </row>
     <row r="55" ht="17.25" customHeight="1" s="103">
       <c r="A55" s="59" t="n"/>
-      <c r="B55" s="60" t="inlineStr">
-        <is>
-          <t>3.2.1</t>
-        </is>
-      </c>
-      <c r="C55" s="82" t="inlineStr">
-        <is>
-          <t>거래 분류: 기준선→학습·확신도 보정·기준값</t>
+      <c r="B55" s="60" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
+          <t>[4주] ML/DL 학습결과서</t>
         </is>
       </c>
       <c r="D55" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E55" s="63" t="n">
         <v>46310</v>
       </c>
       <c r="F55" s="63" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="G55" s="64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H55" s="65" t="n">
         <v>0</v>
@@ -5200,7 +5208,7 @@
       <c r="Y55" s="91" t="n"/>
       <c r="Z55" s="91" t="n"/>
       <c r="AA55" s="91" t="n"/>
-      <c r="AB55" s="72" t="n"/>
+      <c r="AB55" s="92" t="n"/>
       <c r="AC55" s="73" t="n"/>
       <c r="AD55" s="73" t="n"/>
       <c r="AE55" s="73" t="n"/>
@@ -5232,17 +5240,17 @@
       <c r="A56" s="59" t="n"/>
       <c r="B56" s="60" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C56" s="82" t="inlineStr">
         <is>
-          <t>카테고리 비율 예측: 기준선 vs 회귀(MAE)</t>
+          <t>거래 분류: 기준선→학습·확신도 보정·기준값</t>
         </is>
       </c>
       <c r="D56" s="96" t="inlineStr">
         <is>
-          <t>김나은</t>
+          <t>김혜리</t>
         </is>
       </c>
       <c r="E56" s="63" t="n">
@@ -5308,27 +5316,27 @@
       <c r="A57" s="59" t="n"/>
       <c r="B57" s="60" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C57" s="82" t="inlineStr">
         <is>
-          <t>(2차) 또래 비교 회귀: 기준선 vs 회귀(R²)</t>
+          <t>카테고리 비율 예측: 기준선 vs 회귀(MAE)</t>
         </is>
       </c>
       <c r="D57" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E57" s="63" t="n">
         <v>46310</v>
       </c>
       <c r="F57" s="63" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="G57" s="64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H57" s="65" t="n">
         <v>0</v>
@@ -5351,7 +5359,7 @@
       <c r="X57" s="91" t="n"/>
       <c r="Y57" s="91" t="n"/>
       <c r="Z57" s="91" t="n"/>
-      <c r="AA57" s="72" t="n"/>
+      <c r="AA57" s="91" t="n"/>
       <c r="AB57" s="72" t="n"/>
       <c r="AC57" s="73" t="n"/>
       <c r="AD57" s="73" t="n"/>
@@ -5384,27 +5392,27 @@
       <c r="A58" s="59" t="n"/>
       <c r="B58" s="60" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C58" s="82" t="inlineStr">
         <is>
-          <t>모델 3종 비교·학습결과서 검토·제출</t>
+          <t>(2차) 또래 비교 회귀: 기준선 vs 회귀(R²)</t>
         </is>
       </c>
       <c r="D58" s="96" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>권세진</t>
         </is>
       </c>
       <c r="E58" s="63" t="n">
-        <v>46317</v>
+        <v>46310</v>
       </c>
       <c r="F58" s="63" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="G58" s="64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H58" s="65" t="n">
         <v>0</v>
@@ -5422,13 +5430,13 @@
       <c r="S58" s="72" t="n"/>
       <c r="T58" s="72" t="n"/>
       <c r="U58" s="72" t="n"/>
-      <c r="V58" s="72" t="n"/>
-      <c r="W58" s="72" t="n"/>
-      <c r="X58" s="72" t="n"/>
-      <c r="Y58" s="72" t="n"/>
-      <c r="Z58" s="72" t="n"/>
-      <c r="AA58" s="91" t="n"/>
-      <c r="AB58" s="91" t="n"/>
+      <c r="V58" s="91" t="n"/>
+      <c r="W58" s="91" t="n"/>
+      <c r="X58" s="91" t="n"/>
+      <c r="Y58" s="91" t="n"/>
+      <c r="Z58" s="91" t="n"/>
+      <c r="AA58" s="72" t="n"/>
+      <c r="AB58" s="72" t="n"/>
       <c r="AC58" s="73" t="n"/>
       <c r="AD58" s="73" t="n"/>
       <c r="AE58" s="73" t="n"/>
@@ -5456,29 +5464,31 @@
       <c r="BA58" s="72" t="n"/>
       <c r="BB58" s="75" t="n"/>
     </row>
-    <row r="59" ht="21" customHeight="1" s="103">
+    <row r="59" ht="17.25" customHeight="1" s="103">
       <c r="A59" s="59" t="n"/>
-      <c r="B59" s="60" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C59" s="61" t="inlineStr">
-        <is>
-          <t>[4주] 모델 저장/로드·API 연계 문서</t>
+      <c r="B59" s="60" t="inlineStr">
+        <is>
+          <t>3.2.4</t>
+        </is>
+      </c>
+      <c r="C59" s="82" t="inlineStr">
+        <is>
+          <t>모델 3종 비교·학습결과서 검토·제출</t>
         </is>
       </c>
       <c r="D59" s="96" t="inlineStr">
         <is>
-          <t>김혜리</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="E59" s="63" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" s="63" t="n">
         <v>46318</v>
       </c>
       <c r="G59" s="64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="65" t="n">
         <v>0</v>
@@ -5500,9 +5510,9 @@
       <c r="W59" s="72" t="n"/>
       <c r="X59" s="72" t="n"/>
       <c r="Y59" s="72" t="n"/>
-      <c r="Z59" s="91" t="n"/>
+      <c r="Z59" s="72" t="n"/>
       <c r="AA59" s="91" t="n"/>
-      <c r="AB59" s="92" t="n"/>
+      <c r="AB59" s="91" t="n"/>
       <c r="AC59" s="73" t="n"/>
       <c r="AD59" s="73" t="n"/>
       <c r="AE59" s="73" t="n"/>
@@ -5530,160 +5540,158 @@
       <c r="BA59" s="72" t="n"/>
       <c r="BB59" s="75" t="n"/>
     </row>
-    <row r="60" ht="17.25" customHeight="1" s="103">
-      <c r="A60" s="47" t="n"/>
-      <c r="B60" s="48" t="n">
+    <row r="60" ht="21" customHeight="1" s="103">
+      <c r="A60" s="59" t="n"/>
+      <c r="B60" s="60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C60" s="61" t="inlineStr">
+        <is>
+          <t>[4주] 모델 저장/로드·API 연계 문서</t>
+        </is>
+      </c>
+      <c r="D60" s="96" t="inlineStr">
+        <is>
+          <t>김혜리</t>
+        </is>
+      </c>
+      <c r="E60" s="63" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F60" s="63" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G60" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="77" t="n"/>
+      <c r="J60" s="79" t="n"/>
+      <c r="K60" s="72" t="n"/>
+      <c r="L60" s="72" t="n"/>
+      <c r="M60" s="72" t="n"/>
+      <c r="N60" s="70" t="n"/>
+      <c r="O60" s="71" t="n"/>
+      <c r="P60" s="71" t="n"/>
+      <c r="Q60" s="71" t="n"/>
+      <c r="R60" s="70" t="n"/>
+      <c r="S60" s="72" t="n"/>
+      <c r="T60" s="72" t="n"/>
+      <c r="U60" s="72" t="n"/>
+      <c r="V60" s="72" t="n"/>
+      <c r="W60" s="72" t="n"/>
+      <c r="X60" s="72" t="n"/>
+      <c r="Y60" s="72" t="n"/>
+      <c r="Z60" s="91" t="n"/>
+      <c r="AA60" s="91" t="n"/>
+      <c r="AB60" s="92" t="n"/>
+      <c r="AC60" s="73" t="n"/>
+      <c r="AD60" s="73" t="n"/>
+      <c r="AE60" s="73" t="n"/>
+      <c r="AF60" s="73" t="n"/>
+      <c r="AG60" s="73" t="n"/>
+      <c r="AH60" s="72" t="n"/>
+      <c r="AI60" s="72" t="n"/>
+      <c r="AJ60" s="72" t="n"/>
+      <c r="AK60" s="72" t="n"/>
+      <c r="AL60" s="72" t="n"/>
+      <c r="AM60" s="72" t="n"/>
+      <c r="AN60" s="72" t="n"/>
+      <c r="AO60" s="72" t="n"/>
+      <c r="AP60" s="72" t="n"/>
+      <c r="AQ60" s="72" t="n"/>
+      <c r="AR60" s="74" t="n"/>
+      <c r="AS60" s="74" t="n"/>
+      <c r="AT60" s="74" t="n"/>
+      <c r="AU60" s="74" t="n"/>
+      <c r="AV60" s="74" t="n"/>
+      <c r="AW60" s="72" t="n"/>
+      <c r="AX60" s="72" t="n"/>
+      <c r="AY60" s="72" t="n"/>
+      <c r="AZ60" s="72" t="n"/>
+      <c r="BA60" s="72" t="n"/>
+      <c r="BB60" s="75" t="n"/>
+    </row>
+    <row r="61" ht="17.25" customHeight="1" s="103">
+      <c r="A61" s="47" t="n"/>
+      <c r="B61" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="C60" s="49" t="inlineStr">
+      <c r="C61" s="49" t="inlineStr">
         <is>
           <t>모델링 및 평가</t>
         </is>
       </c>
-      <c r="D60" s="50" t="n"/>
-      <c r="E60" s="51" t="n">
+      <c r="D61" s="50" t="n"/>
+      <c r="E61" s="51" t="n">
         <v>46310</v>
       </c>
-      <c r="F60" s="51" t="n">
+      <c r="F61" s="51" t="n">
         <v>46339</v>
       </c>
-      <c r="G60" s="52" t="n">
+      <c r="G61" s="52" t="n">
         <v>22</v>
       </c>
-      <c r="H60" s="53" t="n">
+      <c r="H61" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="58" t="n"/>
-      <c r="J60" s="84" t="n"/>
-      <c r="K60" s="111" t="n"/>
-      <c r="L60" s="111" t="n"/>
-      <c r="M60" s="58" t="n"/>
-      <c r="N60" s="57" t="n"/>
-      <c r="O60" s="58" t="n"/>
-      <c r="P60" s="58" t="n"/>
-      <c r="Q60" s="58" t="n"/>
-      <c r="R60" s="57" t="n"/>
-      <c r="S60" s="58" t="n"/>
-      <c r="T60" s="58" t="n"/>
-      <c r="U60" s="58" t="n"/>
-      <c r="V60" s="93" t="n"/>
-      <c r="W60" s="93" t="n"/>
-      <c r="X60" s="93" t="n"/>
-      <c r="Y60" s="93" t="n"/>
-      <c r="Z60" s="93" t="n"/>
-      <c r="AA60" s="93" t="n"/>
-      <c r="AB60" s="93" t="n"/>
-      <c r="AC60" s="93" t="n"/>
-      <c r="AD60" s="93" t="n"/>
-      <c r="AE60" s="93" t="n"/>
-      <c r="AF60" s="93" t="n"/>
-      <c r="AG60" s="93" t="n"/>
-      <c r="AH60" s="93" t="n"/>
-      <c r="AI60" s="93" t="n"/>
-      <c r="AJ60" s="93" t="n"/>
-      <c r="AK60" s="93" t="n"/>
-      <c r="AL60" s="93" t="n"/>
-      <c r="AM60" s="93" t="n"/>
-      <c r="AN60" s="93" t="n"/>
-      <c r="AO60" s="93" t="n"/>
-      <c r="AP60" s="93" t="n"/>
-      <c r="AQ60" s="93" t="n"/>
-      <c r="AR60" s="58" t="n"/>
-      <c r="AS60" s="58" t="n"/>
-      <c r="AT60" s="58" t="n"/>
-      <c r="AU60" s="58" t="n"/>
-      <c r="AV60" s="58" t="n"/>
-      <c r="AW60" s="58" t="n"/>
-      <c r="AX60" s="58" t="n"/>
-      <c r="AY60" s="58" t="n"/>
-      <c r="AZ60" s="58" t="n"/>
-      <c r="BA60" s="58" t="n"/>
-      <c r="BB60" s="29" t="n"/>
-    </row>
-    <row r="61" ht="17.25" customHeight="1" s="103">
-      <c r="A61" s="59" t="n"/>
-      <c r="B61" s="60" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C61" s="61" t="inlineStr">
-        <is>
-          <t>[4주] 벡터DB/GraphDB 구축 결과서</t>
-        </is>
-      </c>
-      <c r="D61" s="96" t="inlineStr">
-        <is>
-          <t>권세진</t>
-        </is>
-      </c>
-      <c r="E61" s="63" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F61" s="63" t="n">
-        <v>46318</v>
-      </c>
-      <c r="G61" s="64" t="n">
-        <v>7</v>
-      </c>
-      <c r="H61" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="77" t="n"/>
-      <c r="J61" s="79" t="n"/>
-      <c r="K61" s="72" t="n"/>
-      <c r="L61" s="72" t="n"/>
-      <c r="M61" s="72" t="n"/>
-      <c r="N61" s="70" t="n"/>
-      <c r="O61" s="71" t="n"/>
-      <c r="P61" s="71" t="n"/>
-      <c r="Q61" s="71" t="n"/>
-      <c r="R61" s="70" t="n"/>
-      <c r="S61" s="72" t="n"/>
-      <c r="T61" s="72" t="n"/>
-      <c r="U61" s="72" t="n"/>
-      <c r="V61" s="94" t="n"/>
-      <c r="W61" s="94" t="n"/>
-      <c r="X61" s="94" t="n"/>
-      <c r="Y61" s="94" t="n"/>
-      <c r="Z61" s="94" t="n"/>
-      <c r="AA61" s="94" t="n"/>
-      <c r="AB61" s="95" t="n"/>
-      <c r="AC61" s="73" t="n"/>
-      <c r="AD61" s="73" t="n"/>
-      <c r="AE61" s="73" t="n"/>
-      <c r="AF61" s="73" t="n"/>
-      <c r="AG61" s="73" t="n"/>
-      <c r="AH61" s="72" t="n"/>
-      <c r="AI61" s="72" t="n"/>
-      <c r="AJ61" s="72" t="n"/>
-      <c r="AK61" s="72" t="n"/>
-      <c r="AL61" s="72" t="n"/>
-      <c r="AM61" s="72" t="n"/>
-      <c r="AN61" s="72" t="n"/>
-      <c r="AO61" s="72" t="n"/>
-      <c r="AP61" s="72" t="n"/>
-      <c r="AQ61" s="72" t="n"/>
-      <c r="AR61" s="74" t="n"/>
-      <c r="AS61" s="74" t="n"/>
-      <c r="AT61" s="74" t="n"/>
-      <c r="AU61" s="74" t="n"/>
-      <c r="AV61" s="74" t="n"/>
-      <c r="AW61" s="72" t="n"/>
-      <c r="AX61" s="72" t="n"/>
-      <c r="AY61" s="72" t="n"/>
-      <c r="AZ61" s="72" t="n"/>
-      <c r="BA61" s="72" t="n"/>
-      <c r="BB61" s="75" t="n"/>
+      <c r="I61" s="58" t="n"/>
+      <c r="J61" s="84" t="n"/>
+      <c r="K61" s="111" t="n"/>
+      <c r="L61" s="111" t="n"/>
+      <c r="M61" s="58" t="n"/>
+      <c r="N61" s="57" t="n"/>
+      <c r="O61" s="58" t="n"/>
+      <c r="P61" s="58" t="n"/>
+      <c r="Q61" s="58" t="n"/>
+      <c r="R61" s="57" t="n"/>
+      <c r="S61" s="58" t="n"/>
+      <c r="T61" s="58" t="n"/>
+      <c r="U61" s="58" t="n"/>
+      <c r="V61" s="93" t="n"/>
+      <c r="W61" s="93" t="n"/>
+      <c r="X61" s="93" t="n"/>
+      <c r="Y61" s="93" t="n"/>
+      <c r="Z61" s="93" t="n"/>
+      <c r="AA61" s="93" t="n"/>
+      <c r="AB61" s="93" t="n"/>
+      <c r="AC61" s="93" t="n"/>
+      <c r="AD61" s="93" t="n"/>
+      <c r="AE61" s="93" t="n"/>
+      <c r="AF61" s="93" t="n"/>
+      <c r="AG61" s="93" t="n"/>
+      <c r="AH61" s="93" t="n"/>
+      <c r="AI61" s="93" t="n"/>
+      <c r="AJ61" s="93" t="n"/>
+      <c r="AK61" s="93" t="n"/>
+      <c r="AL61" s="93" t="n"/>
+      <c r="AM61" s="93" t="n"/>
+      <c r="AN61" s="93" t="n"/>
+      <c r="AO61" s="93" t="n"/>
+      <c r="AP61" s="93" t="n"/>
+      <c r="AQ61" s="93" t="n"/>
+      <c r="AR61" s="58" t="n"/>
+      <c r="AS61" s="58" t="n"/>
+      <c r="AT61" s="58" t="n"/>
+      <c r="AU61" s="58" t="n"/>
+      <c r="AV61" s="58" t="n"/>
+      <c r="AW61" s="58" t="n"/>
+      <c r="AX61" s="58" t="n"/>
+      <c r="AY61" s="58" t="n"/>
+      <c r="AZ61" s="58" t="n"/>
+      <c r="BA61" s="58" t="n"/>
+      <c r="BB61" s="29" t="n"/>
     </row>
     <row r="62" ht="17.25" customHeight="1" s="103">
       <c r="A62" s="59" t="n"/>
-      <c r="B62" s="60" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="C62" s="82" t="inlineStr">
-        <is>
-          <t>금융 용어·가이드 지식원·임베딩 기준 선정</t>
+      <c r="B62" s="60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C62" s="61" t="inlineStr">
+        <is>
+          <t>[4주] 벡터DB/GraphDB 구축 결과서</t>
         </is>
       </c>
       <c r="D62" s="96" t="inlineStr">
@@ -5692,13 +5700,13 @@
         </is>
       </c>
       <c r="E62" s="63" t="n">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="F62" s="63" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="G62" s="64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H62" s="65" t="n">
         <v>0</v>
@@ -5716,13 +5724,13 @@
       <c r="S62" s="72" t="n"/>
       <c r="T62" s="72" t="n"/>
       <c r="U62" s="72" t="n"/>
-      <c r="V62" s="94" t="n"/>
-      <c r="W62" s="94" t="n"/>
+      <c r="V62" s="72" t="n"/>
+      <c r="W62" s="72" t="n"/>
       <c r="X62" s="94" t="n"/>
-      <c r="Y62" s="72" t="n"/>
-      <c r="Z62" s="72" t="n"/>
-      <c r="AA62" s="72" t="n"/>
-      <c r="AB62" s="72" t="n"/>
+      <c r="Y62" s="94" t="n"/>
+      <c r="Z62" s="94" t="n"/>
+      <c r="AA62" s="94" t="n"/>
+      <c r="AB62" s="95" t="n"/>
       <c r="AC62" s="73" t="n"/>
       <c r="AD62" s="73" t="n"/>
       <c r="AE62" s="73" t="n"/>
@@ -5754,7 +5762,7 @@
       <c r="A63" s="59" t="n"/>
       <c r="B63" s="60" t="inlineStr">
         <is>
-          <t>4.1.2</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="C63" s="82" t="inlineStr">
@@ -5830,7 +5838,7 @@
       <c r="A64" s="59" t="n"/>
       <c r="B64" s="60" t="inlineStr">
         <is>
-          <t>4.1.3</t>
+          <t>4.1.2</t>
         </is>
       </c>
       <c r="C64" s="82" t="inlineStr">
@@ -5985,7 +5993,7 @@
       </c>
       <c r="C66" s="82" t="inlineStr">
         <is>
-          <t xml:space="preserve">라우터 매핑·의도 목록·요청 정보 형식 정의</t>
+          <t>라우터 매핑·의도 목록·요청 정보 형식 정의</t>
         </is>
       </c>
       <c r="D66" s="96" t="inlineStr">
@@ -6363,7 +6371,7 @@
       </c>
       <c r="C71" s="82" t="inlineStr">
         <is>
-          <t xml:space="preserve">(1차) LLM 라우터·통합 챗봇 입력창·선택지·전환</t>
+          <t>(1차) LLM 라우터·통합 챗봇 입력창·선택지·전환</t>
         </is>
       </c>
       <c r="D71" s="96" t="inlineStr">
@@ -8098,7 +8106,7 @@
       </c>
       <c r="D94" s="96" t="inlineStr">
         <is>
-          <t>권세진</t>
+          <t>김나은</t>
         </is>
       </c>
       <c r="E94" s="63" t="n">
@@ -9093,7 +9101,7 @@
         <v>30</v>
       </c>
       <c r="H107" s="53" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="I107" s="58" t="n"/>
       <c r="J107" s="84" t="n"/>
@@ -9167,7 +9175,7 @@
         <v>5</v>
       </c>
       <c r="H108" s="65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="77" t="n"/>
       <c r="J108" s="79" t="n"/>
@@ -9243,7 +9251,7 @@
         <v>4</v>
       </c>
       <c r="H109" s="65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="77" t="n"/>
       <c r="J109" s="79" t="n"/>
@@ -9319,7 +9327,7 @@
         <v>2</v>
       </c>
       <c r="H110" s="65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="77" t="n"/>
       <c r="J110" s="79" t="n"/>

--- a/산출물/01_기획/4팀_WBS.xlsx
+++ b/산출물/01_기획/4팀_WBS.xlsx
@@ -8253,7 +8253,7 @@
       </c>
       <c r="C96" s="82" t="inlineStr">
         <is>
-          <t>(1차) 온보딩·추천 예산(자물쇠·초안 수정)·조정·승인 화면</t>
+          <t>(1차) 온보딩(카테고리 최소 금액 팝업 포함)·추천 예산(자물쇠·초안 수정)·조정·승인 화면</t>
         </is>
       </c>
       <c r="D96" s="96" t="inlineStr">
